--- a/Advanced Excel for practice.xlsx
+++ b/Advanced Excel for practice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f1c7af14bfcc0abe/Desktop/DA DS ITV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAC444C-25A8-4E7A-A263-1D3A79421BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{2BAC444C-25A8-4E7A-A263-1D3A79421BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B92475C-6C78-4B1D-A660-910B31DADB7A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="645" firstSheet="15" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formulas" sheetId="19" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="Advanced Logical Operators " sheetId="29" r:id="rId3"/>
     <sheet name="Database Functions" sheetId="36" r:id="rId4"/>
     <sheet name="Stats Functions" sheetId="10" r:id="rId5"/>
-    <sheet name="State Abbreviations" sheetId="12" r:id="rId6"/>
-    <sheet name="State Income (2001-2004)" sheetId="13" r:id="rId7"/>
+    <sheet name="State Income (2001-2004)" sheetId="13" r:id="rId6"/>
+    <sheet name="State Abbreviations" sheetId="12" r:id="rId7"/>
     <sheet name="Lookup Functions" sheetId="11" r:id="rId8"/>
     <sheet name="Advanced VLOOKUP" sheetId="33" r:id="rId9"/>
     <sheet name="VLOOKUP RANGE" sheetId="34" r:id="rId10"/>
@@ -37,6 +37,8 @@
     <sheet name="Consolidate Summary" sheetId="40" r:id="rId22"/>
   </sheets>
   <definedNames>
+    <definedName name="_2015_Sales">'Advanced Logical Operators '!$D$2:$D$16</definedName>
+    <definedName name="_2016_Sales">'Advanced Logical Operators '!$E$2:$E$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Advanced VLOOKUP'!$A$9:$I$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Cleaning data'!$A$1:$V$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Database Functions'!$B$4:$G$34</definedName>
@@ -76,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6301" uniqueCount="3548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6360" uniqueCount="3570">
   <si>
     <t>State</t>
   </si>
@@ -10745,6 +10747,72 @@
   </si>
   <si>
     <t>In case of no product found output should be "No Amount"</t>
+  </si>
+  <si>
+    <t>SMALL</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>LARGE</t>
+  </si>
+  <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Xl</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>133462|AA-BOS_SMALL</t>
+  </si>
+  <si>
+    <t>191768|AC-NYC_MEDIUM</t>
+  </si>
+  <si>
+    <t>157263|BB-BOS_XL</t>
+  </si>
+  <si>
+    <t>1734372|AA-CHI_SMALL</t>
+  </si>
+  <si>
+    <t>135351|BC-NYC_XL</t>
+  </si>
+  <si>
+    <t>14330305|AC-BOS_LARGE</t>
+  </si>
+  <si>
+    <t>177772|BB-NYC_MEDIUM</t>
+  </si>
+  <si>
+    <t>87192837|AB-CHI_XL</t>
+  </si>
+  <si>
+    <t>161266|BB-CHI_SMALL</t>
+  </si>
+  <si>
+    <t>122892|AA-NYC_MEDIUM</t>
+  </si>
+  <si>
+    <t>128919|AC-CHI_XL</t>
+  </si>
+  <si>
+    <t>191999|BB-BOS_LARGE</t>
+  </si>
+  <si>
+    <t>117091126|BC-NYC_LARGE</t>
+  </si>
+  <si>
+    <t>112283|AB-BOS_MEDIUM</t>
   </si>
 </sst>
 </file>
@@ -11449,7 +11517,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11585,9 +11653,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="21" borderId="11" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="13" borderId="12" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="170" fontId="2" fillId="20" borderId="12" xfId="16" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -11788,6 +11853,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="12" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="17" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent2" xfId="12" builtinId="34"/>
@@ -13468,16 +13537,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>349250</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>295910</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>194310</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -13507,8 +13576,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6013450" y="222250"/>
-          <a:ext cx="4387850" cy="2730500"/>
+          <a:off x="6498590" y="182880"/>
+          <a:ext cx="4325620" cy="2711450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13535,15 +13604,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>35560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>234950</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>48260</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -13573,8 +13642,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4495800" y="768350"/>
-          <a:ext cx="3232150" cy="1447800"/>
+          <a:off x="4699000" y="35560"/>
+          <a:ext cx="3194050" cy="1521460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14116,16 +14185,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>346710</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>179070</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>521970</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>435610</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1270</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>2540</xdr:rowOff>
+      <xdr:rowOff>40640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -14155,7 +14224,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="9345930" y="179070"/>
+          <a:off x="10130790" y="217170"/>
           <a:ext cx="3746500" cy="1286510"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -15951,8 +16020,14 @@
       <c r="D2" s="2">
         <v>18</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="E2" s="41">
+        <f>C2/B2</f>
+        <v>0.5273972602739726</v>
+      </c>
+      <c r="F2" s="41">
+        <f>D2/B2</f>
+        <v>0.12328767123287671</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="20">
@@ -15967,8 +16042,14 @@
       <c r="D3" s="2">
         <v>15</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="E3" s="41">
+        <f t="shared" ref="E3:E26" si="0">C3/B3</f>
+        <v>0.42603550295857989</v>
+      </c>
+      <c r="F3" s="41">
+        <f t="shared" ref="F3:F26" si="1">D3/B3</f>
+        <v>8.8757396449704137E-2</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="20">
@@ -15983,8 +16064,14 @@
       <c r="D4" s="2">
         <v>19</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
+      <c r="E4" s="41">
+        <f t="shared" si="0"/>
+        <v>0.35678391959798994</v>
+      </c>
+      <c r="F4" s="41">
+        <f t="shared" si="1"/>
+        <v>9.5477386934673364E-2</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="20">
@@ -15999,8 +16086,14 @@
       <c r="D5" s="2">
         <v>10</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
+      <c r="E5" s="41">
+        <f t="shared" si="0"/>
+        <v>0.23487544483985764</v>
+      </c>
+      <c r="F5" s="41">
+        <f t="shared" si="1"/>
+        <v>3.5587188612099648E-2</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="20">
@@ -16015,8 +16108,14 @@
       <c r="D6" s="2">
         <v>19</v>
       </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
+      <c r="E6" s="41">
+        <f t="shared" si="0"/>
+        <v>0.19924812030075187</v>
+      </c>
+      <c r="F6" s="41">
+        <f t="shared" si="1"/>
+        <v>7.1428571428571425E-2</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="20">
@@ -16031,8 +16130,14 @@
       <c r="D7" s="2">
         <v>15</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
+      <c r="E7" s="41">
+        <f t="shared" si="0"/>
+        <v>0.30324909747292417</v>
+      </c>
+      <c r="F7" s="41">
+        <f t="shared" si="1"/>
+        <v>5.4151624548736461E-2</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="20">
@@ -16047,8 +16152,14 @@
       <c r="D8" s="2">
         <v>15</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
+      <c r="E8" s="41">
+        <f t="shared" si="0"/>
+        <v>0.50344827586206897</v>
+      </c>
+      <c r="F8" s="41">
+        <f t="shared" si="1"/>
+        <v>0.10344827586206896</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="20">
@@ -16063,8 +16174,14 @@
       <c r="D9" s="2">
         <v>12</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
+      <c r="E9" s="41">
+        <f t="shared" si="0"/>
+        <v>0.30396475770925108</v>
+      </c>
+      <c r="F9" s="41">
+        <f t="shared" si="1"/>
+        <v>5.2863436123348019E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="20">
@@ -16079,8 +16196,14 @@
       <c r="D10" s="2">
         <v>16</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="E10" s="41">
+        <f t="shared" si="0"/>
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="F10" s="41">
+        <f t="shared" si="1"/>
+        <v>8.8888888888888892E-2</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="20">
@@ -16095,8 +16218,14 @@
       <c r="D11" s="2">
         <v>0</v>
       </c>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
+      <c r="E11" s="41" t="str">
+        <f>IFERROR(C11/B11,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F11" s="41" t="str">
+        <f>IFERROR(D11/B11,"-")</f>
+        <v>-</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="20">
@@ -16111,8 +16240,14 @@
       <c r="D12" s="2">
         <v>10</v>
       </c>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
+      <c r="E12" s="41">
+        <f t="shared" si="0"/>
+        <v>0.30991735537190085</v>
+      </c>
+      <c r="F12" s="41">
+        <f t="shared" si="1"/>
+        <v>4.1322314049586778E-2</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="20">
@@ -16127,8 +16262,14 @@
       <c r="D13" s="2">
         <v>16</v>
       </c>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
+      <c r="E13" s="41">
+        <f t="shared" si="0"/>
+        <v>0.34883720930232559</v>
+      </c>
+      <c r="F13" s="41">
+        <f t="shared" si="1"/>
+        <v>7.441860465116279E-2</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
@@ -16143,8 +16284,14 @@
       <c r="D14" s="2">
         <v>16</v>
       </c>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
+      <c r="E14" s="41">
+        <f t="shared" si="0"/>
+        <v>0.33606557377049179</v>
+      </c>
+      <c r="F14" s="41">
+        <f t="shared" si="1"/>
+        <v>6.5573770491803282E-2</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="20">
@@ -16159,8 +16306,14 @@
       <c r="D15" s="2">
         <v>13</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
+      <c r="E15" s="41">
+        <f t="shared" si="0"/>
+        <v>0.39664804469273746</v>
+      </c>
+      <c r="F15" s="41">
+        <f t="shared" si="1"/>
+        <v>7.2625698324022353E-2</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="20">
@@ -16175,8 +16328,14 @@
       <c r="D16" s="2">
         <v>14</v>
       </c>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
+      <c r="E16" s="41">
+        <f t="shared" si="0"/>
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="F16" s="41">
+        <f t="shared" si="1"/>
+        <v>5.0724637681159424E-2</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="20">
@@ -16191,8 +16350,14 @@
       <c r="D17" s="2">
         <v>20</v>
       </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
+      <c r="E17" s="41">
+        <f t="shared" si="0"/>
+        <v>0.61417322834645671</v>
+      </c>
+      <c r="F17" s="41">
+        <f t="shared" si="1"/>
+        <v>0.15748031496062992</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="20">
@@ -16207,8 +16372,14 @@
       <c r="D18" s="2">
         <v>18</v>
       </c>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
+      <c r="E18" s="41">
+        <f t="shared" si="0"/>
+        <v>0.2756183745583039</v>
+      </c>
+      <c r="F18" s="41">
+        <f t="shared" si="1"/>
+        <v>6.3604240282685506E-2</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="20">
@@ -16223,8 +16394,14 @@
       <c r="D19" s="2">
         <v>20</v>
       </c>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
+      <c r="E19" s="41">
+        <f t="shared" si="0"/>
+        <v>0.60317460317460314</v>
+      </c>
+      <c r="F19" s="41">
+        <f t="shared" si="1"/>
+        <v>0.15873015873015872</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="20">
@@ -16239,8 +16416,14 @@
       <c r="D20" s="2">
         <v>19</v>
       </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
+      <c r="E20" s="41">
+        <f t="shared" si="0"/>
+        <v>0.30916030534351147</v>
+      </c>
+      <c r="F20" s="41">
+        <f t="shared" si="1"/>
+        <v>7.2519083969465645E-2</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
@@ -16255,8 +16438,14 @@
       <c r="D21" s="2">
         <v>14</v>
       </c>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
+      <c r="E21" s="41">
+        <f t="shared" si="0"/>
+        <v>0.28222996515679444</v>
+      </c>
+      <c r="F21" s="41">
+        <f t="shared" si="1"/>
+        <v>4.878048780487805E-2</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="20">
@@ -16271,8 +16460,14 @@
       <c r="D22" s="2">
         <v>14</v>
       </c>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
+      <c r="E22" s="41">
+        <f t="shared" si="0"/>
+        <v>0.30483271375464682</v>
+      </c>
+      <c r="F22" s="41">
+        <f t="shared" si="1"/>
+        <v>5.204460966542751E-2</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="20">
@@ -16287,8 +16482,14 @@
       <c r="D23" s="2">
         <v>10</v>
       </c>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
+      <c r="E23" s="41">
+        <f t="shared" si="0"/>
+        <v>0.19852941176470587</v>
+      </c>
+      <c r="F23" s="41">
+        <f t="shared" si="1"/>
+        <v>3.6764705882352942E-2</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="20">
@@ -16303,8 +16504,14 @@
       <c r="D24" s="2">
         <v>11</v>
       </c>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
+      <c r="E24" s="41">
+        <f t="shared" si="0"/>
+        <v>0.33823529411764708</v>
+      </c>
+      <c r="F24" s="41">
+        <f t="shared" si="1"/>
+        <v>5.3921568627450983E-2</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="20">
@@ -16319,8 +16526,14 @@
       <c r="D25" s="2">
         <v>20</v>
       </c>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
+      <c r="E25" s="41">
+        <f t="shared" si="0"/>
+        <v>0.48</v>
+      </c>
+      <c r="F25" s="41">
+        <f t="shared" si="1"/>
+        <v>0.13333333333333333</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="20">
@@ -16335,8 +16548,14 @@
       <c r="D26" s="2">
         <v>19</v>
       </c>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
+      <c r="E26" s="41">
+        <f t="shared" si="0"/>
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="F26" s="41">
+        <f t="shared" si="1"/>
+        <v>7.2796934865900387E-2</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="25"/>
@@ -16367,171 +16586,171 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="123" t="s">
         <v>3463</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="75" t="s">
         <v>3462</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="75" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="75" t="s">
         <v>3459</v>
       </c>
-      <c r="E3" s="119" t="s">
+      <c r="E3" s="118" t="s">
         <v>3461</v>
       </c>
-      <c r="F3" s="120"/>
-      <c r="G3" s="121"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="120"/>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="72" t="s">
         <v>3460</v>
       </c>
-      <c r="B4" s="72">
+      <c r="B4" s="71">
         <v>1200</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="E4" s="75" t="s">
+      <c r="C4" s="70"/>
+      <c r="E4" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="74" t="s">
+      <c r="F4" s="73" t="s">
         <v>3459</v>
       </c>
-      <c r="G4" s="74" t="s">
+      <c r="G4" s="73" t="s">
         <v>3451</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="72" t="s">
         <v>3458</v>
       </c>
-      <c r="B5" s="72">
+      <c r="B5" s="71">
         <v>1300</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="E5" s="70">
+      <c r="C5" s="70"/>
+      <c r="E5" s="69">
         <v>0</v>
       </c>
-      <c r="F5" s="70">
+      <c r="F5" s="69">
         <v>0</v>
       </c>
-      <c r="G5" s="70">
+      <c r="G5" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="72" t="s">
         <v>3457</v>
       </c>
-      <c r="B6" s="72">
+      <c r="B6" s="71">
         <v>2500</v>
       </c>
-      <c r="C6" s="71"/>
-      <c r="E6" s="70">
+      <c r="C6" s="70"/>
+      <c r="E6" s="69">
         <v>1000</v>
       </c>
-      <c r="F6" s="70">
+      <c r="F6" s="69">
         <v>10</v>
       </c>
-      <c r="G6" s="70">
+      <c r="G6" s="69">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="72" t="s">
         <v>3456</v>
       </c>
-      <c r="B7" s="72">
+      <c r="B7" s="71">
         <v>850</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="E7" s="70">
+      <c r="C7" s="70"/>
+      <c r="E7" s="69">
         <v>1500</v>
       </c>
-      <c r="F7" s="70">
+      <c r="F7" s="69">
         <v>30</v>
       </c>
-      <c r="G7" s="70">
+      <c r="G7" s="69">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="72" t="s">
         <v>3455</v>
       </c>
-      <c r="B8" s="72">
+      <c r="B8" s="71">
         <v>3250</v>
       </c>
-      <c r="C8" s="71"/>
-      <c r="E8" s="70">
+      <c r="C8" s="70"/>
+      <c r="E8" s="69">
         <v>2000</v>
       </c>
-      <c r="F8" s="70">
+      <c r="F8" s="69">
         <v>85</v>
       </c>
-      <c r="G8" s="70">
+      <c r="G8" s="69">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="72" t="s">
         <v>3454</v>
       </c>
-      <c r="B9" s="72">
+      <c r="B9" s="71">
         <v>1100</v>
       </c>
-      <c r="C9" s="71"/>
-      <c r="E9" s="70">
+      <c r="C9" s="70"/>
+      <c r="E9" s="69">
         <v>2500</v>
       </c>
-      <c r="F9" s="70">
+      <c r="F9" s="69">
         <v>125</v>
       </c>
-      <c r="G9" s="70">
+      <c r="G9" s="69">
         <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="72" t="s">
         <v>3453</v>
       </c>
-      <c r="B10" s="72">
+      <c r="B10" s="71">
         <v>4520</v>
       </c>
-      <c r="C10" s="71"/>
-      <c r="E10" s="70">
+      <c r="C10" s="70"/>
+      <c r="E10" s="69">
         <v>3000</v>
       </c>
-      <c r="F10" s="70">
+      <c r="F10" s="69">
         <v>200</v>
       </c>
-      <c r="G10" s="70">
+      <c r="G10" s="69">
         <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="122" t="s">
+      <c r="A12" s="121" t="s">
         <v>3452</v>
       </c>
-      <c r="B12" s="123"/>
-      <c r="C12" s="69" t="s">
+      <c r="B12" s="122"/>
+      <c r="C12" s="68" t="s">
         <v>3451</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="E13" s="68"/>
+      <c r="E13" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -16558,157 +16777,157 @@
   <dimension ref="A2:G14"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="77" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="10.21875" style="77" customWidth="1"/>
-    <col min="8" max="16384" width="9.21875" style="77"/>
+    <col min="1" max="1" width="19.44140625" style="76" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.21875" style="76" customWidth="1"/>
+    <col min="8" max="16384" width="9.21875" style="76"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="125" t="s">
         <v>3477</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
     </row>
     <row r="4" spans="1:7" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="125" t="s">
+      <c r="A4" s="124" t="s">
         <v>3476</v>
       </c>
-      <c r="B4" s="125"/>
-      <c r="E4" s="77" t="s">
+      <c r="B4" s="124"/>
+      <c r="E4" s="76" t="s">
         <v>3547</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="77" t="s">
         <v>3475</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="79" t="s">
         <v>3469</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="77" t="s">
         <v>3466</v>
       </c>
-      <c r="B6" s="65"/>
+      <c r="B6" s="64"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="77" t="s">
         <v>3465</v>
       </c>
-      <c r="B7" s="65"/>
+      <c r="B7" s="64"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="77" t="s">
         <v>3464</v>
       </c>
-      <c r="B8" s="65"/>
+      <c r="B8" s="64"/>
     </row>
     <row r="10" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="125" t="s">
+      <c r="A10" s="124" t="s">
         <v>3474</v>
       </c>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="124"/>
     </row>
     <row r="11" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="77" t="s">
         <v>3473</v>
       </c>
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="64" t="s">
         <v>3472</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="78" t="s">
         <v>3471</v>
       </c>
-      <c r="D11" s="65" t="s">
+      <c r="D11" s="64" t="s">
         <v>3470</v>
       </c>
-      <c r="E11" s="79" t="s">
+      <c r="E11" s="78" t="s">
         <v>3469</v>
       </c>
-      <c r="F11" s="65" t="s">
+      <c r="F11" s="64" t="s">
         <v>3468</v>
       </c>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="78" t="s">
         <v>3467</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="77" t="s">
         <v>3466</v>
       </c>
-      <c r="B12" s="65">
+      <c r="B12" s="64">
         <v>120</v>
       </c>
-      <c r="C12" s="74">
+      <c r="C12" s="73">
         <v>150</v>
       </c>
-      <c r="D12" s="65">
+      <c r="D12" s="64">
         <v>135</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E12" s="73">
         <v>90</v>
       </c>
-      <c r="F12" s="65">
+      <c r="F12" s="64">
         <v>95</v>
       </c>
-      <c r="G12" s="74">
+      <c r="G12" s="73">
         <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="77" t="s">
         <v>3465</v>
       </c>
-      <c r="B13" s="65">
+      <c r="B13" s="64">
         <v>55</v>
       </c>
-      <c r="C13" s="74">
+      <c r="C13" s="73">
         <v>110</v>
       </c>
-      <c r="D13" s="65">
+      <c r="D13" s="64">
         <v>75</v>
       </c>
-      <c r="E13" s="74">
+      <c r="E13" s="73">
         <v>95</v>
       </c>
-      <c r="F13" s="65">
+      <c r="F13" s="64">
         <v>75</v>
       </c>
-      <c r="G13" s="74">
+      <c r="G13" s="73">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="77" t="s">
         <v>3464</v>
       </c>
-      <c r="B14" s="65">
+      <c r="B14" s="64">
         <v>70</v>
       </c>
-      <c r="C14" s="74">
+      <c r="C14" s="73">
         <v>115</v>
       </c>
-      <c r="D14" s="65">
+      <c r="D14" s="64">
         <v>65</v>
       </c>
-      <c r="E14" s="74">
+      <c r="E14" s="73">
         <v>55</v>
       </c>
-      <c r="F14" s="65">
+      <c r="F14" s="64">
         <v>85</v>
       </c>
-      <c r="G14" s="74">
+      <c r="G14" s="73">
         <v>65</v>
       </c>
     </row>
@@ -17500,155 +17719,295 @@
       <c r="A2" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="33">
+        <v>133462</v>
+      </c>
       <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
+      <c r="D2" s="33" t="s">
+        <v>3552</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>3548</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>3556</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="33">
+        <v>191768</v>
+      </c>
       <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
+      <c r="D3" s="33" t="s">
+        <v>3553</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>3549</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>3557</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="B4" s="33"/>
+      <c r="B4" s="33">
+        <v>157263</v>
+      </c>
       <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
+      <c r="D4" s="33" t="s">
+        <v>3554</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>3550</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>3558</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="33">
+        <v>1734372</v>
+      </c>
       <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
+      <c r="D5" s="33" t="s">
+        <v>3552</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>3548</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>3559</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="33">
+        <v>135351</v>
+      </c>
       <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
+      <c r="D6" s="33" t="s">
+        <v>3554</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>3550</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>3560</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="B7" s="33"/>
+      <c r="B7" s="33">
+        <v>14330305</v>
+      </c>
       <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
+      <c r="D7" s="33" t="s">
+        <v>3555</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>3551</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>3561</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="33">
+        <v>177772</v>
+      </c>
       <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
+      <c r="D8" s="33" t="s">
+        <v>3553</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>3549</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>3562</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="B9" s="33"/>
+      <c r="B9" s="33">
+        <v>87192837</v>
+      </c>
       <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
+      <c r="D9" s="33" t="s">
+        <v>3554</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>3550</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>3563</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="33">
+        <v>161266</v>
+      </c>
       <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
+      <c r="D10" s="33" t="s">
+        <v>3552</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>3548</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>3564</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="33"/>
+      <c r="B11" s="33">
+        <v>122892</v>
+      </c>
       <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
+      <c r="D11" s="33" t="s">
+        <v>3553</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>3549</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>3565</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="33">
+        <v>128919</v>
+      </c>
       <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
+      <c r="D12" s="33" t="s">
+        <v>3554</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>3550</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>3566</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="33"/>
+      <c r="B13" s="33">
+        <v>191999</v>
+      </c>
       <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
+      <c r="D13" s="33" t="s">
+        <v>3555</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>3551</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>3567</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="B14" s="33"/>
+      <c r="B14" s="33">
+        <v>117091126</v>
+      </c>
       <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
+      <c r="D14" s="33" t="s">
+        <v>3555</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>3551</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>3568</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="B15" s="33"/>
+      <c r="B15" s="33">
+        <v>112283</v>
+      </c>
       <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
+      <c r="D15" s="33" t="s">
+        <v>3553</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>3549</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>3569</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>202</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35271,11 +35630,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5546875" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" style="99" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" style="99" customWidth="1"/>
-    <col min="4" max="5" width="14.88671875" style="99" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" style="98" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" style="98" customWidth="1"/>
+    <col min="4" max="5" width="14.88671875" style="98" customWidth="1"/>
     <col min="6" max="6" width="24" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.44140625" style="98" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="97" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -35305,23 +35664,23 @@
       <c r="A2" s="20">
         <v>41640</v>
       </c>
-      <c r="B2" s="110">
+      <c r="B2" s="109">
         <v>1099</v>
       </c>
-      <c r="C2" s="110">
+      <c r="C2" s="109">
         <v>275</v>
       </c>
-      <c r="D2" s="110">
+      <c r="D2" s="109">
         <v>643</v>
       </c>
-      <c r="E2" s="110">
+      <c r="E2" s="109">
         <f>B2-D2</f>
         <v>456</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G2" s="109">
+      <c r="G2" s="108">
         <f t="shared" ref="G2:G25" si="0">E2/B2</f>
         <v>0.41492265696087355</v>
       </c>
@@ -35330,23 +35689,23 @@
       <c r="A3" s="20">
         <v>41671</v>
       </c>
-      <c r="B3" s="110">
+      <c r="B3" s="109">
         <v>1204</v>
       </c>
-      <c r="C3" s="110">
+      <c r="C3" s="109">
         <f t="shared" ref="C3:C25" si="1">B3-B2</f>
         <v>105</v>
       </c>
-      <c r="D3" s="110">
+      <c r="D3" s="109">
         <v>720</v>
       </c>
-      <c r="E3" s="110">
+      <c r="E3" s="109">
         <v>211</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="109">
+      <c r="G3" s="108">
         <f t="shared" si="0"/>
         <v>0.17524916943521596</v>
       </c>
@@ -35355,24 +35714,24 @@
       <c r="A4" s="20">
         <v>41699</v>
       </c>
-      <c r="B4" s="110">
+      <c r="B4" s="109">
         <v>1944</v>
       </c>
-      <c r="C4" s="110">
+      <c r="C4" s="109">
         <f t="shared" si="1"/>
         <v>740</v>
       </c>
-      <c r="D4" s="110">
+      <c r="D4" s="109">
         <v>964</v>
       </c>
-      <c r="E4" s="110">
+      <c r="E4" s="109">
         <f t="shared" ref="E4:E19" si="2">B4-D4</f>
         <v>980</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>3517</v>
       </c>
-      <c r="G4" s="109">
+      <c r="G4" s="108">
         <f t="shared" si="0"/>
         <v>0.50411522633744854</v>
       </c>
@@ -35381,24 +35740,24 @@
       <c r="A5" s="20">
         <v>41730</v>
       </c>
-      <c r="B5" s="110">
+      <c r="B5" s="109">
         <v>1743</v>
       </c>
-      <c r="C5" s="110">
+      <c r="C5" s="109">
         <f t="shared" si="1"/>
         <v>-201</v>
       </c>
-      <c r="D5" s="110">
+      <c r="D5" s="109">
         <v>830</v>
       </c>
-      <c r="E5" s="110">
+      <c r="E5" s="109">
         <f t="shared" si="2"/>
         <v>913</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="109">
+      <c r="G5" s="108">
         <f t="shared" si="0"/>
         <v>0.52380952380952384</v>
       </c>
@@ -35407,24 +35766,24 @@
       <c r="A6" s="20">
         <v>41760</v>
       </c>
-      <c r="B6" s="110">
+      <c r="B6" s="109">
         <v>1609</v>
       </c>
-      <c r="C6" s="110">
+      <c r="C6" s="109">
         <f t="shared" si="1"/>
         <v>-134</v>
       </c>
-      <c r="D6" s="110">
+      <c r="D6" s="109">
         <v>910</v>
       </c>
-      <c r="E6" s="110">
+      <c r="E6" s="109">
         <f t="shared" si="2"/>
         <v>699</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G6" s="109">
+      <c r="G6" s="108">
         <f t="shared" si="0"/>
         <v>0.43443132380360472</v>
       </c>
@@ -35433,24 +35792,24 @@
       <c r="A7" s="20">
         <v>41791</v>
       </c>
-      <c r="B7" s="110">
+      <c r="B7" s="109">
         <v>1494</v>
       </c>
-      <c r="C7" s="110">
+      <c r="C7" s="109">
         <f t="shared" si="1"/>
         <v>-115</v>
       </c>
-      <c r="D7" s="110">
+      <c r="D7" s="109">
         <v>909</v>
       </c>
-      <c r="E7" s="110">
+      <c r="E7" s="109">
         <f t="shared" si="2"/>
         <v>585</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G7" s="109">
+      <c r="G7" s="108">
         <f t="shared" si="0"/>
         <v>0.39156626506024095</v>
       </c>
@@ -35459,24 +35818,24 @@
       <c r="A8" s="20">
         <v>41821</v>
       </c>
-      <c r="B8" s="110">
+      <c r="B8" s="109">
         <v>1959</v>
       </c>
-      <c r="C8" s="110">
+      <c r="C8" s="109">
         <f t="shared" si="1"/>
         <v>465</v>
       </c>
-      <c r="D8" s="110">
+      <c r="D8" s="109">
         <v>830</v>
       </c>
-      <c r="E8" s="110">
+      <c r="E8" s="109">
         <f t="shared" si="2"/>
         <v>1129</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G8" s="109">
+      <c r="G8" s="108">
         <f t="shared" si="0"/>
         <v>0.57631444614599281</v>
       </c>
@@ -35485,24 +35844,24 @@
       <c r="A9" s="20">
         <v>41852</v>
       </c>
-      <c r="B9" s="110">
+      <c r="B9" s="109">
         <v>1868</v>
       </c>
-      <c r="C9" s="110">
+      <c r="C9" s="109">
         <f t="shared" si="1"/>
         <v>-91</v>
       </c>
-      <c r="D9" s="110">
+      <c r="D9" s="109">
         <v>906</v>
       </c>
-      <c r="E9" s="110">
+      <c r="E9" s="109">
         <f t="shared" si="2"/>
         <v>962</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="109">
+      <c r="G9" s="108">
         <f t="shared" si="0"/>
         <v>0.51498929336188437</v>
       </c>
@@ -35511,24 +35870,24 @@
       <c r="A10" s="20">
         <v>41883</v>
       </c>
-      <c r="B10" s="110">
+      <c r="B10" s="109">
         <v>1162</v>
       </c>
-      <c r="C10" s="110">
+      <c r="C10" s="109">
         <f t="shared" si="1"/>
         <v>-706</v>
       </c>
-      <c r="D10" s="110">
+      <c r="D10" s="109">
         <v>606</v>
       </c>
-      <c r="E10" s="110">
+      <c r="E10" s="109">
         <f t="shared" si="2"/>
         <v>556</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>3517</v>
       </c>
-      <c r="G10" s="109">
+      <c r="G10" s="108">
         <f t="shared" si="0"/>
         <v>0.47848537005163511</v>
       </c>
@@ -35537,24 +35896,24 @@
       <c r="A11" s="20">
         <v>41913</v>
       </c>
-      <c r="B11" s="110">
+      <c r="B11" s="109">
         <v>1424</v>
       </c>
-      <c r="C11" s="110">
+      <c r="C11" s="109">
         <f t="shared" si="1"/>
         <v>262</v>
       </c>
-      <c r="D11" s="110">
+      <c r="D11" s="109">
         <v>943</v>
       </c>
-      <c r="E11" s="110">
+      <c r="E11" s="109">
         <f t="shared" si="2"/>
         <v>481</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>3517</v>
       </c>
-      <c r="G11" s="109">
+      <c r="G11" s="108">
         <f t="shared" si="0"/>
         <v>0.3377808988764045</v>
       </c>
@@ -35563,24 +35922,24 @@
       <c r="A12" s="20">
         <v>41944</v>
       </c>
-      <c r="B12" s="110">
+      <c r="B12" s="109">
         <v>1232</v>
       </c>
-      <c r="C12" s="110">
+      <c r="C12" s="109">
         <f t="shared" si="1"/>
         <v>-192</v>
       </c>
-      <c r="D12" s="110">
+      <c r="D12" s="109">
         <v>801</v>
       </c>
-      <c r="E12" s="110">
+      <c r="E12" s="109">
         <f t="shared" si="2"/>
         <v>431</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G12" s="109">
+      <c r="G12" s="108">
         <f t="shared" si="0"/>
         <v>0.34983766233766234</v>
       </c>
@@ -35589,24 +35948,24 @@
       <c r="A13" s="20">
         <v>41974</v>
       </c>
-      <c r="B13" s="110">
+      <c r="B13" s="109">
         <v>1738</v>
       </c>
-      <c r="C13" s="110">
+      <c r="C13" s="109">
         <f t="shared" si="1"/>
         <v>506</v>
       </c>
-      <c r="D13" s="110">
+      <c r="D13" s="109">
         <v>786</v>
       </c>
-      <c r="E13" s="110">
+      <c r="E13" s="109">
         <f t="shared" si="2"/>
         <v>952</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G13" s="109">
+      <c r="G13" s="108">
         <f t="shared" si="0"/>
         <v>0.54775604142692746</v>
       </c>
@@ -35615,24 +35974,24 @@
       <c r="A14" s="20">
         <v>42005</v>
       </c>
-      <c r="B14" s="110">
+      <c r="B14" s="109">
         <v>1435</v>
       </c>
-      <c r="C14" s="110">
+      <c r="C14" s="109">
         <f t="shared" si="1"/>
         <v>-303</v>
       </c>
-      <c r="D14" s="110">
+      <c r="D14" s="109">
         <v>575</v>
       </c>
-      <c r="E14" s="110">
+      <c r="E14" s="109">
         <f t="shared" si="2"/>
         <v>860</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G14" s="109">
+      <c r="G14" s="108">
         <f t="shared" si="0"/>
         <v>0.5993031358885017</v>
       </c>
@@ -35641,24 +36000,24 @@
       <c r="A15" s="20">
         <v>42036</v>
       </c>
-      <c r="B15" s="110">
+      <c r="B15" s="109">
         <v>1865</v>
       </c>
-      <c r="C15" s="110">
+      <c r="C15" s="109">
         <f t="shared" si="1"/>
         <v>430</v>
       </c>
-      <c r="D15" s="110">
+      <c r="D15" s="109">
         <v>754</v>
       </c>
-      <c r="E15" s="110">
+      <c r="E15" s="109">
         <f t="shared" si="2"/>
         <v>1111</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G15" s="109">
+      <c r="G15" s="108">
         <f t="shared" si="0"/>
         <v>0.59571045576407511</v>
       </c>
@@ -35667,24 +36026,24 @@
       <c r="A16" s="20">
         <v>42064</v>
       </c>
-      <c r="B16" s="110">
+      <c r="B16" s="109">
         <v>1234</v>
       </c>
-      <c r="C16" s="110">
+      <c r="C16" s="109">
         <f t="shared" si="1"/>
         <v>-631</v>
       </c>
-      <c r="D16" s="110">
+      <c r="D16" s="109">
         <v>599</v>
       </c>
-      <c r="E16" s="110">
+      <c r="E16" s="109">
         <f t="shared" si="2"/>
         <v>635</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G16" s="109">
+      <c r="G16" s="108">
         <f t="shared" si="0"/>
         <v>0.51458670988654787</v>
       </c>
@@ -35693,24 +36052,24 @@
       <c r="A17" s="20">
         <v>42095</v>
       </c>
-      <c r="B17" s="110">
+      <c r="B17" s="109">
         <v>1577</v>
       </c>
-      <c r="C17" s="110">
+      <c r="C17" s="109">
         <f t="shared" si="1"/>
         <v>343</v>
       </c>
-      <c r="D17" s="110">
+      <c r="D17" s="109">
         <v>940</v>
       </c>
-      <c r="E17" s="110">
+      <c r="E17" s="109">
         <f t="shared" si="2"/>
         <v>637</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G17" s="109">
+      <c r="G17" s="108">
         <f t="shared" si="0"/>
         <v>0.40393151553582751</v>
       </c>
@@ -35719,24 +36078,24 @@
       <c r="A18" s="20">
         <v>42125</v>
       </c>
-      <c r="B18" s="110">
+      <c r="B18" s="109">
         <v>1983</v>
       </c>
-      <c r="C18" s="110">
+      <c r="C18" s="109">
         <f t="shared" si="1"/>
         <v>406</v>
       </c>
-      <c r="D18" s="110">
+      <c r="D18" s="109">
         <v>954</v>
       </c>
-      <c r="E18" s="110">
+      <c r="E18" s="109">
         <f t="shared" si="2"/>
         <v>1029</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G18" s="109">
+      <c r="G18" s="108">
         <f t="shared" si="0"/>
         <v>0.51891074130105896</v>
       </c>
@@ -35745,24 +36104,24 @@
       <c r="A19" s="20">
         <v>42156</v>
       </c>
-      <c r="B19" s="110">
+      <c r="B19" s="109">
         <v>1356</v>
       </c>
-      <c r="C19" s="110">
+      <c r="C19" s="109">
         <f t="shared" si="1"/>
         <v>-627</v>
       </c>
-      <c r="D19" s="110">
+      <c r="D19" s="109">
         <v>577</v>
       </c>
-      <c r="E19" s="110">
+      <c r="E19" s="109">
         <f t="shared" si="2"/>
         <v>779</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>3517</v>
       </c>
-      <c r="G19" s="109">
+      <c r="G19" s="108">
         <f t="shared" si="0"/>
         <v>0.57448377581120946</v>
       </c>
@@ -35771,23 +36130,23 @@
       <c r="A20" s="20">
         <v>42186</v>
       </c>
-      <c r="B20" s="110">
+      <c r="B20" s="109">
         <v>1874</v>
       </c>
-      <c r="C20" s="110">
+      <c r="C20" s="109">
         <f t="shared" si="1"/>
         <v>518</v>
       </c>
-      <c r="D20" s="110">
+      <c r="D20" s="109">
         <v>865</v>
       </c>
-      <c r="E20" s="110">
+      <c r="E20" s="109">
         <v>883</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="109">
+      <c r="G20" s="108">
         <f t="shared" si="0"/>
         <v>0.47118463180362863</v>
       </c>
@@ -35796,24 +36155,24 @@
       <c r="A21" s="20">
         <v>42217</v>
       </c>
-      <c r="B21" s="110">
+      <c r="B21" s="109">
         <v>1479</v>
       </c>
-      <c r="C21" s="110">
+      <c r="C21" s="109">
         <f t="shared" si="1"/>
         <v>-395</v>
       </c>
-      <c r="D21" s="110">
+      <c r="D21" s="109">
         <v>588</v>
       </c>
-      <c r="E21" s="110">
+      <c r="E21" s="109">
         <f>B21-D21</f>
         <v>891</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="109">
+      <c r="G21" s="108">
         <f t="shared" si="0"/>
         <v>0.60243407707910746</v>
       </c>
@@ -35822,23 +36181,23 @@
       <c r="A22" s="20">
         <v>42248</v>
       </c>
-      <c r="B22" s="110">
+      <c r="B22" s="109">
         <v>1943</v>
       </c>
-      <c r="C22" s="110">
+      <c r="C22" s="109">
         <f t="shared" si="1"/>
         <v>464</v>
       </c>
-      <c r="D22" s="110">
+      <c r="D22" s="109">
         <v>785</v>
       </c>
-      <c r="E22" s="110">
+      <c r="E22" s="109">
         <v>712</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G22" s="109">
+      <c r="G22" s="108">
         <f t="shared" si="0"/>
         <v>0.36644364384971695</v>
       </c>
@@ -35847,24 +36206,24 @@
       <c r="A23" s="20">
         <v>42278</v>
       </c>
-      <c r="B23" s="110">
+      <c r="B23" s="109">
         <v>1444</v>
       </c>
-      <c r="C23" s="110">
+      <c r="C23" s="109">
         <f t="shared" si="1"/>
         <v>-499</v>
       </c>
-      <c r="D23" s="110">
+      <c r="D23" s="109">
         <v>657</v>
       </c>
-      <c r="E23" s="110">
+      <c r="E23" s="109">
         <f>B23-D23</f>
         <v>787</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G23" s="109">
+      <c r="G23" s="108">
         <f t="shared" si="0"/>
         <v>0.54501385041551242</v>
       </c>
@@ -35873,24 +36232,24 @@
       <c r="A24" s="20">
         <v>42309</v>
       </c>
-      <c r="B24" s="110">
+      <c r="B24" s="109">
         <v>1493</v>
       </c>
-      <c r="C24" s="110">
+      <c r="C24" s="109">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="D24" s="110">
+      <c r="D24" s="109">
         <v>880</v>
       </c>
-      <c r="E24" s="110">
+      <c r="E24" s="109">
         <f>B24-D24</f>
         <v>613</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>3517</v>
       </c>
-      <c r="G24" s="109">
+      <c r="G24" s="108">
         <f t="shared" si="0"/>
         <v>0.4105827193569993</v>
       </c>
@@ -35899,24 +36258,24 @@
       <c r="A25" s="20">
         <v>42339</v>
       </c>
-      <c r="B25" s="110">
+      <c r="B25" s="109">
         <v>1738</v>
       </c>
-      <c r="C25" s="110">
+      <c r="C25" s="109">
         <f t="shared" si="1"/>
         <v>245</v>
       </c>
-      <c r="D25" s="110">
+      <c r="D25" s="109">
         <v>580</v>
       </c>
-      <c r="E25" s="110">
+      <c r="E25" s="109">
         <f>B25-D25</f>
         <v>1158</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G25" s="109">
+      <c r="G25" s="108">
         <f t="shared" si="0"/>
         <v>0.66628308400460301</v>
       </c>
@@ -35991,78 +36350,78 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="106" t="s">
         <v>3546</v>
       </c>
-      <c r="C2" s="108">
+      <c r="C2" s="107">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="106" t="s">
         <v>3545</v>
       </c>
-      <c r="C3" s="111">
+      <c r="C3" s="110">
         <f>TIME(10,38,45)</f>
         <v>0.4435763888888889</v>
       </c>
-      <c r="E3" s="107" t="s">
+      <c r="E3" s="106" t="s">
         <v>3544</v>
       </c>
-      <c r="F3" s="108">
+      <c r="F3" s="107">
         <f>DATE(2027,9,26)</f>
         <v>46656</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="107"/>
+      <c r="B4" s="106"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="9" t="s">
         <v>3543</v>
       </c>
-      <c r="C5" s="112">
+      <c r="C5" s="111">
         <f ca="1">YEAR(C2)</f>
         <v>2026</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>3542</v>
       </c>
-      <c r="F5" s="112">
+      <c r="F5" s="111">
         <f ca="1">F3-C2</f>
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="9" t="s">
         <v>3541</v>
       </c>
-      <c r="C6" s="105">
+      <c r="C6" s="104">
         <f ca="1">MONTH(TODAY())</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>3540</v>
       </c>
-      <c r="F6" s="105">
+      <c r="F6" s="104">
         <f ca="1">NETWORKDAYS(C2,F3)</f>
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="9" t="s">
         <v>3539</v>
       </c>
-      <c r="C7" s="105">
+      <c r="C7" s="104">
         <f ca="1">DAY(TODAY())</f>
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>3538</v>
       </c>
-      <c r="F7" s="106" t="str">
+      <c r="F7" s="105" t="str">
         <f>TEXT(F3,"dddd")</f>
         <v>Sunday</v>
       </c>
@@ -36072,7 +36431,7 @@
       <c r="B8" s="9" t="s">
         <v>3537</v>
       </c>
-      <c r="C8" s="105">
+      <c r="C8" s="104">
         <f>HOUR(C3)</f>
         <v>10</v>
       </c>
@@ -36081,14 +36440,14 @@
       <c r="B9" s="9" t="s">
         <v>3536</v>
       </c>
-      <c r="C9" s="105">
+      <c r="C9" s="104">
         <f>MINUTE(C3)</f>
         <v>38</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>3535</v>
       </c>
-      <c r="F9" s="105">
+      <c r="F9" s="104">
         <f ca="1">DATEDIF(C2,F3,"m")</f>
         <v>11</v>
       </c>
@@ -36097,36 +36456,36 @@
       <c r="B10" s="9" t="s">
         <v>3534</v>
       </c>
-      <c r="C10" s="104">
+      <c r="C10" s="103">
         <f>SECOND(C3)</f>
         <v>45</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>3533</v>
       </c>
-      <c r="F10" s="104">
+      <c r="F10" s="103">
         <f ca="1">DATEDIF(C2,F3,"y")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="103"/>
+      <c r="B11" s="102"/>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="9" t="s">
         <v>3532</v>
       </c>
-      <c r="C12" s="102">
+      <c r="C12" s="101">
         <f>DATE(2026,9,30)</f>
         <v>46295</v>
       </c>
-      <c r="G12" s="101"/>
+      <c r="G12" s="100"/>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="9" t="s">
         <v>3531</v>
       </c>
-      <c r="C13" s="100">
+      <c r="C13" s="99">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
@@ -36135,7 +36494,7 @@
       <c r="B14" s="9" t="s">
         <v>3530</v>
       </c>
-      <c r="C14" s="100">
+      <c r="C14" s="99">
         <f>DATE(2026,1,1)</f>
         <v>46023</v>
       </c>
@@ -36150,9 +36509,9 @@
       <c r="B16" s="9" t="s">
         <v>3529</v>
       </c>
-      <c r="C16" s="113">
+      <c r="C16" s="112">
         <f ca="1">DATEDIF(E15,TODAY(),"YD")/365*100</f>
-        <v>74.520547945205479</v>
+        <v>75.06849315068493</v>
       </c>
     </row>
   </sheetData>
@@ -36172,79 +36531,109 @@
   <cols>
     <col min="1" max="1" width="23.44140625" style="49" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.5546875" style="49" customWidth="1"/>
-    <col min="3" max="3" width="18.77734375" style="49" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="49" customWidth="1"/>
     <col min="4" max="16384" width="9.21875" style="49"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="59" t="s">
         <v>3334</v>
       </c>
-      <c r="C1" s="59">
+      <c r="C1" s="58">
         <v>46223</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="57" t="s">
         <v>3333</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="57" t="s">
         <v>3332</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="56" t="s">
         <v>3331</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="55" t="s">
         <v>3330</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="55" t="s">
         <v>3329</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="54" t="s">
         <v>3527</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="53"/>
+      <c r="B5" s="53">
+        <f>DATE(26,7,10)</f>
+        <v>9688</v>
+      </c>
+      <c r="C5" s="129">
+        <f>DATEDIF(B5,$C$1,"YD")</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="54" t="s">
         <v>3523</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="53"/>
+      <c r="B6" s="53">
+        <f>DATE(26,7,5)</f>
+        <v>9683</v>
+      </c>
+      <c r="C6" s="129">
+        <f t="shared" ref="C6:C9" si="0">DATEDIF(B6,$C$1,"YD")</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="54" t="s">
         <v>3524</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="53">
+        <f>DATE(26,6,8)</f>
+        <v>9656</v>
+      </c>
+      <c r="C7" s="129">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="54" t="s">
         <v>3525</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="53"/>
+      <c r="B8" s="53">
+        <f>DATE(26,6,5)</f>
+        <v>9653</v>
+      </c>
+      <c r="C8" s="129">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="54" t="s">
         <v>3526</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="53">
+        <f>DATE(26,7,17)</f>
+        <v>9695</v>
+      </c>
+      <c r="C9" s="129">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A12" s="128" t="s">
+      <c r="A12" s="127" t="s">
         <v>3328</v>
       </c>
-      <c r="B12" s="128"/>
-      <c r="C12" s="128"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="52" t="s">
@@ -36261,8 +36650,14 @@
       <c r="A14" s="51">
         <v>32878</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
+      <c r="B14" s="50">
+        <f>DATEDIF(A14,C1,"D")</f>
+        <v>13345</v>
+      </c>
+      <c r="C14" s="50">
+        <f>DATEDIF(A14,C1,"Y")+1</f>
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -36287,121 +36682,121 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="93" customWidth="1"/>
-    <col min="2" max="16384" width="8.77734375" style="93"/>
+    <col min="1" max="1" width="11.21875" style="92" customWidth="1"/>
+    <col min="2" max="16384" width="8.77734375" style="92"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="128" t="s">
         <v>3513</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="96" t="s">
         <v>3512</v>
       </c>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="95" t="s">
         <v>3511</v>
       </c>
-      <c r="C3" s="96" t="s">
+      <c r="C3" s="95" t="s">
         <v>3510</v>
       </c>
-      <c r="D3" s="96" t="s">
+      <c r="D3" s="95" t="s">
         <v>3509</v>
       </c>
-      <c r="E3" s="96" t="s">
+      <c r="E3" s="95" t="s">
         <v>3508</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="92" t="s">
         <v>3487</v>
       </c>
-      <c r="B4" s="93">
+      <c r="B4" s="92">
         <v>200</v>
       </c>
-      <c r="C4" s="93">
+      <c r="C4" s="92">
         <v>800</v>
       </c>
-      <c r="D4" s="93">
+      <c r="D4" s="92">
         <v>900</v>
       </c>
-      <c r="E4" s="93">
+      <c r="E4" s="92">
         <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="92" t="s">
         <v>3507</v>
       </c>
-      <c r="B5" s="93">
+      <c r="B5" s="92">
         <v>400</v>
       </c>
-      <c r="C5" s="93">
+      <c r="C5" s="92">
         <v>100</v>
       </c>
-      <c r="D5" s="93">
+      <c r="D5" s="92">
         <v>800</v>
       </c>
-      <c r="E5" s="93">
+      <c r="E5" s="92">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="92" t="s">
         <v>3489</v>
       </c>
-      <c r="B6" s="93">
+      <c r="B6" s="92">
         <v>200</v>
       </c>
-      <c r="C6" s="93">
+      <c r="C6" s="92">
         <v>500</v>
       </c>
-      <c r="D6" s="93">
+      <c r="D6" s="92">
         <v>500</v>
       </c>
-      <c r="E6" s="93">
+      <c r="E6" s="92">
         <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="93" t="s">
+      <c r="A7" s="92" t="s">
         <v>3506</v>
       </c>
-      <c r="B7" s="93">
+      <c r="B7" s="92">
         <v>200</v>
       </c>
-      <c r="C7" s="93">
+      <c r="C7" s="92">
         <v>300</v>
       </c>
-      <c r="D7" s="93">
+      <c r="D7" s="92">
         <v>500</v>
       </c>
-      <c r="E7" s="93">
+      <c r="E7" s="92">
         <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="94" t="s">
         <v>3505</v>
       </c>
-      <c r="B9" s="94">
+      <c r="B9" s="93">
         <f>SUM(B4:B7)</f>
         <v>1000</v>
       </c>
-      <c r="C9" s="94">
+      <c r="C9" s="93">
         <f>SUM(C4:C7)</f>
         <v>1700</v>
       </c>
-      <c r="D9" s="94">
+      <c r="D9" s="93">
         <f>SUM(D4:D7)</f>
         <v>2700</v>
       </c>
-      <c r="E9" s="94">
+      <c r="E9" s="93">
         <f>SUM(E4:E7)</f>
         <v>1100</v>
       </c>
@@ -36831,126 +37226,132 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="93" customWidth="1"/>
-    <col min="2" max="16384" width="8.77734375" style="93"/>
+    <col min="1" max="1" width="11.21875" style="92" customWidth="1"/>
+    <col min="2" max="16384" width="8.77734375" style="92"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="128" t="s">
         <v>3515</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="96" t="s">
         <v>3512</v>
       </c>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="95" t="s">
         <v>3511</v>
       </c>
-      <c r="C3" s="96" t="s">
+      <c r="C3" s="95" t="s">
         <v>3510</v>
       </c>
-      <c r="D3" s="96" t="s">
+      <c r="D3" s="95" t="s">
         <v>3509</v>
       </c>
-      <c r="E3" s="96" t="s">
+      <c r="E3" s="95" t="s">
         <v>3508</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="92" t="s">
         <v>3487</v>
       </c>
-      <c r="B4" s="93">
+      <c r="B4" s="92">
         <v>400</v>
       </c>
-      <c r="C4" s="93">
+      <c r="C4" s="92">
         <v>800</v>
       </c>
-      <c r="D4" s="93">
+      <c r="D4" s="92">
         <v>900</v>
       </c>
-      <c r="E4" s="93">
+      <c r="E4" s="92">
         <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="92" t="s">
         <v>3507</v>
       </c>
-      <c r="B5" s="93">
+      <c r="B5" s="92">
         <v>200</v>
       </c>
-      <c r="C5" s="93">
+      <c r="C5" s="92">
         <v>500</v>
       </c>
-      <c r="D5" s="93">
+      <c r="D5" s="92">
         <v>1200</v>
       </c>
-      <c r="E5" s="93">
+      <c r="E5" s="92">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="92" t="s">
         <v>3489</v>
       </c>
-      <c r="B6" s="93">
+      <c r="B6" s="92">
         <v>300</v>
       </c>
-      <c r="C6" s="93">
+      <c r="C6" s="92">
         <v>400</v>
       </c>
-      <c r="D6" s="93">
+      <c r="D6" s="92">
         <v>1400</v>
       </c>
-      <c r="E6" s="93">
+      <c r="E6" s="92">
         <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="93" t="s">
+      <c r="A7" s="92" t="s">
         <v>3506</v>
       </c>
-      <c r="B7" s="93">
+      <c r="B7" s="92">
         <v>100</v>
       </c>
-      <c r="C7" s="93">
+      <c r="C7" s="92">
         <v>300</v>
       </c>
-      <c r="D7" s="93">
+      <c r="D7" s="92">
         <v>500</v>
       </c>
-      <c r="E7" s="93">
+      <c r="E7" s="92">
         <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="94" t="s">
         <v>3505</v>
       </c>
-      <c r="B9" s="94">
+      <c r="B9" s="93">
         <f>SUM(B4:B7)</f>
         <v>1000</v>
       </c>
-      <c r="C9" s="94">
+      <c r="C9" s="93">
         <f>SUM(C4:C7)</f>
         <v>2000</v>
       </c>
-      <c r="D9" s="94">
+      <c r="D9" s="93">
         <f>SUM(D4:D7)</f>
         <v>4000</v>
       </c>
-      <c r="E9" s="94">
+      <c r="E9" s="93">
         <f>SUM(E4:E7)</f>
         <v>1000</v>
       </c>
     </row>
   </sheetData>
+  <dataConsolidate>
+    <dataRefs count="2">
+      <dataRef ref="A1:E9" sheet="Maine"/>
+      <dataRef ref="A1:E9" sheet="New Hampshire"/>
+    </dataRefs>
+  </dataConsolidate>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -36970,121 +37371,121 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="93" customWidth="1"/>
-    <col min="2" max="16384" width="8.77734375" style="93"/>
+    <col min="1" max="1" width="11.21875" style="92" customWidth="1"/>
+    <col min="2" max="16384" width="8.77734375" style="92"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="128" t="s">
         <v>3514</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="96" t="s">
         <v>3512</v>
       </c>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="95" t="s">
         <v>3511</v>
       </c>
-      <c r="C3" s="96" t="s">
+      <c r="C3" s="95" t="s">
         <v>3510</v>
       </c>
-      <c r="D3" s="96" t="s">
+      <c r="D3" s="95" t="s">
         <v>3509</v>
       </c>
-      <c r="E3" s="96" t="s">
+      <c r="E3" s="95" t="s">
         <v>3508</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="92" t="s">
         <v>3487</v>
       </c>
-      <c r="B4" s="93">
+      <c r="B4" s="92">
         <v>200</v>
       </c>
-      <c r="C4" s="93">
+      <c r="C4" s="92">
         <v>600</v>
       </c>
-      <c r="D4" s="93">
+      <c r="D4" s="92">
         <v>700</v>
       </c>
-      <c r="E4" s="93">
+      <c r="E4" s="92">
         <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="92" t="s">
         <v>3507</v>
       </c>
-      <c r="B5" s="93">
+      <c r="B5" s="92">
         <v>300</v>
       </c>
-      <c r="C5" s="93">
+      <c r="C5" s="92">
         <v>200</v>
       </c>
-      <c r="D5" s="93">
+      <c r="D5" s="92">
         <v>500</v>
       </c>
-      <c r="E5" s="93">
+      <c r="E5" s="92">
         <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="92" t="s">
         <v>3489</v>
       </c>
-      <c r="B6" s="93">
+      <c r="B6" s="92">
         <v>200</v>
       </c>
-      <c r="C6" s="93">
+      <c r="C6" s="92">
         <v>400</v>
       </c>
-      <c r="D6" s="93">
+      <c r="D6" s="92">
         <v>500</v>
       </c>
-      <c r="E6" s="93">
+      <c r="E6" s="92">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="93" t="s">
+      <c r="A7" s="92" t="s">
         <v>3506</v>
       </c>
-      <c r="B7" s="93">
+      <c r="B7" s="92">
         <v>300</v>
       </c>
-      <c r="C7" s="93">
+      <c r="C7" s="92">
         <v>300</v>
       </c>
-      <c r="D7" s="93">
+      <c r="D7" s="92">
         <v>100</v>
       </c>
-      <c r="E7" s="93">
+      <c r="E7" s="92">
         <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="94" t="s">
         <v>3505</v>
       </c>
-      <c r="B9" s="94">
+      <c r="B9" s="93">
         <f>SUM(B4:B7)</f>
         <v>1000</v>
       </c>
-      <c r="C9" s="94">
+      <c r="C9" s="93">
         <f>SUM(C4:C7)</f>
         <v>1500</v>
       </c>
-      <c r="D9" s="94">
+      <c r="D9" s="93">
         <f>SUM(D4:D7)</f>
         <v>1800</v>
       </c>
-      <c r="E9" s="94">
+      <c r="E9" s="93">
         <f>SUM(E4:E7)</f>
         <v>1300</v>
       </c>
@@ -37109,37 +37510,112 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="93" customWidth="1"/>
-    <col min="2" max="16384" width="8.77734375" style="93"/>
+    <col min="1" max="1" width="11.21875" style="92" customWidth="1"/>
+    <col min="2" max="16384" width="8.77734375" style="92"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="129"/>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
+      <c r="A1" s="128"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="97"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
+      <c r="A3" s="96"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95" t="s">
+        <v>3510</v>
+      </c>
+      <c r="D3" s="95" t="s">
+        <v>3509</v>
+      </c>
+      <c r="E3" s="95" t="s">
+        <v>3508</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="92">
+        <v>400</v>
+      </c>
+      <c r="C4" s="92">
+        <v>800</v>
+      </c>
+      <c r="D4" s="92">
+        <v>900</v>
+      </c>
+      <c r="E4" s="92">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="92">
+        <v>200</v>
+      </c>
+      <c r="C5" s="92">
+        <v>1500</v>
+      </c>
+      <c r="D5" s="92">
+        <v>2400</v>
+      </c>
+      <c r="E5" s="92">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="92">
+        <v>300</v>
+      </c>
+      <c r="C6" s="92">
+        <v>900</v>
+      </c>
+      <c r="D6" s="92">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="92">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="92">
+        <v>100</v>
+      </c>
+      <c r="C7" s="92">
+        <v>300</v>
+      </c>
+      <c r="D7" s="92">
+        <v>500</v>
+      </c>
+      <c r="E7" s="92">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="92">
+        <v>1000</v>
+      </c>
+      <c r="C8" s="130">
+        <v>3500</v>
+      </c>
+      <c r="D8" s="130">
+        <v>5800</v>
+      </c>
+      <c r="E8" s="130">
+        <v>2300</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="95"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
+      <c r="A9" s="94"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
     </row>
   </sheetData>
-  <dataConsolidate topLabels="1">
-    <dataRefs count="3">
-      <dataRef ref="A3:E9" sheet="Connecticut"/>
-      <dataRef ref="A3:E9" sheet="Maine"/>
-      <dataRef ref="A3:E9" sheet="New Hampshire"/>
+  <dataConsolidate leftLabels="1" topLabels="1">
+    <dataRefs count="2">
+      <dataRef ref="B3:E9" sheet="Maine"/>
+      <dataRef ref="B3:E9" sheet="New Hampshire"/>
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="1">
@@ -37159,7 +37635,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5546875" style="2" customWidth="1"/>
@@ -37207,7 +37683,10 @@
       <c r="G2" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="H2" s="48"/>
+      <c r="H2" s="48">
+        <f>MAX(E6:E11)</f>
+        <v>25897</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -37245,7 +37724,10 @@
       <c r="G4" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="H4" s="48"/>
+      <c r="H4" s="48">
+        <f>_xlfn.MAXIFS(E2:E16,B2:B16,"NYC",C2:C16,"Electronics")</f>
+        <v>15414</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -37324,7 +37806,10 @@
       <c r="G8" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="H8" s="48"/>
+      <c r="H8" s="48">
+        <f>SUMIF(B2:B16,"BOS",_2015_Sales)+SUMIF(B2:B16,"BOS",_2016_Sales)</f>
+        <v>140337</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -37460,6 +37945,12 @@
       </c>
       <c r="E16" s="8">
         <v>17631</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C19" s="8">
+        <f>SUM(D2:E5)</f>
+        <v>140337</v>
       </c>
     </row>
   </sheetData>
@@ -37479,8 +37970,8 @@
   <cols>
     <col min="1" max="1" width="1.21875" style="49" customWidth="1"/>
     <col min="2" max="2" width="9.44140625" style="49" customWidth="1"/>
-    <col min="3" max="3" width="18.77734375" style="68" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="68" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" style="67" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="67" customWidth="1"/>
     <col min="5" max="6" width="14.44140625" style="49" customWidth="1"/>
     <col min="7" max="7" width="16.21875" style="49" customWidth="1"/>
     <col min="8" max="8" width="3.44140625" style="49" customWidth="1"/>
@@ -37493,1135 +37984,1135 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="113" t="s">
         <v>3504</v>
       </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="116"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="115"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="91" t="s">
         <v>3500</v>
       </c>
-      <c r="C4" s="92" t="s">
+      <c r="C4" s="91" t="s">
         <v>3496</v>
       </c>
-      <c r="D4" s="92" t="s">
+      <c r="D4" s="91" t="s">
         <v>3503</v>
       </c>
-      <c r="E4" s="92" t="s">
+      <c r="E4" s="91" t="s">
         <v>3502</v>
       </c>
-      <c r="F4" s="92" t="s">
+      <c r="F4" s="91" t="s">
         <v>3501</v>
       </c>
-      <c r="G4" s="91" t="s">
+      <c r="G4" s="90" t="s">
         <v>3499</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="60"/>
-      <c r="B5" s="87" t="s">
+      <c r="A5" s="59"/>
+      <c r="B5" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C5" s="83" t="s">
+      <c r="C5" s="82" t="s">
         <v>3491</v>
       </c>
-      <c r="D5" s="82">
+      <c r="D5" s="81">
         <v>800</v>
       </c>
-      <c r="E5" s="82">
+      <c r="E5" s="81">
         <v>650</v>
       </c>
-      <c r="F5" s="82">
+      <c r="F5" s="81">
         <v>700</v>
       </c>
-      <c r="G5" s="81"/>
+      <c r="G5" s="80"/>
     </row>
     <row r="6" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="60"/>
-      <c r="B6" s="87" t="s">
+      <c r="A6" s="59"/>
+      <c r="B6" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C6" s="83" t="s">
+      <c r="C6" s="82" t="s">
         <v>3312</v>
       </c>
-      <c r="D6" s="82">
+      <c r="D6" s="81">
         <v>900</v>
       </c>
-      <c r="E6" s="82">
+      <c r="E6" s="81">
         <v>850</v>
       </c>
-      <c r="F6" s="82">
+      <c r="F6" s="81">
         <v>850</v>
       </c>
-      <c r="G6" s="81"/>
-      <c r="J6" s="90"/>
-      <c r="K6" s="90"/>
-      <c r="L6" s="88"/>
+      <c r="G6" s="80"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="87"/>
     </row>
     <row r="7" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="60"/>
-      <c r="B7" s="87" t="s">
+      <c r="A7" s="59"/>
+      <c r="B7" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C7" s="83" t="s">
+      <c r="C7" s="82" t="s">
         <v>3485</v>
       </c>
-      <c r="D7" s="82">
+      <c r="D7" s="81">
         <v>4850</v>
       </c>
-      <c r="E7" s="82">
+      <c r="E7" s="81">
         <v>3200</v>
       </c>
-      <c r="F7" s="82">
+      <c r="F7" s="81">
         <v>1155</v>
       </c>
-      <c r="G7" s="81"/>
-      <c r="I7" s="86" t="s">
+      <c r="G7" s="80"/>
+      <c r="I7" s="85" t="s">
         <v>3500</v>
       </c>
-      <c r="J7" s="86" t="s">
+      <c r="J7" s="85" t="s">
         <v>3496</v>
       </c>
-      <c r="K7" s="86" t="s">
+      <c r="K7" s="85" t="s">
         <v>3499</v>
       </c>
-      <c r="L7" s="88"/>
+      <c r="L7" s="87"/>
     </row>
     <row r="8" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="60"/>
-      <c r="B8" s="87" t="s">
+      <c r="A8" s="59"/>
+      <c r="B8" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="82" t="s">
         <v>3492</v>
       </c>
-      <c r="D8" s="82">
+      <c r="D8" s="81">
         <v>1250</v>
       </c>
-      <c r="E8" s="82">
+      <c r="E8" s="81">
         <v>1250</v>
       </c>
-      <c r="F8" s="82">
+      <c r="F8" s="81">
         <v>1250</v>
       </c>
-      <c r="G8" s="81"/>
-      <c r="I8" s="85" t="s">
+      <c r="G8" s="80"/>
+      <c r="I8" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="J8" s="85" t="s">
+      <c r="J8" s="84" t="s">
         <v>3487</v>
       </c>
-      <c r="K8" s="89"/>
-      <c r="L8" s="88"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="87"/>
     </row>
     <row r="9" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="60"/>
-      <c r="B9" s="87" t="s">
+      <c r="A9" s="59"/>
+      <c r="B9" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C9" s="83" t="s">
+      <c r="C9" s="82" t="s">
         <v>3487</v>
       </c>
-      <c r="D9" s="82">
+      <c r="D9" s="81">
         <v>2025</v>
       </c>
-      <c r="E9" s="82">
+      <c r="E9" s="81">
         <v>2200</v>
       </c>
-      <c r="F9" s="82">
+      <c r="F9" s="81">
         <v>1650</v>
       </c>
-      <c r="G9" s="81"/>
-      <c r="L9" s="88"/>
+      <c r="G9" s="80"/>
+      <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="60"/>
-      <c r="B10" s="87" t="s">
+      <c r="A10" s="59"/>
+      <c r="B10" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C10" s="83" t="s">
+      <c r="C10" s="82" t="s">
         <v>3489</v>
       </c>
-      <c r="D10" s="82">
+      <c r="D10" s="81">
         <v>1350</v>
       </c>
-      <c r="E10" s="82">
+      <c r="E10" s="81">
         <v>1500</v>
       </c>
-      <c r="F10" s="82">
+      <c r="F10" s="81">
         <v>1700</v>
       </c>
-      <c r="G10" s="81"/>
+      <c r="G10" s="80"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="60"/>
-      <c r="B11" s="87" t="s">
+      <c r="A11" s="59"/>
+      <c r="B11" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C11" s="83" t="s">
+      <c r="C11" s="82" t="s">
         <v>3490</v>
       </c>
-      <c r="D11" s="82">
+      <c r="D11" s="81">
         <v>3300</v>
       </c>
-      <c r="E11" s="82">
+      <c r="E11" s="81">
         <v>3500</v>
       </c>
-      <c r="F11" s="82">
+      <c r="F11" s="81">
         <v>3700</v>
       </c>
-      <c r="G11" s="81"/>
+      <c r="G11" s="80"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="60"/>
-      <c r="B12" s="87" t="s">
+      <c r="A12" s="59"/>
+      <c r="B12" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C12" s="83" t="s">
+      <c r="C12" s="82" t="s">
         <v>3486</v>
       </c>
-      <c r="D12" s="82">
+      <c r="D12" s="81">
         <v>3825</v>
       </c>
-      <c r="E12" s="82">
+      <c r="E12" s="81">
         <v>3725</v>
       </c>
-      <c r="F12" s="82">
+      <c r="F12" s="81">
         <v>3750</v>
       </c>
-      <c r="G12" s="81"/>
+      <c r="G12" s="80"/>
     </row>
     <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="60"/>
-      <c r="B13" s="87" t="s">
+      <c r="A13" s="59"/>
+      <c r="B13" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C13" s="83" t="s">
+      <c r="C13" s="82" t="s">
         <v>3488</v>
       </c>
-      <c r="D13" s="82">
+      <c r="D13" s="81">
         <v>8900</v>
       </c>
-      <c r="E13" s="82">
+      <c r="E13" s="81">
         <v>10315</v>
       </c>
-      <c r="F13" s="82">
+      <c r="F13" s="81">
         <v>5250</v>
       </c>
-      <c r="G13" s="81"/>
-      <c r="I13" s="86" t="s">
+      <c r="G13" s="80"/>
+      <c r="I13" s="85" t="s">
         <v>3496</v>
       </c>
-      <c r="J13" s="86" t="s">
+      <c r="J13" s="85" t="s">
         <v>3498</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="60"/>
-      <c r="B14" s="87" t="s">
+      <c r="A14" s="59"/>
+      <c r="B14" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="82" t="s">
         <v>3483</v>
       </c>
-      <c r="D14" s="82">
+      <c r="D14" s="81">
         <v>6250</v>
       </c>
-      <c r="E14" s="82">
+      <c r="E14" s="81">
         <v>6000</v>
       </c>
-      <c r="F14" s="82">
+      <c r="F14" s="81">
         <v>6500</v>
       </c>
-      <c r="G14" s="81"/>
-      <c r="I14" s="85" t="s">
+      <c r="G14" s="80"/>
+      <c r="I14" s="84" t="s">
         <v>3487</v>
       </c>
-      <c r="J14" s="84"/>
+      <c r="J14" s="83"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="60"/>
-      <c r="B15" s="87" t="s">
+      <c r="A15" s="59"/>
+      <c r="B15" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C15" s="83" t="s">
+      <c r="C15" s="82" t="s">
         <v>3484</v>
       </c>
-      <c r="D15" s="82">
+      <c r="D15" s="81">
         <v>8000</v>
       </c>
-      <c r="E15" s="82">
+      <c r="E15" s="81">
         <v>8000</v>
       </c>
-      <c r="F15" s="82">
+      <c r="F15" s="81">
         <v>8000</v>
       </c>
-      <c r="G15" s="81"/>
+      <c r="G15" s="80"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="60"/>
-      <c r="B16" s="87" t="s">
+      <c r="A16" s="59"/>
+      <c r="B16" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C16" s="83" t="s">
+      <c r="C16" s="82" t="s">
         <v>3481</v>
       </c>
-      <c r="D16" s="82">
+      <c r="D16" s="81">
         <v>11500</v>
       </c>
-      <c r="E16" s="82">
+      <c r="E16" s="81">
         <v>12500</v>
       </c>
-      <c r="F16" s="82">
+      <c r="F16" s="81">
         <v>12500</v>
       </c>
-      <c r="G16" s="81"/>
+      <c r="G16" s="80"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="60"/>
-      <c r="B17" s="87" t="s">
+      <c r="A17" s="59"/>
+      <c r="B17" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="82" t="s">
         <v>3482</v>
       </c>
-      <c r="D17" s="82">
+      <c r="D17" s="81">
         <v>12250</v>
       </c>
-      <c r="E17" s="82">
+      <c r="E17" s="81">
         <v>12250</v>
       </c>
-      <c r="F17" s="82">
+      <c r="F17" s="81">
         <v>12750</v>
       </c>
-      <c r="G17" s="81"/>
+      <c r="G17" s="80"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="60"/>
-      <c r="B18" s="87" t="s">
+      <c r="A18" s="59"/>
+      <c r="B18" s="86" t="s">
         <v>3497</v>
       </c>
-      <c r="C18" s="83" t="s">
+      <c r="C18" s="82" t="s">
         <v>3478</v>
       </c>
-      <c r="D18" s="82">
+      <c r="D18" s="81">
         <v>25000</v>
       </c>
-      <c r="E18" s="82">
+      <c r="E18" s="81">
         <v>24000</v>
       </c>
-      <c r="F18" s="82">
+      <c r="F18" s="81">
         <v>26390</v>
       </c>
-      <c r="G18" s="81"/>
+      <c r="G18" s="80"/>
     </row>
     <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="60"/>
-      <c r="B19" s="83" t="s">
+      <c r="A19" s="59"/>
+      <c r="B19" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="82" t="s">
         <v>3491</v>
       </c>
-      <c r="D19" s="82">
+      <c r="D19" s="81">
         <v>800</v>
       </c>
-      <c r="E19" s="82">
+      <c r="E19" s="81">
         <v>950</v>
       </c>
-      <c r="F19" s="82">
+      <c r="F19" s="81">
         <v>750</v>
       </c>
-      <c r="G19" s="81"/>
-      <c r="I19" s="86" t="s">
+      <c r="G19" s="80"/>
+      <c r="I19" s="85" t="s">
         <v>3496</v>
       </c>
-      <c r="J19" s="86" t="s">
+      <c r="J19" s="85" t="s">
         <v>3495</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="83" t="s">
+      <c r="B20" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C20" s="83" t="s">
+      <c r="C20" s="82" t="s">
         <v>3492</v>
       </c>
-      <c r="D20" s="82">
+      <c r="D20" s="81">
         <v>850</v>
       </c>
-      <c r="E20" s="82">
+      <c r="E20" s="81">
         <v>750</v>
       </c>
-      <c r="F20" s="82">
+      <c r="F20" s="81">
         <v>800</v>
       </c>
-      <c r="G20" s="81"/>
-      <c r="I20" s="85" t="s">
+      <c r="G20" s="80"/>
+      <c r="I20" s="84" t="s">
         <v>3484</v>
       </c>
-      <c r="J20" s="84"/>
+      <c r="J20" s="83"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="83" t="s">
+      <c r="B21" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C21" s="83" t="s">
+      <c r="C21" s="82" t="s">
         <v>3489</v>
       </c>
-      <c r="D21" s="82">
+      <c r="D21" s="81">
         <v>940</v>
       </c>
-      <c r="E21" s="82">
+      <c r="E21" s="81">
         <v>950</v>
       </c>
-      <c r="F21" s="82">
+      <c r="F21" s="81">
         <v>820</v>
       </c>
-      <c r="G21" s="81"/>
+      <c r="G21" s="80"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C22" s="83" t="s">
+      <c r="C22" s="82" t="s">
         <v>3312</v>
       </c>
-      <c r="D22" s="82">
+      <c r="D22" s="81">
         <v>980</v>
       </c>
-      <c r="E22" s="82">
+      <c r="E22" s="81">
         <v>850</v>
       </c>
-      <c r="F22" s="82">
+      <c r="F22" s="81">
         <v>950</v>
       </c>
-      <c r="G22" s="81"/>
+      <c r="G22" s="80"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C23" s="83" t="s">
+      <c r="C23" s="82" t="s">
         <v>3488</v>
       </c>
-      <c r="D23" s="82">
+      <c r="D23" s="81">
         <v>1250</v>
       </c>
-      <c r="E23" s="82">
+      <c r="E23" s="81">
         <v>1250</v>
       </c>
-      <c r="F23" s="82">
+      <c r="F23" s="81">
         <v>1250</v>
       </c>
-      <c r="G23" s="81"/>
+      <c r="G23" s="80"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="83" t="s">
+      <c r="B24" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C24" s="83" t="s">
+      <c r="C24" s="82" t="s">
         <v>3487</v>
       </c>
-      <c r="D24" s="82">
+      <c r="D24" s="81">
         <v>1150</v>
       </c>
-      <c r="E24" s="82">
+      <c r="E24" s="81">
         <v>1255</v>
       </c>
-      <c r="F24" s="82">
+      <c r="F24" s="81">
         <v>1400</v>
       </c>
-      <c r="G24" s="81"/>
+      <c r="G24" s="80"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C25" s="83" t="s">
+      <c r="C25" s="82" t="s">
         <v>3490</v>
       </c>
-      <c r="D25" s="82">
+      <c r="D25" s="81">
         <v>2410</v>
       </c>
-      <c r="E25" s="82">
+      <c r="E25" s="81">
         <v>1850</v>
       </c>
-      <c r="F25" s="82">
+      <c r="F25" s="81">
         <v>2390</v>
       </c>
-      <c r="G25" s="81"/>
+      <c r="G25" s="80"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C26" s="83" t="s">
+      <c r="C26" s="82" t="s">
         <v>3486</v>
       </c>
-      <c r="D26" s="82">
+      <c r="D26" s="81">
         <v>3200</v>
       </c>
-      <c r="E26" s="82">
+      <c r="E26" s="81">
         <v>3760</v>
       </c>
-      <c r="F26" s="82">
+      <c r="F26" s="81">
         <v>3750</v>
       </c>
-      <c r="G26" s="81"/>
+      <c r="G26" s="80"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="83" t="s">
+      <c r="B27" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C27" s="83" t="s">
+      <c r="C27" s="82" t="s">
         <v>3485</v>
       </c>
-      <c r="D27" s="82">
+      <c r="D27" s="81">
         <v>5000</v>
       </c>
-      <c r="E27" s="82">
+      <c r="E27" s="81">
         <v>4800</v>
       </c>
-      <c r="F27" s="82">
+      <c r="F27" s="81">
         <v>4500</v>
       </c>
-      <c r="G27" s="81"/>
+      <c r="G27" s="80"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="83" t="s">
+      <c r="B28" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C28" s="83" t="s">
+      <c r="C28" s="82" t="s">
         <v>3483</v>
       </c>
-      <c r="D28" s="82">
+      <c r="D28" s="81">
         <v>5250</v>
       </c>
-      <c r="E28" s="82">
+      <c r="E28" s="81">
         <v>8990</v>
       </c>
-      <c r="F28" s="82">
+      <c r="F28" s="81">
         <v>5515</v>
       </c>
-      <c r="G28" s="81"/>
+      <c r="G28" s="80"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="83" t="s">
+      <c r="B29" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C29" s="83" t="s">
+      <c r="C29" s="82" t="s">
         <v>3484</v>
       </c>
-      <c r="D29" s="82">
+      <c r="D29" s="81">
         <v>6020</v>
       </c>
-      <c r="E29" s="82">
+      <c r="E29" s="81">
         <v>6020</v>
       </c>
-      <c r="F29" s="82">
+      <c r="F29" s="81">
         <v>6020</v>
       </c>
-      <c r="G29" s="81"/>
+      <c r="G29" s="80"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="83" t="s">
+      <c r="B30" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C30" s="83" t="s">
+      <c r="C30" s="82" t="s">
         <v>3481</v>
       </c>
-      <c r="D30" s="82">
+      <c r="D30" s="81">
         <v>12940</v>
       </c>
-      <c r="E30" s="82">
+      <c r="E30" s="81">
         <v>11300</v>
       </c>
-      <c r="F30" s="82">
+      <c r="F30" s="81">
         <v>11500</v>
       </c>
-      <c r="G30" s="81"/>
+      <c r="G30" s="80"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B31" s="83" t="s">
+      <c r="B31" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C31" s="83" t="s">
+      <c r="C31" s="82" t="s">
         <v>3482</v>
       </c>
-      <c r="D31" s="82">
+      <c r="D31" s="81">
         <v>14250</v>
       </c>
-      <c r="E31" s="82">
+      <c r="E31" s="81">
         <v>15250</v>
       </c>
-      <c r="F31" s="82">
+      <c r="F31" s="81">
         <v>12050</v>
       </c>
-      <c r="G31" s="81"/>
+      <c r="G31" s="80"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B32" s="83" t="s">
+      <c r="B32" s="82" t="s">
         <v>3494</v>
       </c>
-      <c r="C32" s="83" t="s">
+      <c r="C32" s="82" t="s">
         <v>3478</v>
       </c>
-      <c r="D32" s="82">
+      <c r="D32" s="81">
         <v>25700</v>
       </c>
-      <c r="E32" s="82">
+      <c r="E32" s="81">
         <v>24200</v>
       </c>
-      <c r="F32" s="82">
+      <c r="F32" s="81">
         <v>26930</v>
       </c>
-      <c r="G32" s="81"/>
+      <c r="G32" s="80"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="83" t="s">
+      <c r="B33" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C33" s="83" t="s">
+      <c r="C33" s="82" t="s">
         <v>3492</v>
       </c>
-      <c r="D33" s="82">
+      <c r="D33" s="81">
         <v>2140</v>
       </c>
-      <c r="E33" s="82">
+      <c r="E33" s="81">
         <v>2310</v>
       </c>
-      <c r="F33" s="82">
+      <c r="F33" s="81">
         <v>2000</v>
       </c>
-      <c r="G33" s="81"/>
+      <c r="G33" s="80"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="83" t="s">
+      <c r="B34" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C34" s="83" t="s">
+      <c r="C34" s="82" t="s">
         <v>3491</v>
       </c>
-      <c r="D34" s="82">
+      <c r="D34" s="81">
         <v>730</v>
       </c>
-      <c r="E34" s="82">
+      <c r="E34" s="81">
         <v>525</v>
       </c>
-      <c r="F34" s="82">
+      <c r="F34" s="81">
         <v>430</v>
       </c>
-      <c r="G34" s="81"/>
+      <c r="G34" s="80"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="83" t="s">
+      <c r="B35" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C35" s="83" t="s">
+      <c r="C35" s="82" t="s">
         <v>3312</v>
       </c>
-      <c r="D35" s="82">
+      <c r="D35" s="81">
         <v>700</v>
       </c>
-      <c r="E35" s="82">
+      <c r="E35" s="81">
         <v>750</v>
       </c>
-      <c r="F35" s="82">
+      <c r="F35" s="81">
         <v>750</v>
       </c>
-      <c r="G35" s="81"/>
+      <c r="G35" s="80"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="83" t="s">
+      <c r="B36" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C36" s="83" t="s">
+      <c r="C36" s="82" t="s">
         <v>3489</v>
       </c>
-      <c r="D36" s="82">
+      <c r="D36" s="81">
         <v>2000</v>
       </c>
-      <c r="E36" s="82">
+      <c r="E36" s="81">
         <v>950</v>
       </c>
-      <c r="F36" s="82">
+      <c r="F36" s="81">
         <v>800</v>
       </c>
-      <c r="G36" s="81"/>
+      <c r="G36" s="80"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="83" t="s">
+      <c r="B37" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C37" s="83" t="s">
+      <c r="C37" s="82" t="s">
         <v>3490</v>
       </c>
-      <c r="D37" s="82">
+      <c r="D37" s="81">
         <v>745</v>
       </c>
-      <c r="E37" s="82">
+      <c r="E37" s="81">
         <v>780</v>
       </c>
-      <c r="F37" s="82">
+      <c r="F37" s="81">
         <v>900</v>
       </c>
-      <c r="G37" s="81"/>
+      <c r="G37" s="80"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="83" t="s">
+      <c r="B38" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C38" s="83" t="s">
+      <c r="C38" s="82" t="s">
         <v>3487</v>
       </c>
-      <c r="D38" s="82">
+      <c r="D38" s="81">
         <v>1150</v>
       </c>
-      <c r="E38" s="82">
+      <c r="E38" s="81">
         <v>1200</v>
       </c>
-      <c r="F38" s="82">
+      <c r="F38" s="81">
         <v>1400</v>
       </c>
-      <c r="G38" s="81"/>
+      <c r="G38" s="80"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="83" t="s">
+      <c r="B39" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C39" s="83" t="s">
+      <c r="C39" s="82" t="s">
         <v>3485</v>
       </c>
-      <c r="D39" s="82">
+      <c r="D39" s="81">
         <v>2780</v>
       </c>
-      <c r="E39" s="82">
+      <c r="E39" s="81">
         <v>3590</v>
       </c>
-      <c r="F39" s="82">
+      <c r="F39" s="81">
         <v>2300</v>
       </c>
-      <c r="G39" s="81"/>
+      <c r="G39" s="80"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="83" t="s">
+      <c r="B40" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C40" s="83" t="s">
+      <c r="C40" s="82" t="s">
         <v>3488</v>
       </c>
-      <c r="D40" s="82">
+      <c r="D40" s="81">
         <v>3490</v>
       </c>
-      <c r="E40" s="82">
+      <c r="E40" s="81">
         <v>32840</v>
       </c>
-      <c r="F40" s="82">
+      <c r="F40" s="81">
         <v>3070</v>
       </c>
-      <c r="G40" s="81"/>
+      <c r="G40" s="80"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="83" t="s">
+      <c r="B41" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C41" s="83" t="s">
+      <c r="C41" s="82" t="s">
         <v>3484</v>
       </c>
-      <c r="D41" s="82">
+      <c r="D41" s="81">
         <v>4700</v>
       </c>
-      <c r="E41" s="82">
+      <c r="E41" s="81">
         <v>4700</v>
       </c>
-      <c r="F41" s="82">
+      <c r="F41" s="81">
         <v>4700</v>
       </c>
-      <c r="G41" s="81"/>
+      <c r="G41" s="80"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="83" t="s">
+      <c r="B42" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C42" s="83" t="s">
+      <c r="C42" s="82" t="s">
         <v>3483</v>
       </c>
-      <c r="D42" s="82">
+      <c r="D42" s="81">
         <v>5250</v>
       </c>
-      <c r="E42" s="82">
+      <c r="E42" s="81">
         <v>5000</v>
       </c>
-      <c r="F42" s="82">
+      <c r="F42" s="81">
         <v>5500</v>
       </c>
-      <c r="G42" s="81"/>
+      <c r="G42" s="80"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="83" t="s">
+      <c r="B43" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C43" s="83" t="s">
+      <c r="C43" s="82" t="s">
         <v>3486</v>
       </c>
-      <c r="D43" s="82">
+      <c r="D43" s="81">
         <v>6980</v>
       </c>
-      <c r="E43" s="82">
+      <c r="E43" s="81">
         <v>6310</v>
       </c>
-      <c r="F43" s="82">
+      <c r="F43" s="81">
         <v>6375</v>
       </c>
-      <c r="G43" s="81"/>
+      <c r="G43" s="80"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B44" s="83" t="s">
+      <c r="B44" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C44" s="83" t="s">
+      <c r="C44" s="82" t="s">
         <v>3482</v>
       </c>
-      <c r="D44" s="82">
+      <c r="D44" s="81">
         <v>11250</v>
       </c>
-      <c r="E44" s="82">
+      <c r="E44" s="81">
         <v>11250</v>
       </c>
-      <c r="F44" s="82">
+      <c r="F44" s="81">
         <v>11750</v>
       </c>
-      <c r="G44" s="81"/>
+      <c r="G44" s="80"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B45" s="83" t="s">
+      <c r="B45" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C45" s="83" t="s">
+      <c r="C45" s="82" t="s">
         <v>3481</v>
       </c>
-      <c r="D45" s="82">
+      <c r="D45" s="81">
         <v>24500</v>
       </c>
-      <c r="E45" s="82">
+      <c r="E45" s="81">
         <v>23500</v>
       </c>
-      <c r="F45" s="82">
+      <c r="F45" s="81">
         <v>24500</v>
       </c>
-      <c r="G45" s="81"/>
+      <c r="G45" s="80"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B46" s="83" t="s">
+      <c r="B46" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C46" s="83" t="s">
+      <c r="C46" s="82" t="s">
         <v>3480</v>
       </c>
-      <c r="D46" s="82">
+      <c r="D46" s="81">
         <v>56900</v>
       </c>
-      <c r="E46" s="82">
+      <c r="E46" s="81">
         <v>62800</v>
       </c>
-      <c r="F46" s="82">
+      <c r="F46" s="81">
         <v>60870</v>
       </c>
-      <c r="G46" s="81"/>
+      <c r="G46" s="80"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B47" s="83" t="s">
+      <c r="B47" s="82" t="s">
         <v>3493</v>
       </c>
-      <c r="C47" s="83" t="s">
+      <c r="C47" s="82" t="s">
         <v>3478</v>
       </c>
-      <c r="D47" s="82">
+      <c r="D47" s="81">
         <v>24290</v>
       </c>
-      <c r="E47" s="82">
+      <c r="E47" s="81">
         <v>24050</v>
       </c>
-      <c r="F47" s="82">
+      <c r="F47" s="81">
         <v>26600</v>
       </c>
-      <c r="G47" s="81"/>
+      <c r="G47" s="80"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B48" s="83" t="s">
+      <c r="B48" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C48" s="83" t="s">
+      <c r="C48" s="82" t="s">
         <v>3492</v>
       </c>
-      <c r="D48" s="82">
+      <c r="D48" s="81">
         <v>775</v>
       </c>
-      <c r="E48" s="82">
+      <c r="E48" s="81">
         <v>750</v>
       </c>
-      <c r="F48" s="82">
+      <c r="F48" s="81">
         <v>700</v>
       </c>
-      <c r="G48" s="81"/>
+      <c r="G48" s="80"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B49" s="83" t="s">
+      <c r="B49" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C49" s="83" t="s">
+      <c r="C49" s="82" t="s">
         <v>3312</v>
       </c>
-      <c r="D49" s="82">
+      <c r="D49" s="81">
         <v>700</v>
       </c>
-      <c r="E49" s="82">
+      <c r="E49" s="81">
         <v>750</v>
       </c>
-      <c r="F49" s="82">
+      <c r="F49" s="81">
         <v>750</v>
       </c>
-      <c r="G49" s="81"/>
+      <c r="G49" s="80"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B50" s="83" t="s">
+      <c r="B50" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C50" s="83" t="s">
+      <c r="C50" s="82" t="s">
         <v>3491</v>
       </c>
-      <c r="D50" s="82">
+      <c r="D50" s="81">
         <v>300</v>
       </c>
-      <c r="E50" s="82">
+      <c r="E50" s="81">
         <v>100</v>
       </c>
-      <c r="F50" s="82">
+      <c r="F50" s="81">
         <v>150</v>
       </c>
-      <c r="G50" s="81"/>
+      <c r="G50" s="80"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B51" s="83" t="s">
+      <c r="B51" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C51" s="83" t="s">
+      <c r="C51" s="82" t="s">
         <v>3490</v>
       </c>
-      <c r="D51" s="82">
+      <c r="D51" s="81">
         <v>2000</v>
       </c>
-      <c r="E51" s="82">
+      <c r="E51" s="81">
         <v>1800</v>
       </c>
-      <c r="F51" s="82">
+      <c r="F51" s="81">
         <v>1900</v>
       </c>
-      <c r="G51" s="81"/>
+      <c r="G51" s="80"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B52" s="83" t="s">
+      <c r="B52" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C52" s="83" t="s">
+      <c r="C52" s="82" t="s">
         <v>3489</v>
       </c>
-      <c r="D52" s="82">
+      <c r="D52" s="81">
         <v>2000</v>
       </c>
-      <c r="E52" s="82">
+      <c r="E52" s="81">
         <v>950</v>
       </c>
-      <c r="F52" s="82">
+      <c r="F52" s="81">
         <v>800</v>
       </c>
-      <c r="G52" s="81"/>
+      <c r="G52" s="80"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B53" s="83" t="s">
+      <c r="B53" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C53" s="83" t="s">
+      <c r="C53" s="82" t="s">
         <v>3488</v>
       </c>
-      <c r="D53" s="82">
+      <c r="D53" s="81">
         <v>1250</v>
       </c>
-      <c r="E53" s="82">
+      <c r="E53" s="81">
         <v>1250</v>
       </c>
-      <c r="F53" s="82">
+      <c r="F53" s="81">
         <v>1250</v>
       </c>
-      <c r="G53" s="81"/>
+      <c r="G53" s="80"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B54" s="83" t="s">
+      <c r="B54" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C54" s="83" t="s">
+      <c r="C54" s="82" t="s">
         <v>3487</v>
       </c>
-      <c r="D54" s="82">
+      <c r="D54" s="81">
         <v>1150</v>
       </c>
-      <c r="E54" s="82">
+      <c r="E54" s="81">
         <v>1200</v>
       </c>
-      <c r="F54" s="82">
+      <c r="F54" s="81">
         <v>1435</v>
       </c>
-      <c r="G54" s="81"/>
+      <c r="G54" s="80"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B55" s="83" t="s">
+      <c r="B55" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C55" s="83" t="s">
+      <c r="C55" s="82" t="s">
         <v>3486</v>
       </c>
-      <c r="D55" s="82">
+      <c r="D55" s="81">
         <v>3800</v>
       </c>
-      <c r="E55" s="82">
+      <c r="E55" s="81">
         <v>3700</v>
       </c>
-      <c r="F55" s="82">
+      <c r="F55" s="81">
         <v>3750</v>
       </c>
-      <c r="G55" s="81"/>
+      <c r="G55" s="80"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B56" s="83" t="s">
+      <c r="B56" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C56" s="83" t="s">
+      <c r="C56" s="82" t="s">
         <v>3485</v>
       </c>
-      <c r="D56" s="82">
+      <c r="D56" s="81">
         <v>5000</v>
       </c>
-      <c r="E56" s="82">
+      <c r="E56" s="81">
         <v>4800</v>
       </c>
-      <c r="F56" s="82">
+      <c r="F56" s="81">
         <v>4545</v>
       </c>
-      <c r="G56" s="81"/>
+      <c r="G56" s="80"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B57" s="83" t="s">
+      <c r="B57" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C57" s="83" t="s">
+      <c r="C57" s="82" t="s">
         <v>3484</v>
       </c>
-      <c r="D57" s="82">
+      <c r="D57" s="81">
         <v>5000</v>
       </c>
-      <c r="E57" s="82">
+      <c r="E57" s="81">
         <v>5000</v>
       </c>
-      <c r="F57" s="82">
+      <c r="F57" s="81">
         <v>5000</v>
       </c>
-      <c r="G57" s="81"/>
+      <c r="G57" s="80"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B58" s="83" t="s">
+      <c r="B58" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C58" s="83" t="s">
+      <c r="C58" s="82" t="s">
         <v>3483</v>
       </c>
-      <c r="D58" s="82">
+      <c r="D58" s="81">
         <v>5250</v>
       </c>
-      <c r="E58" s="82">
+      <c r="E58" s="81">
         <v>5335</v>
       </c>
-      <c r="F58" s="82">
+      <c r="F58" s="81">
         <v>5500</v>
       </c>
-      <c r="G58" s="81"/>
+      <c r="G58" s="80"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B59" s="83" t="s">
+      <c r="B59" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C59" s="83" t="s">
+      <c r="C59" s="82" t="s">
         <v>3482</v>
       </c>
-      <c r="D59" s="82">
+      <c r="D59" s="81">
         <v>10250</v>
       </c>
-      <c r="E59" s="82">
+      <c r="E59" s="81">
         <v>10250</v>
       </c>
-      <c r="F59" s="82">
+      <c r="F59" s="81">
         <v>10750</v>
       </c>
-      <c r="G59" s="81"/>
+      <c r="G59" s="80"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B60" s="83" t="s">
+      <c r="B60" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C60" s="83" t="s">
+      <c r="C60" s="82" t="s">
         <v>3481</v>
       </c>
-      <c r="D60" s="82">
+      <c r="D60" s="81">
         <v>14500</v>
       </c>
-      <c r="E60" s="82">
+      <c r="E60" s="81">
         <v>13500</v>
       </c>
-      <c r="F60" s="82">
+      <c r="F60" s="81">
         <v>15500</v>
       </c>
-      <c r="G60" s="81"/>
+      <c r="G60" s="80"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B61" s="83" t="s">
+      <c r="B61" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C61" s="83" t="s">
+      <c r="C61" s="82" t="s">
         <v>3480</v>
       </c>
-      <c r="D61" s="82">
+      <c r="D61" s="81">
         <v>72000</v>
       </c>
-      <c r="E61" s="82">
+      <c r="E61" s="81">
         <v>70000</v>
       </c>
-      <c r="F61" s="82">
+      <c r="F61" s="81">
         <v>70000</v>
       </c>
-      <c r="G61" s="81"/>
+      <c r="G61" s="80"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B62" s="83" t="s">
+      <c r="B62" s="82" t="s">
         <v>3479</v>
       </c>
-      <c r="C62" s="83" t="s">
+      <c r="C62" s="82" t="s">
         <v>3478</v>
       </c>
-      <c r="D62" s="82">
+      <c r="D62" s="81">
         <v>25000</v>
       </c>
-      <c r="E62" s="82">
+      <c r="E62" s="81">
         <v>24000</v>
       </c>
-      <c r="F62" s="82">
+      <c r="F62" s="81">
         <v>26000</v>
       </c>
-      <c r="G62" s="81"/>
+      <c r="G62" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -39914,444 +40405,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
-    <tabColor theme="0" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:B52"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B46" s="16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>135</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.249977111117893"/>
@@ -43212,6 +43265,444 @@
       </c>
       <c r="D190" s="18">
         <v>36778</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <tabColor theme="0" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:B52"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -47375,822 +47866,822 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="116" t="s">
         <v>3450</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
     </row>
     <row r="2" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="117"/>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
+      <c r="A2" s="116"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
     </row>
     <row r="3" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="63" t="s">
         <v>3448</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="63" t="s">
         <v>3320</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="63" t="s">
         <v>3323</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="63" t="s">
         <v>3447</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="63" t="s">
         <v>3443</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="66">
+      <c r="A4" s="65">
         <v>1672</v>
       </c>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="67"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="66"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="118" t="s">
+      <c r="A7" s="117" t="s">
         <v>3449</v>
       </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="117"/>
-      <c r="B8" s="117"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117"/>
-      <c r="I8" s="117"/>
+      <c r="A8" s="116"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="116"/>
+      <c r="H8" s="116"/>
+      <c r="I8" s="116"/>
     </row>
     <row r="9" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="63" t="s">
         <v>3448</v>
       </c>
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="63" t="s">
         <v>3320</v>
       </c>
-      <c r="C9" s="64" t="s">
+      <c r="C9" s="63" t="s">
         <v>3323</v>
       </c>
-      <c r="D9" s="64" t="s">
+      <c r="D9" s="63" t="s">
         <v>3447</v>
       </c>
-      <c r="E9" s="64" t="s">
+      <c r="E9" s="63" t="s">
         <v>3313</v>
       </c>
-      <c r="F9" s="64" t="s">
+      <c r="F9" s="63" t="s">
         <v>3446</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="63" t="s">
         <v>3445</v>
       </c>
-      <c r="H9" s="64" t="s">
+      <c r="H9" s="63" t="s">
         <v>3444</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="63" t="s">
         <v>3443</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="63">
+      <c r="A10" s="62">
         <v>1054</v>
       </c>
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="62" t="s">
         <v>3356</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="62" t="s">
         <v>3442</v>
       </c>
-      <c r="D10" s="63" t="s">
+      <c r="D10" s="62" t="s">
         <v>3342</v>
       </c>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="62" t="s">
         <v>3441</v>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="62">
         <v>148</v>
       </c>
-      <c r="G10" s="63" t="s">
+      <c r="G10" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H10" s="62">
+      <c r="H10" s="61">
         <v>38092.25</v>
       </c>
-      <c r="I10" s="61">
+      <c r="I10" s="60">
         <v>11.25</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="63">
+      <c r="A11" s="62">
         <v>1056</v>
       </c>
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="62" t="s">
         <v>3440</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="62" t="s">
         <v>3439</v>
       </c>
-      <c r="D11" s="63" t="s">
+      <c r="D11" s="62" t="s">
         <v>3342</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="62" t="s">
         <v>3438</v>
       </c>
-      <c r="F11" s="63">
+      <c r="F11" s="62">
         <v>121</v>
       </c>
-      <c r="G11" s="63" t="s">
+      <c r="G11" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H11" s="62">
+      <c r="H11" s="61">
         <v>33901.25</v>
       </c>
-      <c r="I11" s="61">
+      <c r="I11" s="60">
         <v>12.25</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="63">
+      <c r="A12" s="62">
         <v>1067</v>
       </c>
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="62" t="s">
         <v>3437</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="62" t="s">
         <v>3436</v>
       </c>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="62" t="s">
         <v>3342</v>
       </c>
-      <c r="E12" s="63" t="s">
+      <c r="E12" s="62" t="s">
         <v>3435</v>
       </c>
-      <c r="F12" s="63">
+      <c r="F12" s="62">
         <v>123</v>
       </c>
-      <c r="G12" s="63" t="s">
+      <c r="G12" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H12" s="62">
+      <c r="H12" s="61">
         <v>36788.25</v>
       </c>
-      <c r="I12" s="61">
+      <c r="I12" s="60">
         <v>14.55</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="63">
+      <c r="A13" s="62">
         <v>1075</v>
       </c>
-      <c r="B13" s="63" t="s">
+      <c r="B13" s="62" t="s">
         <v>3434</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="62" t="s">
         <v>3433</v>
       </c>
-      <c r="D13" s="63" t="s">
+      <c r="D13" s="62" t="s">
         <v>3385</v>
       </c>
-      <c r="E13" s="63" t="s">
+      <c r="E13" s="62" t="s">
         <v>3432</v>
       </c>
-      <c r="F13" s="63">
+      <c r="F13" s="62">
         <v>126</v>
       </c>
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H13" s="62">
+      <c r="H13" s="61">
         <v>38571.25</v>
       </c>
-      <c r="I13" s="61">
+      <c r="I13" s="60">
         <v>11.25</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="63">
+      <c r="A14" s="62">
         <v>1078</v>
       </c>
-      <c r="B14" s="63" t="s">
+      <c r="B14" s="62" t="s">
         <v>3431</v>
       </c>
-      <c r="C14" s="63" t="s">
+      <c r="C14" s="62" t="s">
         <v>3430</v>
       </c>
-      <c r="D14" s="63" t="s">
+      <c r="D14" s="62" t="s">
         <v>3354</v>
       </c>
-      <c r="E14" s="63" t="s">
+      <c r="E14" s="62" t="s">
         <v>3429</v>
       </c>
-      <c r="F14" s="63">
+      <c r="F14" s="62">
         <v>101</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H14" s="62">
+      <c r="H14" s="61">
         <v>36251.25</v>
       </c>
-      <c r="I14" s="61">
+      <c r="I14" s="60">
         <v>10.199999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="63">
+      <c r="A15" s="62">
         <v>1152</v>
       </c>
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="62" t="s">
         <v>3428</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="D15" s="63" t="s">
+      <c r="D15" s="62" t="s">
         <v>3385</v>
       </c>
-      <c r="E15" s="63" t="s">
+      <c r="E15" s="62" t="s">
         <v>3427</v>
       </c>
-      <c r="F15" s="63">
+      <c r="F15" s="62">
         <v>118</v>
       </c>
-      <c r="G15" s="63" t="s">
+      <c r="G15" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H15" s="62">
+      <c r="H15" s="61">
         <v>37642.25</v>
       </c>
-      <c r="I15" s="61">
+      <c r="I15" s="60">
         <v>12.25</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="63">
+      <c r="A16" s="62">
         <v>1196</v>
       </c>
-      <c r="B16" s="63" t="s">
+      <c r="B16" s="62" t="s">
         <v>3426</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="62" t="s">
         <v>3425</v>
       </c>
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="62" t="s">
         <v>3337</v>
       </c>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="62" t="s">
         <v>3424</v>
       </c>
-      <c r="F16" s="63">
+      <c r="F16" s="62">
         <v>289</v>
       </c>
-      <c r="G16" s="63" t="s">
+      <c r="G16" s="62" t="s">
         <v>3335</v>
       </c>
-      <c r="H16" s="62">
+      <c r="H16" s="61">
         <v>40634.25</v>
       </c>
-      <c r="I16" s="61">
+      <c r="I16" s="60">
         <v>9.9499999999999993</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="63">
+      <c r="A17" s="62">
         <v>1284</v>
       </c>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="62" t="s">
         <v>3423</v>
       </c>
-      <c r="C17" s="63" t="s">
+      <c r="C17" s="62" t="s">
         <v>3386</v>
       </c>
-      <c r="D17" s="63" t="s">
+      <c r="D17" s="62" t="s">
         <v>3377</v>
       </c>
-      <c r="E17" s="63" t="s">
+      <c r="E17" s="62" t="s">
         <v>3422</v>
       </c>
-      <c r="F17" s="63">
+      <c r="F17" s="62">
         <v>124</v>
       </c>
-      <c r="G17" s="63" t="s">
+      <c r="G17" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H17" s="62">
+      <c r="H17" s="61">
         <v>35799.25</v>
       </c>
-      <c r="I17" s="61">
+      <c r="I17" s="60">
         <v>12.3</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="63">
+      <c r="A18" s="62">
         <v>1290</v>
       </c>
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="62" t="s">
         <v>3421</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="62" t="s">
         <v>3420</v>
       </c>
-      <c r="D18" s="63" t="s">
+      <c r="D18" s="62" t="s">
         <v>3385</v>
       </c>
-      <c r="E18" s="63" t="s">
+      <c r="E18" s="62" t="s">
         <v>3419</v>
       </c>
-      <c r="F18" s="63">
+      <c r="F18" s="62">
         <v>113</v>
       </c>
-      <c r="G18" s="63" t="s">
+      <c r="G18" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H18" s="62">
+      <c r="H18" s="61">
         <v>35798.25</v>
       </c>
-      <c r="I18" s="61">
+      <c r="I18" s="60">
         <v>13.25</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="63">
+      <c r="A19" s="62">
         <v>1293</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B19" s="62" t="s">
         <v>3418</v>
       </c>
-      <c r="C19" s="63" t="s">
+      <c r="C19" s="62" t="s">
         <v>3417</v>
       </c>
-      <c r="D19" s="63" t="s">
+      <c r="D19" s="62" t="s">
         <v>3337</v>
       </c>
-      <c r="E19" s="63" t="s">
+      <c r="E19" s="62" t="s">
         <v>3416</v>
       </c>
-      <c r="F19" s="63">
+      <c r="F19" s="62">
         <v>205</v>
       </c>
-      <c r="G19" s="63" t="s">
+      <c r="G19" s="62" t="s">
         <v>3335</v>
       </c>
-      <c r="H19" s="62">
+      <c r="H19" s="61">
         <v>35687.25</v>
       </c>
-      <c r="I19" s="61">
+      <c r="I19" s="60">
         <v>10.199999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="63">
+      <c r="A20" s="62">
         <v>1299</v>
       </c>
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="62" t="s">
         <v>3415</v>
       </c>
-      <c r="C20" s="63" t="s">
+      <c r="C20" s="62" t="s">
         <v>3414</v>
       </c>
-      <c r="D20" s="63" t="s">
+      <c r="D20" s="62" t="s">
         <v>3346</v>
       </c>
-      <c r="E20" s="63" t="s">
+      <c r="E20" s="62" t="s">
         <v>3413</v>
       </c>
-      <c r="F20" s="63">
+      <c r="F20" s="62">
         <v>127</v>
       </c>
-      <c r="G20" s="63" t="s">
+      <c r="G20" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H20" s="62">
+      <c r="H20" s="61">
         <v>37611.25</v>
       </c>
-      <c r="I20" s="61">
+      <c r="I20" s="60">
         <v>12.2</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="63">
+      <c r="A21" s="62">
         <v>1302</v>
       </c>
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="62" t="s">
         <v>3356</v>
       </c>
-      <c r="C21" s="63" t="s">
+      <c r="C21" s="62" t="s">
         <v>3412</v>
       </c>
-      <c r="D21" s="63" t="s">
+      <c r="D21" s="62" t="s">
         <v>3377</v>
       </c>
-      <c r="E21" s="63" t="s">
+      <c r="E21" s="62" t="s">
         <v>3411</v>
       </c>
-      <c r="F21" s="63">
+      <c r="F21" s="62">
         <v>139</v>
       </c>
-      <c r="G21" s="63" t="s">
+      <c r="G21" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H21" s="62">
+      <c r="H21" s="61">
         <v>35648.25</v>
       </c>
-      <c r="I21" s="61">
+      <c r="I21" s="60">
         <v>14.25</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="63">
+      <c r="A22" s="62">
         <v>1310</v>
       </c>
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="62" t="s">
         <v>3356</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="62" t="s">
         <v>3410</v>
       </c>
-      <c r="D22" s="63" t="s">
+      <c r="D22" s="62" t="s">
         <v>3346</v>
       </c>
-      <c r="E22" s="63" t="s">
+      <c r="E22" s="62" t="s">
         <v>3409</v>
       </c>
-      <c r="F22" s="63">
+      <c r="F22" s="62">
         <v>137</v>
       </c>
-      <c r="G22" s="63" t="s">
+      <c r="G22" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H22" s="62">
+      <c r="H22" s="61">
         <v>36437.25</v>
       </c>
-      <c r="I22" s="61">
+      <c r="I22" s="60">
         <v>11.5</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="63">
+      <c r="A23" s="62">
         <v>1329</v>
       </c>
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="62" t="s">
         <v>3408</v>
       </c>
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="62" t="s">
         <v>3407</v>
       </c>
-      <c r="D23" s="63" t="s">
+      <c r="D23" s="62" t="s">
         <v>3354</v>
       </c>
-      <c r="E23" s="63" t="s">
+      <c r="E23" s="62" t="s">
         <v>3406</v>
       </c>
-      <c r="F23" s="63">
+      <c r="F23" s="62">
         <v>151</v>
       </c>
-      <c r="G23" s="63" t="s">
+      <c r="G23" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H23" s="62">
+      <c r="H23" s="61">
         <v>37309.25</v>
       </c>
-      <c r="I23" s="61">
+      <c r="I23" s="60">
         <v>10.35</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="63">
+      <c r="A24" s="62">
         <v>1333</v>
       </c>
-      <c r="B24" s="63" t="s">
+      <c r="B24" s="62" t="s">
         <v>3405</v>
       </c>
-      <c r="C24" s="63" t="s">
+      <c r="C24" s="62" t="s">
         <v>3404</v>
       </c>
-      <c r="D24" s="63" t="s">
+      <c r="D24" s="62" t="s">
         <v>3337</v>
       </c>
-      <c r="E24" s="63" t="s">
+      <c r="E24" s="62" t="s">
         <v>3403</v>
       </c>
-      <c r="F24" s="63">
+      <c r="F24" s="62">
         <v>122</v>
       </c>
-      <c r="G24" s="63" t="s">
+      <c r="G24" s="62" t="s">
         <v>3335</v>
       </c>
-      <c r="H24" s="62">
+      <c r="H24" s="61">
         <v>37727.25</v>
       </c>
-      <c r="I24" s="61">
+      <c r="I24" s="60">
         <v>10.15</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="63">
+      <c r="A25" s="62">
         <v>1368</v>
       </c>
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="62" t="s">
         <v>3402</v>
       </c>
-      <c r="C25" s="63" t="s">
+      <c r="C25" s="62" t="s">
         <v>3401</v>
       </c>
-      <c r="D25" s="63" t="s">
+      <c r="D25" s="62" t="s">
         <v>3385</v>
       </c>
-      <c r="E25" s="63" t="s">
+      <c r="E25" s="62" t="s">
         <v>3400</v>
       </c>
-      <c r="F25" s="63">
+      <c r="F25" s="62">
         <v>132</v>
       </c>
-      <c r="G25" s="63" t="s">
+      <c r="G25" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H25" s="62">
+      <c r="H25" s="61">
         <v>35134.25</v>
       </c>
-      <c r="I25" s="61">
+      <c r="I25" s="60">
         <v>12.25</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="63">
+      <c r="A26" s="62">
         <v>1509</v>
       </c>
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="62" t="s">
         <v>3344</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="62" t="s">
         <v>3399</v>
       </c>
-      <c r="D26" s="63" t="s">
+      <c r="D26" s="62" t="s">
         <v>3342</v>
       </c>
-      <c r="E26" s="63" t="s">
+      <c r="E26" s="62" t="s">
         <v>3398</v>
       </c>
-      <c r="F26" s="63">
+      <c r="F26" s="62">
         <v>135</v>
       </c>
-      <c r="G26" s="63" t="s">
+      <c r="G26" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H26" s="62">
+      <c r="H26" s="61">
         <v>35965.25</v>
       </c>
-      <c r="I26" s="61">
+      <c r="I26" s="60">
         <v>13.25</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="63">
+      <c r="A27" s="62">
         <v>1516</v>
       </c>
-      <c r="B27" s="63" t="s">
+      <c r="B27" s="62" t="s">
         <v>3356</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="D27" s="63" t="s">
+      <c r="D27" s="62" t="s">
         <v>3354</v>
       </c>
-      <c r="E27" s="63" t="s">
+      <c r="E27" s="62" t="s">
         <v>3397</v>
       </c>
-      <c r="F27" s="63">
+      <c r="F27" s="62">
         <v>105</v>
       </c>
-      <c r="G27" s="63" t="s">
+      <c r="G27" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H27" s="62">
+      <c r="H27" s="61">
         <v>35860.25</v>
       </c>
-      <c r="I27" s="61">
+      <c r="I27" s="60">
         <v>9.5</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="63">
+      <c r="A28" s="62">
         <v>1529</v>
       </c>
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="62" t="s">
         <v>3396</v>
       </c>
-      <c r="C28" s="63" t="s">
+      <c r="C28" s="62" t="s">
         <v>3395</v>
       </c>
-      <c r="D28" s="63" t="s">
+      <c r="D28" s="62" t="s">
         <v>3377</v>
       </c>
-      <c r="E28" s="63" t="s">
+      <c r="E28" s="62" t="s">
         <v>3394</v>
       </c>
-      <c r="F28" s="63">
+      <c r="F28" s="62">
         <v>129</v>
       </c>
-      <c r="G28" s="63" t="s">
+      <c r="G28" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H28" s="62">
+      <c r="H28" s="61">
         <v>36553.25</v>
       </c>
-      <c r="I28" s="61">
+      <c r="I28" s="60">
         <v>11.3</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="63">
+      <c r="A29" s="62">
         <v>1656</v>
       </c>
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="62" t="s">
         <v>3393</v>
       </c>
-      <c r="C29" s="63" t="s">
+      <c r="C29" s="62" t="s">
         <v>3392</v>
       </c>
-      <c r="D29" s="63" t="s">
+      <c r="D29" s="62" t="s">
         <v>3346</v>
       </c>
-      <c r="E29" s="63" t="s">
+      <c r="E29" s="62" t="s">
         <v>3391</v>
       </c>
-      <c r="F29" s="63">
+      <c r="F29" s="62">
         <v>149</v>
       </c>
-      <c r="G29" s="63" t="s">
+      <c r="G29" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H29" s="62">
+      <c r="H29" s="61">
         <v>36873.25</v>
       </c>
-      <c r="I29" s="61">
+      <c r="I29" s="60">
         <v>12.35</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="63">
+      <c r="A30" s="62">
         <v>1672</v>
       </c>
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="62" t="s">
         <v>3390</v>
       </c>
-      <c r="C30" s="63" t="s">
+      <c r="C30" s="62" t="s">
         <v>3389</v>
       </c>
-      <c r="D30" s="63" t="s">
+      <c r="D30" s="62" t="s">
         <v>3346</v>
       </c>
-      <c r="E30" s="63" t="s">
+      <c r="E30" s="62" t="s">
         <v>3388</v>
       </c>
-      <c r="F30" s="63">
+      <c r="F30" s="62">
         <v>114</v>
       </c>
-      <c r="G30" s="63" t="s">
+      <c r="G30" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H30" s="62">
+      <c r="H30" s="61">
         <v>37727.25</v>
       </c>
-      <c r="I30" s="61">
+      <c r="I30" s="60">
         <v>11.9</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="63">
+      <c r="A31" s="62">
         <v>1673</v>
       </c>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="62" t="s">
         <v>3387</v>
       </c>
-      <c r="C31" s="63" t="s">
+      <c r="C31" s="62" t="s">
         <v>3386</v>
       </c>
-      <c r="D31" s="63" t="s">
+      <c r="D31" s="62" t="s">
         <v>3385</v>
       </c>
-      <c r="E31" s="63" t="s">
+      <c r="E31" s="62" t="s">
         <v>3384</v>
       </c>
-      <c r="F31" s="63">
+      <c r="F31" s="62">
         <v>112</v>
       </c>
-      <c r="G31" s="63" t="s">
+      <c r="G31" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H31" s="62">
+      <c r="H31" s="61">
         <v>38436.25</v>
       </c>
-      <c r="I31" s="61">
+      <c r="I31" s="60">
         <v>11.85</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="63">
+      <c r="A32" s="62">
         <v>1676</v>
       </c>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="62" t="s">
         <v>3344</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="62" t="s">
         <v>3383</v>
       </c>
-      <c r="D32" s="63" t="s">
+      <c r="D32" s="62" t="s">
         <v>3377</v>
       </c>
-      <c r="E32" s="63" t="s">
+      <c r="E32" s="62" t="s">
         <v>3382</v>
       </c>
-      <c r="F32" s="63">
+      <c r="F32" s="62">
         <v>115</v>
       </c>
-      <c r="G32" s="63" t="s">
+      <c r="G32" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H32" s="62">
+      <c r="H32" s="61">
         <v>34633.25</v>
       </c>
-      <c r="I32" s="61">
+      <c r="I32" s="60">
         <v>10.75</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="63">
+      <c r="A33" s="62">
         <v>1721</v>
       </c>
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="62" t="s">
         <v>3381</v>
       </c>
-      <c r="C33" s="63" t="s">
+      <c r="C33" s="62" t="s">
         <v>3380</v>
       </c>
-      <c r="D33" s="63" t="s">
+      <c r="D33" s="62" t="s">
         <v>3337</v>
       </c>
-      <c r="E33" s="63" t="s">
+      <c r="E33" s="62" t="s">
         <v>3379</v>
       </c>
-      <c r="F33" s="63">
+      <c r="F33" s="62">
         <v>102</v>
       </c>
-      <c r="G33" s="63" t="s">
+      <c r="G33" s="62" t="s">
         <v>3335</v>
       </c>
-      <c r="H33" s="62">
+      <c r="H33" s="61">
         <v>37839.25</v>
       </c>
-      <c r="I33" s="61">
+      <c r="I33" s="60">
         <v>9.75</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="63">
+      <c r="A34" s="62">
         <v>1723</v>
       </c>
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="62" t="s">
         <v>3378</v>
       </c>
-      <c r="C34" s="63" t="s">
+      <c r="C34" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="D34" s="63" t="s">
+      <c r="D34" s="62" t="s">
         <v>3377</v>
       </c>
-      <c r="E34" s="63" t="s">
+      <c r="E34" s="62" t="s">
         <v>3376</v>
       </c>
-      <c r="F34" s="63">
+      <c r="F34" s="62">
         <v>145</v>
       </c>
-      <c r="G34" s="63" t="s">
+      <c r="G34" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H34" s="62">
+      <c r="H34" s="61">
         <v>33279.25</v>
       </c>
-      <c r="I34" s="61">
+      <c r="I34" s="60">
         <v>13.95</v>
       </c>
       <c r="M34" s="49" t="s">
@@ -48198,350 +48689,350 @@
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="63">
+      <c r="A35" s="62">
         <v>1758</v>
       </c>
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="62" t="s">
         <v>3374</v>
       </c>
-      <c r="C35" s="63" t="s">
+      <c r="C35" s="62" t="s">
         <v>3373</v>
       </c>
-      <c r="D35" s="63" t="s">
+      <c r="D35" s="62" t="s">
         <v>3354</v>
       </c>
-      <c r="E35" s="63" t="s">
+      <c r="E35" s="62" t="s">
         <v>3372</v>
       </c>
-      <c r="F35" s="63">
+      <c r="F35" s="62">
         <v>107</v>
       </c>
-      <c r="G35" s="63" t="s">
+      <c r="G35" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H35" s="62">
+      <c r="H35" s="61">
         <v>34776.25</v>
       </c>
-      <c r="I35" s="61">
+      <c r="I35" s="60">
         <v>11.2</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="63">
+      <c r="A36" s="62">
         <v>1792</v>
       </c>
-      <c r="B36" s="63" t="s">
+      <c r="B36" s="62" t="s">
         <v>3371</v>
       </c>
-      <c r="C36" s="63" t="s">
+      <c r="C36" s="62" t="s">
         <v>3370</v>
       </c>
-      <c r="D36" s="63" t="s">
+      <c r="D36" s="62" t="s">
         <v>3342</v>
       </c>
-      <c r="E36" s="63" t="s">
+      <c r="E36" s="62" t="s">
         <v>3369</v>
       </c>
-      <c r="F36" s="63">
+      <c r="F36" s="62">
         <v>111</v>
       </c>
-      <c r="G36" s="63" t="s">
+      <c r="G36" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H36" s="62">
+      <c r="H36" s="61">
         <v>37979.25</v>
       </c>
-      <c r="I36" s="61">
+      <c r="I36" s="60">
         <v>10.3</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="63">
+      <c r="A37" s="62">
         <v>1814</v>
       </c>
-      <c r="B37" s="63" t="s">
+      <c r="B37" s="62" t="s">
         <v>3368</v>
       </c>
-      <c r="C37" s="63" t="s">
+      <c r="C37" s="62" t="s">
         <v>3367</v>
       </c>
-      <c r="D37" s="63" t="s">
+      <c r="D37" s="62" t="s">
         <v>3337</v>
       </c>
-      <c r="E37" s="63" t="s">
+      <c r="E37" s="62" t="s">
         <v>3366</v>
       </c>
-      <c r="F37" s="63">
+      <c r="F37" s="62">
         <v>103</v>
       </c>
-      <c r="G37" s="63" t="s">
+      <c r="G37" s="62" t="s">
         <v>3335</v>
       </c>
-      <c r="H37" s="62">
+      <c r="H37" s="61">
         <v>37319.25</v>
       </c>
-      <c r="I37" s="61">
+      <c r="I37" s="60">
         <v>12.25</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="63">
+      <c r="A38" s="62">
         <v>1908</v>
       </c>
-      <c r="B38" s="63" t="s">
+      <c r="B38" s="62" t="s">
         <v>3365</v>
       </c>
-      <c r="C38" s="63" t="s">
+      <c r="C38" s="62" t="s">
         <v>3364</v>
       </c>
-      <c r="D38" s="63" t="s">
+      <c r="D38" s="62" t="s">
         <v>3342</v>
       </c>
-      <c r="E38" s="63" t="s">
+      <c r="E38" s="62" t="s">
         <v>3363</v>
       </c>
-      <c r="F38" s="63">
+      <c r="F38" s="62">
         <v>152</v>
       </c>
-      <c r="G38" s="63" t="s">
+      <c r="G38" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H38" s="62">
+      <c r="H38" s="61">
         <v>35565.25</v>
       </c>
-      <c r="I38" s="61">
+      <c r="I38" s="60">
         <v>10.25</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="63">
+      <c r="A39" s="62">
         <v>1931</v>
       </c>
-      <c r="B39" s="63" t="s">
+      <c r="B39" s="62" t="s">
         <v>3344</v>
       </c>
-      <c r="C39" s="63" t="s">
+      <c r="C39" s="62" t="s">
         <v>3362</v>
       </c>
-      <c r="D39" s="63" t="s">
+      <c r="D39" s="62" t="s">
         <v>3354</v>
       </c>
-      <c r="E39" s="63" t="s">
+      <c r="E39" s="62" t="s">
         <v>3361</v>
       </c>
-      <c r="F39" s="63">
+      <c r="F39" s="62">
         <v>110</v>
       </c>
-      <c r="G39" s="63" t="s">
+      <c r="G39" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H39" s="62">
+      <c r="H39" s="61">
         <v>37427.25</v>
       </c>
-      <c r="I39" s="61">
+      <c r="I39" s="60">
         <v>9.85</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" s="63">
+      <c r="A40" s="62">
         <v>1960</v>
       </c>
-      <c r="B40" s="63" t="s">
+      <c r="B40" s="62" t="s">
         <v>3360</v>
       </c>
-      <c r="C40" s="63" t="s">
+      <c r="C40" s="62" t="s">
         <v>219</v>
       </c>
-      <c r="D40" s="63" t="s">
+      <c r="D40" s="62" t="s">
         <v>3346</v>
       </c>
-      <c r="E40" s="63" t="s">
+      <c r="E40" s="62" t="s">
         <v>3359</v>
       </c>
-      <c r="F40" s="63">
+      <c r="F40" s="62">
         <v>150</v>
       </c>
-      <c r="G40" s="63" t="s">
+      <c r="G40" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H40" s="62">
+      <c r="H40" s="61">
         <v>36477.25</v>
       </c>
-      <c r="I40" s="61">
+      <c r="I40" s="60">
         <v>11.65</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="63">
+      <c r="A41" s="62">
         <v>1964</v>
       </c>
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="62" t="s">
         <v>3351</v>
       </c>
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="62" t="s">
         <v>3358</v>
       </c>
-      <c r="D41" s="63" t="s">
+      <c r="D41" s="62" t="s">
         <v>3354</v>
       </c>
-      <c r="E41" s="63" t="s">
+      <c r="E41" s="62" t="s">
         <v>3357</v>
       </c>
-      <c r="F41" s="63">
+      <c r="F41" s="62">
         <v>108</v>
       </c>
-      <c r="G41" s="63" t="s">
+      <c r="G41" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H41" s="62">
+      <c r="H41" s="61">
         <v>38307.25</v>
       </c>
-      <c r="I41" s="61">
+      <c r="I41" s="60">
         <v>9.25</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="63">
+      <c r="A42" s="62">
         <v>1975</v>
       </c>
-      <c r="B42" s="63" t="s">
+      <c r="B42" s="62" t="s">
         <v>3356</v>
       </c>
-      <c r="C42" s="63" t="s">
+      <c r="C42" s="62" t="s">
         <v>3355</v>
       </c>
-      <c r="D42" s="63" t="s">
+      <c r="D42" s="62" t="s">
         <v>3354</v>
       </c>
-      <c r="E42" s="63" t="s">
+      <c r="E42" s="62" t="s">
         <v>3353</v>
       </c>
-      <c r="F42" s="63">
+      <c r="F42" s="62">
         <v>125</v>
       </c>
-      <c r="G42" s="63" t="s">
+      <c r="G42" s="62" t="s">
         <v>3352</v>
       </c>
-      <c r="H42" s="62">
+      <c r="H42" s="61">
         <v>39873.25</v>
       </c>
-      <c r="I42" s="61">
+      <c r="I42" s="60">
         <v>9.25</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="63">
+      <c r="A43" s="62">
         <v>1983</v>
       </c>
-      <c r="B43" s="63" t="s">
+      <c r="B43" s="62" t="s">
         <v>3351</v>
       </c>
-      <c r="C43" s="63" t="s">
+      <c r="C43" s="62" t="s">
         <v>3350</v>
       </c>
-      <c r="D43" s="63" t="s">
+      <c r="D43" s="62" t="s">
         <v>3342</v>
       </c>
-      <c r="E43" s="63" t="s">
+      <c r="E43" s="62" t="s">
         <v>3349</v>
       </c>
-      <c r="F43" s="63">
+      <c r="F43" s="62">
         <v>154</v>
       </c>
-      <c r="G43" s="63" t="s">
+      <c r="G43" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H43" s="62">
+      <c r="H43" s="61">
         <v>40357.25</v>
       </c>
-      <c r="I43" s="61">
+      <c r="I43" s="60">
         <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="63">
+      <c r="A44" s="62">
         <v>1990</v>
       </c>
-      <c r="B44" s="63" t="s">
+      <c r="B44" s="62" t="s">
         <v>3348</v>
       </c>
-      <c r="C44" s="63" t="s">
+      <c r="C44" s="62" t="s">
         <v>3347</v>
       </c>
-      <c r="D44" s="63" t="s">
+      <c r="D44" s="62" t="s">
         <v>3346</v>
       </c>
-      <c r="E44" s="63" t="s">
+      <c r="E44" s="62" t="s">
         <v>3345</v>
       </c>
-      <c r="F44" s="63">
+      <c r="F44" s="62">
         <v>198</v>
       </c>
-      <c r="G44" s="63" t="s">
+      <c r="G44" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H44" s="62">
+      <c r="H44" s="61">
         <v>40588.25</v>
       </c>
-      <c r="I44" s="61">
+      <c r="I44" s="60">
         <v>10.95</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="63">
+      <c r="A45" s="62">
         <v>1995</v>
       </c>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="62" t="s">
         <v>3344</v>
       </c>
-      <c r="C45" s="63" t="s">
+      <c r="C45" s="62" t="s">
         <v>3343</v>
       </c>
-      <c r="D45" s="63" t="s">
+      <c r="D45" s="62" t="s">
         <v>3342</v>
       </c>
-      <c r="E45" s="63" t="s">
+      <c r="E45" s="62" t="s">
         <v>3341</v>
       </c>
-      <c r="F45" s="63">
+      <c r="F45" s="62">
         <v>198</v>
       </c>
-      <c r="G45" s="63" t="s">
+      <c r="G45" s="62" t="s">
         <v>3340</v>
       </c>
-      <c r="H45" s="62">
+      <c r="H45" s="61">
         <v>40603.25</v>
       </c>
-      <c r="I45" s="61">
+      <c r="I45" s="60">
         <v>11.75</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="63">
+      <c r="A46" s="62">
         <v>2006</v>
       </c>
-      <c r="B46" s="63" t="s">
+      <c r="B46" s="62" t="s">
         <v>3339</v>
       </c>
-      <c r="C46" s="63" t="s">
+      <c r="C46" s="62" t="s">
         <v>3338</v>
       </c>
-      <c r="D46" s="63" t="s">
+      <c r="D46" s="62" t="s">
         <v>3337</v>
       </c>
-      <c r="E46" s="63" t="s">
+      <c r="E46" s="62" t="s">
         <v>3336</v>
       </c>
-      <c r="F46" s="63">
+      <c r="F46" s="62">
         <v>428</v>
       </c>
-      <c r="G46" s="63" t="s">
+      <c r="G46" s="62" t="s">
         <v>3335</v>
       </c>
-      <c r="H46" s="62">
+      <c r="H46" s="61">
         <v>40729.25</v>
       </c>
-      <c r="I46" s="61">
+      <c r="I46" s="60">
         <v>10.15</v>
       </c>
     </row>

--- a/Advanced Excel for practice.xlsx
+++ b/Advanced Excel for practice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f1c7af14bfcc0abe/Desktop/DA DS ITV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{2BAC444C-25A8-4E7A-A263-1D3A79421BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B92475C-6C78-4B1D-A660-910B31DADB7A}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{2BAC444C-25A8-4E7A-A263-1D3A79421BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8E940C1-7243-44C3-84F7-696EB153E310}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="645" firstSheet="15" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="645" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formulas" sheetId="19" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6360" uniqueCount="3570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6366" uniqueCount="3572">
   <si>
     <t>State</t>
   </si>
@@ -10813,6 +10813,12 @@
   </si>
   <si>
     <t>112283|AB-BOS_MEDIUM</t>
+  </si>
+  <si>
+    <t>Pay rate</t>
+  </si>
+  <si>
+    <t>Empolyee lookup</t>
   </si>
 </sst>
 </file>
@@ -11099,7 +11105,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -11222,6 +11228,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -11517,7 +11535,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11689,12 +11707,6 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="9" xfId="8" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="8" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="8" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -11805,6 +11817,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="12" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="17" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="33" fillId="14" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11853,10 +11869,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="12" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="11" xfId="17" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="17" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="17" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="13" fillId="8" borderId="11" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="11" xfId="17" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent2" xfId="12" builtinId="34"/>
@@ -15335,16 +15365,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>538701</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>141136</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>69850</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>116233</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>177358</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -15374,8 +15404,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8064500" y="266700"/>
-          <a:ext cx="4064000" cy="768350"/>
+          <a:off x="9997440" y="2046136"/>
+          <a:ext cx="3983879" cy="765092"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15396,16 +15426,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>546100</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>597453</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>34898</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>174985</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>70569</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -15435,8 +15465,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8115300" y="1219200"/>
-          <a:ext cx="4064000" cy="768350"/>
+          <a:off x="10056192" y="3033202"/>
+          <a:ext cx="3983879" cy="764540"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16598,13 +16628,13 @@
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="73" t="s">
         <v>3462</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="73" t="s">
         <v>3459</v>
       </c>
       <c r="E3" s="118" t="s">
@@ -16614,128 +16644,128 @@
       <c r="G3" s="120"/>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="70" t="s">
         <v>3460</v>
       </c>
-      <c r="B4" s="71">
+      <c r="B4" s="69">
         <v>1200</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="E4" s="74" t="s">
+      <c r="C4" s="68"/>
+      <c r="E4" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="71" t="s">
         <v>3459</v>
       </c>
-      <c r="G4" s="73" t="s">
+      <c r="G4" s="71" t="s">
         <v>3451</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="70" t="s">
         <v>3458</v>
       </c>
-      <c r="B5" s="71">
+      <c r="B5" s="69">
         <v>1300</v>
       </c>
-      <c r="C5" s="70"/>
-      <c r="E5" s="69">
+      <c r="C5" s="68"/>
+      <c r="E5" s="67">
         <v>0</v>
       </c>
-      <c r="F5" s="69">
+      <c r="F5" s="67">
         <v>0</v>
       </c>
-      <c r="G5" s="69">
+      <c r="G5" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="70" t="s">
         <v>3457</v>
       </c>
-      <c r="B6" s="71">
+      <c r="B6" s="69">
         <v>2500</v>
       </c>
-      <c r="C6" s="70"/>
-      <c r="E6" s="69">
+      <c r="C6" s="68"/>
+      <c r="E6" s="67">
         <v>1000</v>
       </c>
-      <c r="F6" s="69">
+      <c r="F6" s="67">
         <v>10</v>
       </c>
-      <c r="G6" s="69">
+      <c r="G6" s="67">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="70" t="s">
         <v>3456</v>
       </c>
-      <c r="B7" s="71">
+      <c r="B7" s="69">
         <v>850</v>
       </c>
-      <c r="C7" s="70"/>
-      <c r="E7" s="69">
+      <c r="C7" s="68"/>
+      <c r="E7" s="67">
         <v>1500</v>
       </c>
-      <c r="F7" s="69">
+      <c r="F7" s="67">
         <v>30</v>
       </c>
-      <c r="G7" s="69">
+      <c r="G7" s="67">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="70" t="s">
         <v>3455</v>
       </c>
-      <c r="B8" s="71">
+      <c r="B8" s="69">
         <v>3250</v>
       </c>
-      <c r="C8" s="70"/>
-      <c r="E8" s="69">
+      <c r="C8" s="68"/>
+      <c r="E8" s="67">
         <v>2000</v>
       </c>
-      <c r="F8" s="69">
+      <c r="F8" s="67">
         <v>85</v>
       </c>
-      <c r="G8" s="69">
+      <c r="G8" s="67">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="72" t="s">
+      <c r="A9" s="70" t="s">
         <v>3454</v>
       </c>
-      <c r="B9" s="71">
+      <c r="B9" s="69">
         <v>1100</v>
       </c>
-      <c r="C9" s="70"/>
-      <c r="E9" s="69">
+      <c r="C9" s="68"/>
+      <c r="E9" s="67">
         <v>2500</v>
       </c>
-      <c r="F9" s="69">
+      <c r="F9" s="67">
         <v>125</v>
       </c>
-      <c r="G9" s="69">
+      <c r="G9" s="67">
         <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="72" t="s">
+      <c r="A10" s="70" t="s">
         <v>3453</v>
       </c>
-      <c r="B10" s="71">
+      <c r="B10" s="69">
         <v>4520</v>
       </c>
-      <c r="C10" s="70"/>
-      <c r="E10" s="69">
+      <c r="C10" s="68"/>
+      <c r="E10" s="67">
         <v>3000</v>
       </c>
-      <c r="F10" s="69">
+      <c r="F10" s="67">
         <v>200</v>
       </c>
-      <c r="G10" s="69">
+      <c r="G10" s="67">
         <v>250</v>
       </c>
     </row>
@@ -16745,12 +16775,12 @@
         <v>3452</v>
       </c>
       <c r="B12" s="122"/>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="66" t="s">
         <v>3451</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="E13" s="67"/>
+      <c r="E13" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -16777,9 +16807,9 @@
   <dimension ref="A2:G14"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="76" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="10.21875" style="76" customWidth="1"/>
-    <col min="8" max="16384" width="9.21875" style="76"/>
+    <col min="1" max="1" width="19.44140625" style="74" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.21875" style="74" customWidth="1"/>
+    <col min="8" max="16384" width="9.21875" style="74"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
@@ -16798,32 +16828,32 @@
         <v>3476</v>
       </c>
       <c r="B4" s="124"/>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="74" t="s">
         <v>3547</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="75" t="s">
         <v>3475</v>
       </c>
-      <c r="B5" s="79" t="s">
+      <c r="B5" s="77" t="s">
         <v>3469</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="75" t="s">
         <v>3466</v>
       </c>
       <c r="B6" s="64"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="75" t="s">
         <v>3465</v>
       </c>
       <c r="B7" s="64"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="75" t="s">
         <v>3464</v>
       </c>
       <c r="B8" s="64"/>
@@ -16840,94 +16870,94 @@
       <c r="G10" s="124"/>
     </row>
     <row r="11" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="75" t="s">
         <v>3473</v>
       </c>
       <c r="B11" s="64" t="s">
         <v>3472</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="76" t="s">
         <v>3471</v>
       </c>
       <c r="D11" s="64" t="s">
         <v>3470</v>
       </c>
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="76" t="s">
         <v>3469</v>
       </c>
       <c r="F11" s="64" t="s">
         <v>3468</v>
       </c>
-      <c r="G11" s="78" t="s">
+      <c r="G11" s="76" t="s">
         <v>3467</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="75" t="s">
         <v>3466</v>
       </c>
       <c r="B12" s="64">
         <v>120</v>
       </c>
-      <c r="C12" s="73">
+      <c r="C12" s="71">
         <v>150</v>
       </c>
       <c r="D12" s="64">
         <v>135</v>
       </c>
-      <c r="E12" s="73">
+      <c r="E12" s="71">
         <v>90</v>
       </c>
       <c r="F12" s="64">
         <v>95</v>
       </c>
-      <c r="G12" s="73">
+      <c r="G12" s="71">
         <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="75" t="s">
         <v>3465</v>
       </c>
       <c r="B13" s="64">
         <v>55</v>
       </c>
-      <c r="C13" s="73">
+      <c r="C13" s="71">
         <v>110</v>
       </c>
       <c r="D13" s="64">
         <v>75</v>
       </c>
-      <c r="E13" s="73">
+      <c r="E13" s="71">
         <v>95</v>
       </c>
       <c r="F13" s="64">
         <v>75</v>
       </c>
-      <c r="G13" s="73">
+      <c r="G13" s="71">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="75" t="s">
         <v>3464</v>
       </c>
       <c r="B14" s="64">
         <v>70</v>
       </c>
-      <c r="C14" s="73">
+      <c r="C14" s="71">
         <v>115</v>
       </c>
       <c r="D14" s="64">
         <v>65</v>
       </c>
-      <c r="E14" s="73">
+      <c r="E14" s="71">
         <v>55</v>
       </c>
       <c r="F14" s="64">
         <v>85</v>
       </c>
-      <c r="G14" s="73">
+      <c r="G14" s="71">
         <v>65</v>
       </c>
     </row>
@@ -35630,11 +35660,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5546875" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" style="98" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" style="98" customWidth="1"/>
-    <col min="4" max="5" width="14.88671875" style="98" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" style="96" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" style="96" customWidth="1"/>
+    <col min="4" max="5" width="14.88671875" style="96" customWidth="1"/>
     <col min="6" max="6" width="24" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.44140625" style="97" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="95" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -35664,23 +35694,23 @@
       <c r="A2" s="20">
         <v>41640</v>
       </c>
-      <c r="B2" s="109">
+      <c r="B2" s="107">
         <v>1099</v>
       </c>
-      <c r="C2" s="109">
+      <c r="C2" s="107">
         <v>275</v>
       </c>
-      <c r="D2" s="109">
+      <c r="D2" s="107">
         <v>643</v>
       </c>
-      <c r="E2" s="109">
+      <c r="E2" s="107">
         <f>B2-D2</f>
         <v>456</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G2" s="108">
+      <c r="G2" s="106">
         <f t="shared" ref="G2:G25" si="0">E2/B2</f>
         <v>0.41492265696087355</v>
       </c>
@@ -35689,23 +35719,23 @@
       <c r="A3" s="20">
         <v>41671</v>
       </c>
-      <c r="B3" s="109">
+      <c r="B3" s="107">
         <v>1204</v>
       </c>
-      <c r="C3" s="109">
+      <c r="C3" s="107">
         <f t="shared" ref="C3:C25" si="1">B3-B2</f>
         <v>105</v>
       </c>
-      <c r="D3" s="109">
+      <c r="D3" s="107">
         <v>720</v>
       </c>
-      <c r="E3" s="109">
+      <c r="E3" s="107">
         <v>211</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="108">
+      <c r="G3" s="106">
         <f t="shared" si="0"/>
         <v>0.17524916943521596</v>
       </c>
@@ -35714,24 +35744,24 @@
       <c r="A4" s="20">
         <v>41699</v>
       </c>
-      <c r="B4" s="109">
+      <c r="B4" s="107">
         <v>1944</v>
       </c>
-      <c r="C4" s="109">
+      <c r="C4" s="107">
         <f t="shared" si="1"/>
         <v>740</v>
       </c>
-      <c r="D4" s="109">
+      <c r="D4" s="107">
         <v>964</v>
       </c>
-      <c r="E4" s="109">
+      <c r="E4" s="107">
         <f t="shared" ref="E4:E19" si="2">B4-D4</f>
         <v>980</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>3517</v>
       </c>
-      <c r="G4" s="108">
+      <c r="G4" s="106">
         <f t="shared" si="0"/>
         <v>0.50411522633744854</v>
       </c>
@@ -35740,24 +35770,24 @@
       <c r="A5" s="20">
         <v>41730</v>
       </c>
-      <c r="B5" s="109">
+      <c r="B5" s="107">
         <v>1743</v>
       </c>
-      <c r="C5" s="109">
+      <c r="C5" s="107">
         <f t="shared" si="1"/>
         <v>-201</v>
       </c>
-      <c r="D5" s="109">
+      <c r="D5" s="107">
         <v>830</v>
       </c>
-      <c r="E5" s="109">
+      <c r="E5" s="107">
         <f t="shared" si="2"/>
         <v>913</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="108">
+      <c r="G5" s="106">
         <f t="shared" si="0"/>
         <v>0.52380952380952384</v>
       </c>
@@ -35766,24 +35796,24 @@
       <c r="A6" s="20">
         <v>41760</v>
       </c>
-      <c r="B6" s="109">
+      <c r="B6" s="107">
         <v>1609</v>
       </c>
-      <c r="C6" s="109">
+      <c r="C6" s="107">
         <f t="shared" si="1"/>
         <v>-134</v>
       </c>
-      <c r="D6" s="109">
+      <c r="D6" s="107">
         <v>910</v>
       </c>
-      <c r="E6" s="109">
+      <c r="E6" s="107">
         <f t="shared" si="2"/>
         <v>699</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G6" s="108">
+      <c r="G6" s="106">
         <f t="shared" si="0"/>
         <v>0.43443132380360472</v>
       </c>
@@ -35792,24 +35822,24 @@
       <c r="A7" s="20">
         <v>41791</v>
       </c>
-      <c r="B7" s="109">
+      <c r="B7" s="107">
         <v>1494</v>
       </c>
-      <c r="C7" s="109">
+      <c r="C7" s="107">
         <f t="shared" si="1"/>
         <v>-115</v>
       </c>
-      <c r="D7" s="109">
+      <c r="D7" s="107">
         <v>909</v>
       </c>
-      <c r="E7" s="109">
+      <c r="E7" s="107">
         <f t="shared" si="2"/>
         <v>585</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G7" s="108">
+      <c r="G7" s="106">
         <f t="shared" si="0"/>
         <v>0.39156626506024095</v>
       </c>
@@ -35818,24 +35848,24 @@
       <c r="A8" s="20">
         <v>41821</v>
       </c>
-      <c r="B8" s="109">
+      <c r="B8" s="107">
         <v>1959</v>
       </c>
-      <c r="C8" s="109">
+      <c r="C8" s="107">
         <f t="shared" si="1"/>
         <v>465</v>
       </c>
-      <c r="D8" s="109">
+      <c r="D8" s="107">
         <v>830</v>
       </c>
-      <c r="E8" s="109">
+      <c r="E8" s="107">
         <f t="shared" si="2"/>
         <v>1129</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G8" s="108">
+      <c r="G8" s="106">
         <f t="shared" si="0"/>
         <v>0.57631444614599281</v>
       </c>
@@ -35844,24 +35874,24 @@
       <c r="A9" s="20">
         <v>41852</v>
       </c>
-      <c r="B9" s="109">
+      <c r="B9" s="107">
         <v>1868</v>
       </c>
-      <c r="C9" s="109">
+      <c r="C9" s="107">
         <f t="shared" si="1"/>
         <v>-91</v>
       </c>
-      <c r="D9" s="109">
+      <c r="D9" s="107">
         <v>906</v>
       </c>
-      <c r="E9" s="109">
+      <c r="E9" s="107">
         <f t="shared" si="2"/>
         <v>962</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="108">
+      <c r="G9" s="106">
         <f t="shared" si="0"/>
         <v>0.51498929336188437</v>
       </c>
@@ -35870,24 +35900,24 @@
       <c r="A10" s="20">
         <v>41883</v>
       </c>
-      <c r="B10" s="109">
+      <c r="B10" s="107">
         <v>1162</v>
       </c>
-      <c r="C10" s="109">
+      <c r="C10" s="107">
         <f t="shared" si="1"/>
         <v>-706</v>
       </c>
-      <c r="D10" s="109">
+      <c r="D10" s="107">
         <v>606</v>
       </c>
-      <c r="E10" s="109">
+      <c r="E10" s="107">
         <f t="shared" si="2"/>
         <v>556</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>3517</v>
       </c>
-      <c r="G10" s="108">
+      <c r="G10" s="106">
         <f t="shared" si="0"/>
         <v>0.47848537005163511</v>
       </c>
@@ -35896,24 +35926,24 @@
       <c r="A11" s="20">
         <v>41913</v>
       </c>
-      <c r="B11" s="109">
+      <c r="B11" s="107">
         <v>1424</v>
       </c>
-      <c r="C11" s="109">
+      <c r="C11" s="107">
         <f t="shared" si="1"/>
         <v>262</v>
       </c>
-      <c r="D11" s="109">
+      <c r="D11" s="107">
         <v>943</v>
       </c>
-      <c r="E11" s="109">
+      <c r="E11" s="107">
         <f t="shared" si="2"/>
         <v>481</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>3517</v>
       </c>
-      <c r="G11" s="108">
+      <c r="G11" s="106">
         <f t="shared" si="0"/>
         <v>0.3377808988764045</v>
       </c>
@@ -35922,24 +35952,24 @@
       <c r="A12" s="20">
         <v>41944</v>
       </c>
-      <c r="B12" s="109">
+      <c r="B12" s="107">
         <v>1232</v>
       </c>
-      <c r="C12" s="109">
+      <c r="C12" s="107">
         <f t="shared" si="1"/>
         <v>-192</v>
       </c>
-      <c r="D12" s="109">
+      <c r="D12" s="107">
         <v>801</v>
       </c>
-      <c r="E12" s="109">
+      <c r="E12" s="107">
         <f t="shared" si="2"/>
         <v>431</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G12" s="108">
+      <c r="G12" s="106">
         <f t="shared" si="0"/>
         <v>0.34983766233766234</v>
       </c>
@@ -35948,24 +35978,24 @@
       <c r="A13" s="20">
         <v>41974</v>
       </c>
-      <c r="B13" s="109">
+      <c r="B13" s="107">
         <v>1738</v>
       </c>
-      <c r="C13" s="109">
+      <c r="C13" s="107">
         <f t="shared" si="1"/>
         <v>506</v>
       </c>
-      <c r="D13" s="109">
+      <c r="D13" s="107">
         <v>786</v>
       </c>
-      <c r="E13" s="109">
+      <c r="E13" s="107">
         <f t="shared" si="2"/>
         <v>952</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G13" s="108">
+      <c r="G13" s="106">
         <f t="shared" si="0"/>
         <v>0.54775604142692746</v>
       </c>
@@ -35974,24 +36004,24 @@
       <c r="A14" s="20">
         <v>42005</v>
       </c>
-      <c r="B14" s="109">
+      <c r="B14" s="107">
         <v>1435</v>
       </c>
-      <c r="C14" s="109">
+      <c r="C14" s="107">
         <f t="shared" si="1"/>
         <v>-303</v>
       </c>
-      <c r="D14" s="109">
+      <c r="D14" s="107">
         <v>575</v>
       </c>
-      <c r="E14" s="109">
+      <c r="E14" s="107">
         <f t="shared" si="2"/>
         <v>860</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G14" s="108">
+      <c r="G14" s="106">
         <f t="shared" si="0"/>
         <v>0.5993031358885017</v>
       </c>
@@ -36000,24 +36030,24 @@
       <c r="A15" s="20">
         <v>42036</v>
       </c>
-      <c r="B15" s="109">
+      <c r="B15" s="107">
         <v>1865</v>
       </c>
-      <c r="C15" s="109">
+      <c r="C15" s="107">
         <f t="shared" si="1"/>
         <v>430</v>
       </c>
-      <c r="D15" s="109">
+      <c r="D15" s="107">
         <v>754</v>
       </c>
-      <c r="E15" s="109">
+      <c r="E15" s="107">
         <f t="shared" si="2"/>
         <v>1111</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G15" s="108">
+      <c r="G15" s="106">
         <f t="shared" si="0"/>
         <v>0.59571045576407511</v>
       </c>
@@ -36026,24 +36056,24 @@
       <c r="A16" s="20">
         <v>42064</v>
       </c>
-      <c r="B16" s="109">
+      <c r="B16" s="107">
         <v>1234</v>
       </c>
-      <c r="C16" s="109">
+      <c r="C16" s="107">
         <f t="shared" si="1"/>
         <v>-631</v>
       </c>
-      <c r="D16" s="109">
+      <c r="D16" s="107">
         <v>599</v>
       </c>
-      <c r="E16" s="109">
+      <c r="E16" s="107">
         <f t="shared" si="2"/>
         <v>635</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G16" s="108">
+      <c r="G16" s="106">
         <f t="shared" si="0"/>
         <v>0.51458670988654787</v>
       </c>
@@ -36052,24 +36082,24 @@
       <c r="A17" s="20">
         <v>42095</v>
       </c>
-      <c r="B17" s="109">
+      <c r="B17" s="107">
         <v>1577</v>
       </c>
-      <c r="C17" s="109">
+      <c r="C17" s="107">
         <f t="shared" si="1"/>
         <v>343</v>
       </c>
-      <c r="D17" s="109">
+      <c r="D17" s="107">
         <v>940</v>
       </c>
-      <c r="E17" s="109">
+      <c r="E17" s="107">
         <f t="shared" si="2"/>
         <v>637</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G17" s="108">
+      <c r="G17" s="106">
         <f t="shared" si="0"/>
         <v>0.40393151553582751</v>
       </c>
@@ -36078,24 +36108,24 @@
       <c r="A18" s="20">
         <v>42125</v>
       </c>
-      <c r="B18" s="109">
+      <c r="B18" s="107">
         <v>1983</v>
       </c>
-      <c r="C18" s="109">
+      <c r="C18" s="107">
         <f t="shared" si="1"/>
         <v>406</v>
       </c>
-      <c r="D18" s="109">
+      <c r="D18" s="107">
         <v>954</v>
       </c>
-      <c r="E18" s="109">
+      <c r="E18" s="107">
         <f t="shared" si="2"/>
         <v>1029</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G18" s="108">
+      <c r="G18" s="106">
         <f t="shared" si="0"/>
         <v>0.51891074130105896</v>
       </c>
@@ -36104,24 +36134,24 @@
       <c r="A19" s="20">
         <v>42156</v>
       </c>
-      <c r="B19" s="109">
+      <c r="B19" s="107">
         <v>1356</v>
       </c>
-      <c r="C19" s="109">
+      <c r="C19" s="107">
         <f t="shared" si="1"/>
         <v>-627</v>
       </c>
-      <c r="D19" s="109">
+      <c r="D19" s="107">
         <v>577</v>
       </c>
-      <c r="E19" s="109">
+      <c r="E19" s="107">
         <f t="shared" si="2"/>
         <v>779</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>3517</v>
       </c>
-      <c r="G19" s="108">
+      <c r="G19" s="106">
         <f t="shared" si="0"/>
         <v>0.57448377581120946</v>
       </c>
@@ -36130,23 +36160,23 @@
       <c r="A20" s="20">
         <v>42186</v>
       </c>
-      <c r="B20" s="109">
+      <c r="B20" s="107">
         <v>1874</v>
       </c>
-      <c r="C20" s="109">
+      <c r="C20" s="107">
         <f t="shared" si="1"/>
         <v>518</v>
       </c>
-      <c r="D20" s="109">
+      <c r="D20" s="107">
         <v>865</v>
       </c>
-      <c r="E20" s="109">
+      <c r="E20" s="107">
         <v>883</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="108">
+      <c r="G20" s="106">
         <f t="shared" si="0"/>
         <v>0.47118463180362863</v>
       </c>
@@ -36155,24 +36185,24 @@
       <c r="A21" s="20">
         <v>42217</v>
       </c>
-      <c r="B21" s="109">
+      <c r="B21" s="107">
         <v>1479</v>
       </c>
-      <c r="C21" s="109">
+      <c r="C21" s="107">
         <f t="shared" si="1"/>
         <v>-395</v>
       </c>
-      <c r="D21" s="109">
+      <c r="D21" s="107">
         <v>588</v>
       </c>
-      <c r="E21" s="109">
+      <c r="E21" s="107">
         <f>B21-D21</f>
         <v>891</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="108">
+      <c r="G21" s="106">
         <f t="shared" si="0"/>
         <v>0.60243407707910746</v>
       </c>
@@ -36181,23 +36211,23 @@
       <c r="A22" s="20">
         <v>42248</v>
       </c>
-      <c r="B22" s="109">
+      <c r="B22" s="107">
         <v>1943</v>
       </c>
-      <c r="C22" s="109">
+      <c r="C22" s="107">
         <f t="shared" si="1"/>
         <v>464</v>
       </c>
-      <c r="D22" s="109">
+      <c r="D22" s="107">
         <v>785</v>
       </c>
-      <c r="E22" s="109">
+      <c r="E22" s="107">
         <v>712</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G22" s="108">
+      <c r="G22" s="106">
         <f t="shared" si="0"/>
         <v>0.36644364384971695</v>
       </c>
@@ -36206,24 +36236,24 @@
       <c r="A23" s="20">
         <v>42278</v>
       </c>
-      <c r="B23" s="109">
+      <c r="B23" s="107">
         <v>1444</v>
       </c>
-      <c r="C23" s="109">
+      <c r="C23" s="107">
         <f t="shared" si="1"/>
         <v>-499</v>
       </c>
-      <c r="D23" s="109">
+      <c r="D23" s="107">
         <v>657</v>
       </c>
-      <c r="E23" s="109">
+      <c r="E23" s="107">
         <f>B23-D23</f>
         <v>787</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G23" s="108">
+      <c r="G23" s="106">
         <f t="shared" si="0"/>
         <v>0.54501385041551242</v>
       </c>
@@ -36232,24 +36262,24 @@
       <c r="A24" s="20">
         <v>42309</v>
       </c>
-      <c r="B24" s="109">
+      <c r="B24" s="107">
         <v>1493</v>
       </c>
-      <c r="C24" s="109">
+      <c r="C24" s="107">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="D24" s="109">
+      <c r="D24" s="107">
         <v>880</v>
       </c>
-      <c r="E24" s="109">
+      <c r="E24" s="107">
         <f>B24-D24</f>
         <v>613</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>3517</v>
       </c>
-      <c r="G24" s="108">
+      <c r="G24" s="106">
         <f t="shared" si="0"/>
         <v>0.4105827193569993</v>
       </c>
@@ -36258,24 +36288,24 @@
       <c r="A25" s="20">
         <v>42339</v>
       </c>
-      <c r="B25" s="109">
+      <c r="B25" s="107">
         <v>1738</v>
       </c>
-      <c r="C25" s="109">
+      <c r="C25" s="107">
         <f t="shared" si="1"/>
         <v>245</v>
       </c>
-      <c r="D25" s="109">
+      <c r="D25" s="107">
         <v>580</v>
       </c>
-      <c r="E25" s="109">
+      <c r="E25" s="107">
         <f>B25-D25</f>
         <v>1158</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G25" s="108">
+      <c r="G25" s="106">
         <f t="shared" si="0"/>
         <v>0.66628308400460301</v>
       </c>
@@ -36350,78 +36380,78 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="104" t="s">
         <v>3546</v>
       </c>
-      <c r="C2" s="107">
+      <c r="C2" s="105">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="104" t="s">
         <v>3545</v>
       </c>
-      <c r="C3" s="110">
+      <c r="C3" s="108">
         <f>TIME(10,38,45)</f>
         <v>0.4435763888888889</v>
       </c>
-      <c r="E3" s="106" t="s">
+      <c r="E3" s="104" t="s">
         <v>3544</v>
       </c>
-      <c r="F3" s="107">
+      <c r="F3" s="105">
         <f>DATE(2027,9,26)</f>
         <v>46656</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="106"/>
+      <c r="B4" s="104"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="9" t="s">
         <v>3543</v>
       </c>
-      <c r="C5" s="111">
+      <c r="C5" s="109">
         <f ca="1">YEAR(C2)</f>
         <v>2026</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>3542</v>
       </c>
-      <c r="F5" s="111">
+      <c r="F5" s="109">
         <f ca="1">F3-C2</f>
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="9" t="s">
         <v>3541</v>
       </c>
-      <c r="C6" s="104">
+      <c r="C6" s="102">
         <f ca="1">MONTH(TODAY())</f>
         <v>10</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>3540</v>
       </c>
-      <c r="F6" s="104">
+      <c r="F6" s="102">
         <f ca="1">NETWORKDAYS(C2,F3)</f>
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="9" t="s">
         <v>3539</v>
       </c>
-      <c r="C7" s="104">
+      <c r="C7" s="102">
         <f ca="1">DAY(TODAY())</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>3538</v>
       </c>
-      <c r="F7" s="105" t="str">
+      <c r="F7" s="103" t="str">
         <f>TEXT(F3,"dddd")</f>
         <v>Sunday</v>
       </c>
@@ -36431,7 +36461,7 @@
       <c r="B8" s="9" t="s">
         <v>3537</v>
       </c>
-      <c r="C8" s="104">
+      <c r="C8" s="102">
         <f>HOUR(C3)</f>
         <v>10</v>
       </c>
@@ -36440,14 +36470,14 @@
       <c r="B9" s="9" t="s">
         <v>3536</v>
       </c>
-      <c r="C9" s="104">
+      <c r="C9" s="102">
         <f>MINUTE(C3)</f>
         <v>38</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>3535</v>
       </c>
-      <c r="F9" s="104">
+      <c r="F9" s="102">
         <f ca="1">DATEDIF(C2,F3,"m")</f>
         <v>11</v>
       </c>
@@ -36456,36 +36486,36 @@
       <c r="B10" s="9" t="s">
         <v>3534</v>
       </c>
-      <c r="C10" s="103">
+      <c r="C10" s="101">
         <f>SECOND(C3)</f>
         <v>45</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>3533</v>
       </c>
-      <c r="F10" s="103">
+      <c r="F10" s="101">
         <f ca="1">DATEDIF(C2,F3,"y")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="102"/>
+      <c r="B11" s="100"/>
     </row>
     <row r="12" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="9" t="s">
         <v>3532</v>
       </c>
-      <c r="C12" s="101">
+      <c r="C12" s="99">
         <f>DATE(2026,9,30)</f>
         <v>46295</v>
       </c>
-      <c r="G12" s="100"/>
+      <c r="G12" s="98"/>
     </row>
     <row r="13" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="9" t="s">
         <v>3531</v>
       </c>
-      <c r="C13" s="99">
+      <c r="C13" s="97">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
@@ -36494,7 +36524,7 @@
       <c r="B14" s="9" t="s">
         <v>3530</v>
       </c>
-      <c r="C14" s="99">
+      <c r="C14" s="97">
         <f>DATE(2026,1,1)</f>
         <v>46023</v>
       </c>
@@ -36509,9 +36539,9 @@
       <c r="B16" s="9" t="s">
         <v>3529</v>
       </c>
-      <c r="C16" s="112">
+      <c r="C16" s="110">
         <f ca="1">DATEDIF(E15,TODAY(),"YD")/365*100</f>
-        <v>75.06849315068493</v>
+        <v>76.438356164383563</v>
       </c>
     </row>
   </sheetData>
@@ -36571,7 +36601,7 @@
         <f>DATE(26,7,10)</f>
         <v>9688</v>
       </c>
-      <c r="C5" s="129">
+      <c r="C5" s="111">
         <f>DATEDIF(B5,$C$1,"YD")</f>
         <v>10</v>
       </c>
@@ -36584,7 +36614,7 @@
         <f>DATE(26,7,5)</f>
         <v>9683</v>
       </c>
-      <c r="C6" s="129">
+      <c r="C6" s="111">
         <f t="shared" ref="C6:C9" si="0">DATEDIF(B6,$C$1,"YD")</f>
         <v>15</v>
       </c>
@@ -36597,7 +36627,7 @@
         <f>DATE(26,6,8)</f>
         <v>9656</v>
       </c>
-      <c r="C7" s="129">
+      <c r="C7" s="111">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
@@ -36610,7 +36640,7 @@
         <f>DATE(26,6,5)</f>
         <v>9653</v>
       </c>
-      <c r="C8" s="129">
+      <c r="C8" s="111">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
@@ -36623,7 +36653,7 @@
         <f>DATE(26,7,17)</f>
         <v>9695</v>
       </c>
-      <c r="C9" s="129">
+      <c r="C9" s="111">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -36682,8 +36712,8 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="92" customWidth="1"/>
-    <col min="2" max="16384" width="8.77734375" style="92"/>
+    <col min="1" max="1" width="11.21875" style="90" customWidth="1"/>
+    <col min="2" max="16384" width="8.77734375" style="90"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -36696,107 +36726,107 @@
       <c r="E1" s="128"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="94" t="s">
         <v>3512</v>
       </c>
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="93" t="s">
         <v>3511</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C3" s="93" t="s">
         <v>3510</v>
       </c>
-      <c r="D3" s="95" t="s">
+      <c r="D3" s="93" t="s">
         <v>3509</v>
       </c>
-      <c r="E3" s="95" t="s">
+      <c r="E3" s="93" t="s">
         <v>3508</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="90" t="s">
         <v>3487</v>
       </c>
-      <c r="B4" s="92">
+      <c r="B4" s="90">
         <v>200</v>
       </c>
-      <c r="C4" s="92">
+      <c r="C4" s="90">
         <v>800</v>
       </c>
-      <c r="D4" s="92">
+      <c r="D4" s="90">
         <v>900</v>
       </c>
-      <c r="E4" s="92">
+      <c r="E4" s="90">
         <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="90" t="s">
         <v>3507</v>
       </c>
-      <c r="B5" s="92">
+      <c r="B5" s="90">
         <v>400</v>
       </c>
-      <c r="C5" s="92">
+      <c r="C5" s="90">
         <v>100</v>
       </c>
-      <c r="D5" s="92">
+      <c r="D5" s="90">
         <v>800</v>
       </c>
-      <c r="E5" s="92">
+      <c r="E5" s="90">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="90" t="s">
         <v>3489</v>
       </c>
-      <c r="B6" s="92">
+      <c r="B6" s="90">
         <v>200</v>
       </c>
-      <c r="C6" s="92">
+      <c r="C6" s="90">
         <v>500</v>
       </c>
-      <c r="D6" s="92">
+      <c r="D6" s="90">
         <v>500</v>
       </c>
-      <c r="E6" s="92">
+      <c r="E6" s="90">
         <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="90" t="s">
         <v>3506</v>
       </c>
-      <c r="B7" s="92">
+      <c r="B7" s="90">
         <v>200</v>
       </c>
-      <c r="C7" s="92">
+      <c r="C7" s="90">
         <v>300</v>
       </c>
-      <c r="D7" s="92">
+      <c r="D7" s="90">
         <v>500</v>
       </c>
-      <c r="E7" s="92">
+      <c r="E7" s="90">
         <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="94" t="s">
+      <c r="A9" s="92" t="s">
         <v>3505</v>
       </c>
-      <c r="B9" s="93">
+      <c r="B9" s="91">
         <f>SUM(B4:B7)</f>
         <v>1000</v>
       </c>
-      <c r="C9" s="93">
+      <c r="C9" s="91">
         <f>SUM(C4:C7)</f>
         <v>1700</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="91">
         <f>SUM(D4:D7)</f>
         <v>2700</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="91">
         <f>SUM(E4:E7)</f>
         <v>1100</v>
       </c>
@@ -37226,8 +37256,8 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="92" customWidth="1"/>
-    <col min="2" max="16384" width="8.77734375" style="92"/>
+    <col min="1" max="1" width="11.21875" style="90" customWidth="1"/>
+    <col min="2" max="16384" width="8.77734375" style="90"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -37240,107 +37270,107 @@
       <c r="E1" s="128"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="94" t="s">
         <v>3512</v>
       </c>
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="93" t="s">
         <v>3511</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C3" s="93" t="s">
         <v>3510</v>
       </c>
-      <c r="D3" s="95" t="s">
+      <c r="D3" s="93" t="s">
         <v>3509</v>
       </c>
-      <c r="E3" s="95" t="s">
+      <c r="E3" s="93" t="s">
         <v>3508</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="90" t="s">
         <v>3487</v>
       </c>
-      <c r="B4" s="92">
+      <c r="B4" s="90">
         <v>400</v>
       </c>
-      <c r="C4" s="92">
+      <c r="C4" s="90">
         <v>800</v>
       </c>
-      <c r="D4" s="92">
+      <c r="D4" s="90">
         <v>900</v>
       </c>
-      <c r="E4" s="92">
+      <c r="E4" s="90">
         <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="90" t="s">
         <v>3507</v>
       </c>
-      <c r="B5" s="92">
+      <c r="B5" s="90">
         <v>200</v>
       </c>
-      <c r="C5" s="92">
+      <c r="C5" s="90">
         <v>500</v>
       </c>
-      <c r="D5" s="92">
+      <c r="D5" s="90">
         <v>1200</v>
       </c>
-      <c r="E5" s="92">
+      <c r="E5" s="90">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="90" t="s">
         <v>3489</v>
       </c>
-      <c r="B6" s="92">
+      <c r="B6" s="90">
         <v>300</v>
       </c>
-      <c r="C6" s="92">
+      <c r="C6" s="90">
         <v>400</v>
       </c>
-      <c r="D6" s="92">
+      <c r="D6" s="90">
         <v>1400</v>
       </c>
-      <c r="E6" s="92">
+      <c r="E6" s="90">
         <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="90" t="s">
         <v>3506</v>
       </c>
-      <c r="B7" s="92">
+      <c r="B7" s="90">
         <v>100</v>
       </c>
-      <c r="C7" s="92">
+      <c r="C7" s="90">
         <v>300</v>
       </c>
-      <c r="D7" s="92">
+      <c r="D7" s="90">
         <v>500</v>
       </c>
-      <c r="E7" s="92">
+      <c r="E7" s="90">
         <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="94" t="s">
+      <c r="A9" s="92" t="s">
         <v>3505</v>
       </c>
-      <c r="B9" s="93">
+      <c r="B9" s="91">
         <f>SUM(B4:B7)</f>
         <v>1000</v>
       </c>
-      <c r="C9" s="93">
+      <c r="C9" s="91">
         <f>SUM(C4:C7)</f>
         <v>2000</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="91">
         <f>SUM(D4:D7)</f>
         <v>4000</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="91">
         <f>SUM(E4:E7)</f>
         <v>1000</v>
       </c>
@@ -37371,8 +37401,8 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="92" customWidth="1"/>
-    <col min="2" max="16384" width="8.77734375" style="92"/>
+    <col min="1" max="1" width="11.21875" style="90" customWidth="1"/>
+    <col min="2" max="16384" width="8.77734375" style="90"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -37385,107 +37415,107 @@
       <c r="E1" s="128"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="94" t="s">
         <v>3512</v>
       </c>
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="93" t="s">
         <v>3511</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C3" s="93" t="s">
         <v>3510</v>
       </c>
-      <c r="D3" s="95" t="s">
+      <c r="D3" s="93" t="s">
         <v>3509</v>
       </c>
-      <c r="E3" s="95" t="s">
+      <c r="E3" s="93" t="s">
         <v>3508</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="90" t="s">
         <v>3487</v>
       </c>
-      <c r="B4" s="92">
+      <c r="B4" s="90">
         <v>200</v>
       </c>
-      <c r="C4" s="92">
+      <c r="C4" s="90">
         <v>600</v>
       </c>
-      <c r="D4" s="92">
+      <c r="D4" s="90">
         <v>700</v>
       </c>
-      <c r="E4" s="92">
+      <c r="E4" s="90">
         <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="90" t="s">
         <v>3507</v>
       </c>
-      <c r="B5" s="92">
+      <c r="B5" s="90">
         <v>300</v>
       </c>
-      <c r="C5" s="92">
+      <c r="C5" s="90">
         <v>200</v>
       </c>
-      <c r="D5" s="92">
+      <c r="D5" s="90">
         <v>500</v>
       </c>
-      <c r="E5" s="92">
+      <c r="E5" s="90">
         <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="90" t="s">
         <v>3489</v>
       </c>
-      <c r="B6" s="92">
+      <c r="B6" s="90">
         <v>200</v>
       </c>
-      <c r="C6" s="92">
+      <c r="C6" s="90">
         <v>400</v>
       </c>
-      <c r="D6" s="92">
+      <c r="D6" s="90">
         <v>500</v>
       </c>
-      <c r="E6" s="92">
+      <c r="E6" s="90">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="90" t="s">
         <v>3506</v>
       </c>
-      <c r="B7" s="92">
+      <c r="B7" s="90">
         <v>300</v>
       </c>
-      <c r="C7" s="92">
+      <c r="C7" s="90">
         <v>300</v>
       </c>
-      <c r="D7" s="92">
+      <c r="D7" s="90">
         <v>100</v>
       </c>
-      <c r="E7" s="92">
+      <c r="E7" s="90">
         <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="94" t="s">
+      <c r="A9" s="92" t="s">
         <v>3505</v>
       </c>
-      <c r="B9" s="93">
+      <c r="B9" s="91">
         <f>SUM(B4:B7)</f>
         <v>1000</v>
       </c>
-      <c r="C9" s="93">
+      <c r="C9" s="91">
         <f>SUM(C4:C7)</f>
         <v>1500</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="91">
         <f>SUM(D4:D7)</f>
         <v>1800</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="91">
         <f>SUM(E4:E7)</f>
         <v>1300</v>
       </c>
@@ -37510,8 +37540,8 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="92" customWidth="1"/>
-    <col min="2" max="16384" width="8.77734375" style="92"/>
+    <col min="1" max="1" width="11.21875" style="90" customWidth="1"/>
+    <col min="2" max="16384" width="8.77734375" style="90"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -37522,97 +37552,97 @@
       <c r="E1" s="128"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="96"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95" t="s">
+      <c r="A3" s="94"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93" t="s">
         <v>3510</v>
       </c>
-      <c r="D3" s="95" t="s">
+      <c r="D3" s="93" t="s">
         <v>3509</v>
       </c>
-      <c r="E3" s="95" t="s">
+      <c r="E3" s="93" t="s">
         <v>3508</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="92">
+      <c r="B4" s="90">
         <v>400</v>
       </c>
-      <c r="C4" s="92">
+      <c r="C4" s="90">
         <v>800</v>
       </c>
-      <c r="D4" s="92">
+      <c r="D4" s="90">
         <v>900</v>
       </c>
-      <c r="E4" s="92">
+      <c r="E4" s="90">
         <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="92">
+      <c r="B5" s="90">
         <v>200</v>
       </c>
-      <c r="C5" s="92">
+      <c r="C5" s="90">
         <v>1500</v>
       </c>
-      <c r="D5" s="92">
+      <c r="D5" s="90">
         <v>2400</v>
       </c>
-      <c r="E5" s="92">
+      <c r="E5" s="90">
         <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="92">
+      <c r="B6" s="90">
         <v>300</v>
       </c>
-      <c r="C6" s="92">
+      <c r="C6" s="90">
         <v>900</v>
       </c>
-      <c r="D6" s="92">
+      <c r="D6" s="90">
         <v>2000</v>
       </c>
-      <c r="E6" s="92">
+      <c r="E6" s="90">
         <v>1100</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="92">
+      <c r="B7" s="90">
         <v>100</v>
       </c>
-      <c r="C7" s="92">
+      <c r="C7" s="90">
         <v>300</v>
       </c>
-      <c r="D7" s="92">
+      <c r="D7" s="90">
         <v>500</v>
       </c>
-      <c r="E7" s="92">
+      <c r="E7" s="90">
         <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="92">
+      <c r="B8" s="90">
         <v>1000</v>
       </c>
-      <c r="C8" s="130">
+      <c r="C8" s="112">
         <v>3500</v>
       </c>
-      <c r="D8" s="130">
+      <c r="D8" s="112">
         <v>5800</v>
       </c>
-      <c r="E8" s="130">
+      <c r="E8" s="112">
         <v>2300</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="94"/>
-      <c r="B9" s="93"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
     </row>
   </sheetData>
-  <dataConsolidate leftLabels="1" topLabels="1">
+  <dataConsolidate topLabels="1">
     <dataRefs count="2">
       <dataRef ref="B3:E9" sheet="Maine"/>
       <dataRef ref="B3:E9" sheet="New Hampshire"/>
@@ -37970,8 +38000,8 @@
   <cols>
     <col min="1" max="1" width="1.21875" style="49" customWidth="1"/>
     <col min="2" max="2" width="9.44140625" style="49" customWidth="1"/>
-    <col min="3" max="3" width="18.77734375" style="67" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="67" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" style="65" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="65" customWidth="1"/>
     <col min="5" max="6" width="14.44140625" style="49" customWidth="1"/>
     <col min="7" max="7" width="16.21875" style="49" customWidth="1"/>
     <col min="8" max="8" width="3.44140625" style="49" customWidth="1"/>
@@ -37994,1125 +38024,1125 @@
       <c r="G2" s="115"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="89" t="s">
         <v>3500</v>
       </c>
-      <c r="C4" s="91" t="s">
+      <c r="C4" s="89" t="s">
         <v>3496</v>
       </c>
-      <c r="D4" s="91" t="s">
+      <c r="D4" s="89" t="s">
         <v>3503</v>
       </c>
-      <c r="E4" s="91" t="s">
+      <c r="E4" s="89" t="s">
         <v>3502</v>
       </c>
-      <c r="F4" s="91" t="s">
+      <c r="F4" s="89" t="s">
         <v>3501</v>
       </c>
-      <c r="G4" s="90" t="s">
+      <c r="G4" s="88" t="s">
         <v>3499</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="59"/>
-      <c r="B5" s="86" t="s">
+      <c r="B5" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C5" s="82" t="s">
+      <c r="C5" s="80" t="s">
         <v>3491</v>
       </c>
-      <c r="D5" s="81">
+      <c r="D5" s="79">
         <v>800</v>
       </c>
-      <c r="E5" s="81">
+      <c r="E5" s="79">
         <v>650</v>
       </c>
-      <c r="F5" s="81">
+      <c r="F5" s="79">
         <v>700</v>
       </c>
-      <c r="G5" s="80"/>
+      <c r="G5" s="78"/>
     </row>
     <row r="6" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="59"/>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C6" s="82" t="s">
+      <c r="C6" s="80" t="s">
         <v>3312</v>
       </c>
-      <c r="D6" s="81">
+      <c r="D6" s="79">
         <v>900</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="79">
         <v>850</v>
       </c>
-      <c r="F6" s="81">
+      <c r="F6" s="79">
         <v>850</v>
       </c>
-      <c r="G6" s="80"/>
-      <c r="J6" s="89"/>
-      <c r="K6" s="89"/>
-      <c r="L6" s="87"/>
+      <c r="G6" s="78"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="85"/>
     </row>
     <row r="7" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="59"/>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C7" s="82" t="s">
+      <c r="C7" s="80" t="s">
         <v>3485</v>
       </c>
-      <c r="D7" s="81">
+      <c r="D7" s="79">
         <v>4850</v>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="79">
         <v>3200</v>
       </c>
-      <c r="F7" s="81">
+      <c r="F7" s="79">
         <v>1155</v>
       </c>
-      <c r="G7" s="80"/>
-      <c r="I7" s="85" t="s">
+      <c r="G7" s="78"/>
+      <c r="I7" s="83" t="s">
         <v>3500</v>
       </c>
-      <c r="J7" s="85" t="s">
+      <c r="J7" s="83" t="s">
         <v>3496</v>
       </c>
-      <c r="K7" s="85" t="s">
+      <c r="K7" s="83" t="s">
         <v>3499</v>
       </c>
-      <c r="L7" s="87"/>
+      <c r="L7" s="85"/>
     </row>
     <row r="8" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="59"/>
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C8" s="82" t="s">
+      <c r="C8" s="80" t="s">
         <v>3492</v>
       </c>
-      <c r="D8" s="81">
+      <c r="D8" s="79">
         <v>1250</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="79">
         <v>1250</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="79">
         <v>1250</v>
       </c>
-      <c r="G8" s="80"/>
-      <c r="I8" s="84" t="s">
+      <c r="G8" s="78"/>
+      <c r="I8" s="82" t="s">
         <v>3497</v>
       </c>
-      <c r="J8" s="84" t="s">
+      <c r="J8" s="82" t="s">
         <v>3487</v>
       </c>
-      <c r="K8" s="88"/>
-      <c r="L8" s="87"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="85"/>
     </row>
     <row r="9" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="59"/>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C9" s="82" t="s">
+      <c r="C9" s="80" t="s">
         <v>3487</v>
       </c>
-      <c r="D9" s="81">
+      <c r="D9" s="79">
         <v>2025</v>
       </c>
-      <c r="E9" s="81">
+      <c r="E9" s="79">
         <v>2200</v>
       </c>
-      <c r="F9" s="81">
+      <c r="F9" s="79">
         <v>1650</v>
       </c>
-      <c r="G9" s="80"/>
-      <c r="L9" s="87"/>
+      <c r="G9" s="78"/>
+      <c r="L9" s="85"/>
     </row>
     <row r="10" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="59"/>
-      <c r="B10" s="86" t="s">
+      <c r="B10" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C10" s="82" t="s">
+      <c r="C10" s="80" t="s">
         <v>3489</v>
       </c>
-      <c r="D10" s="81">
+      <c r="D10" s="79">
         <v>1350</v>
       </c>
-      <c r="E10" s="81">
+      <c r="E10" s="79">
         <v>1500</v>
       </c>
-      <c r="F10" s="81">
+      <c r="F10" s="79">
         <v>1700</v>
       </c>
-      <c r="G10" s="80"/>
+      <c r="G10" s="78"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="59"/>
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="80" t="s">
         <v>3490</v>
       </c>
-      <c r="D11" s="81">
+      <c r="D11" s="79">
         <v>3300</v>
       </c>
-      <c r="E11" s="81">
+      <c r="E11" s="79">
         <v>3500</v>
       </c>
-      <c r="F11" s="81">
+      <c r="F11" s="79">
         <v>3700</v>
       </c>
-      <c r="G11" s="80"/>
+      <c r="G11" s="78"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="59"/>
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C12" s="82" t="s">
+      <c r="C12" s="80" t="s">
         <v>3486</v>
       </c>
-      <c r="D12" s="81">
+      <c r="D12" s="79">
         <v>3825</v>
       </c>
-      <c r="E12" s="81">
+      <c r="E12" s="79">
         <v>3725</v>
       </c>
-      <c r="F12" s="81">
+      <c r="F12" s="79">
         <v>3750</v>
       </c>
-      <c r="G12" s="80"/>
+      <c r="G12" s="78"/>
     </row>
     <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="59"/>
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C13" s="82" t="s">
+      <c r="C13" s="80" t="s">
         <v>3488</v>
       </c>
-      <c r="D13" s="81">
+      <c r="D13" s="79">
         <v>8900</v>
       </c>
-      <c r="E13" s="81">
+      <c r="E13" s="79">
         <v>10315</v>
       </c>
-      <c r="F13" s="81">
+      <c r="F13" s="79">
         <v>5250</v>
       </c>
-      <c r="G13" s="80"/>
-      <c r="I13" s="85" t="s">
+      <c r="G13" s="78"/>
+      <c r="I13" s="83" t="s">
         <v>3496</v>
       </c>
-      <c r="J13" s="85" t="s">
+      <c r="J13" s="83" t="s">
         <v>3498</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="59"/>
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C14" s="82" t="s">
+      <c r="C14" s="80" t="s">
         <v>3483</v>
       </c>
-      <c r="D14" s="81">
+      <c r="D14" s="79">
         <v>6250</v>
       </c>
-      <c r="E14" s="81">
+      <c r="E14" s="79">
         <v>6000</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="79">
         <v>6500</v>
       </c>
-      <c r="G14" s="80"/>
-      <c r="I14" s="84" t="s">
+      <c r="G14" s="78"/>
+      <c r="I14" s="82" t="s">
         <v>3487</v>
       </c>
-      <c r="J14" s="83"/>
+      <c r="J14" s="81"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="59"/>
-      <c r="B15" s="86" t="s">
+      <c r="B15" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C15" s="82" t="s">
+      <c r="C15" s="80" t="s">
         <v>3484</v>
       </c>
-      <c r="D15" s="81">
+      <c r="D15" s="79">
         <v>8000</v>
       </c>
-      <c r="E15" s="81">
+      <c r="E15" s="79">
         <v>8000</v>
       </c>
-      <c r="F15" s="81">
+      <c r="F15" s="79">
         <v>8000</v>
       </c>
-      <c r="G15" s="80"/>
+      <c r="G15" s="78"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="59"/>
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C16" s="82" t="s">
+      <c r="C16" s="80" t="s">
         <v>3481</v>
       </c>
-      <c r="D16" s="81">
+      <c r="D16" s="79">
         <v>11500</v>
       </c>
-      <c r="E16" s="81">
+      <c r="E16" s="79">
         <v>12500</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="79">
         <v>12500</v>
       </c>
-      <c r="G16" s="80"/>
+      <c r="G16" s="78"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="59"/>
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C17" s="82" t="s">
+      <c r="C17" s="80" t="s">
         <v>3482</v>
       </c>
-      <c r="D17" s="81">
+      <c r="D17" s="79">
         <v>12250</v>
       </c>
-      <c r="E17" s="81">
+      <c r="E17" s="79">
         <v>12250</v>
       </c>
-      <c r="F17" s="81">
+      <c r="F17" s="79">
         <v>12750</v>
       </c>
-      <c r="G17" s="80"/>
+      <c r="G17" s="78"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="59"/>
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="84" t="s">
         <v>3497</v>
       </c>
-      <c r="C18" s="82" t="s">
+      <c r="C18" s="80" t="s">
         <v>3478</v>
       </c>
-      <c r="D18" s="81">
+      <c r="D18" s="79">
         <v>25000</v>
       </c>
-      <c r="E18" s="81">
+      <c r="E18" s="79">
         <v>24000</v>
       </c>
-      <c r="F18" s="81">
+      <c r="F18" s="79">
         <v>26390</v>
       </c>
-      <c r="G18" s="80"/>
+      <c r="G18" s="78"/>
     </row>
     <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="59"/>
-      <c r="B19" s="82" t="s">
+      <c r="B19" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C19" s="82" t="s">
+      <c r="C19" s="80" t="s">
         <v>3491</v>
       </c>
-      <c r="D19" s="81">
+      <c r="D19" s="79">
         <v>800</v>
       </c>
-      <c r="E19" s="81">
+      <c r="E19" s="79">
         <v>950</v>
       </c>
-      <c r="F19" s="81">
+      <c r="F19" s="79">
         <v>750</v>
       </c>
-      <c r="G19" s="80"/>
-      <c r="I19" s="85" t="s">
+      <c r="G19" s="78"/>
+      <c r="I19" s="83" t="s">
         <v>3496</v>
       </c>
-      <c r="J19" s="85" t="s">
+      <c r="J19" s="83" t="s">
         <v>3495</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C20" s="82" t="s">
+      <c r="C20" s="80" t="s">
         <v>3492</v>
       </c>
-      <c r="D20" s="81">
+      <c r="D20" s="79">
         <v>850</v>
       </c>
-      <c r="E20" s="81">
+      <c r="E20" s="79">
         <v>750</v>
       </c>
-      <c r="F20" s="81">
+      <c r="F20" s="79">
         <v>800</v>
       </c>
-      <c r="G20" s="80"/>
-      <c r="I20" s="84" t="s">
+      <c r="G20" s="78"/>
+      <c r="I20" s="82" t="s">
         <v>3484</v>
       </c>
-      <c r="J20" s="83"/>
+      <c r="J20" s="81"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="82" t="s">
+      <c r="B21" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C21" s="82" t="s">
+      <c r="C21" s="80" t="s">
         <v>3489</v>
       </c>
-      <c r="D21" s="81">
+      <c r="D21" s="79">
         <v>940</v>
       </c>
-      <c r="E21" s="81">
+      <c r="E21" s="79">
         <v>950</v>
       </c>
-      <c r="F21" s="81">
+      <c r="F21" s="79">
         <v>820</v>
       </c>
-      <c r="G21" s="80"/>
+      <c r="G21" s="78"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="82" t="s">
+      <c r="B22" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C22" s="82" t="s">
+      <c r="C22" s="80" t="s">
         <v>3312</v>
       </c>
-      <c r="D22" s="81">
+      <c r="D22" s="79">
         <v>980</v>
       </c>
-      <c r="E22" s="81">
+      <c r="E22" s="79">
         <v>850</v>
       </c>
-      <c r="F22" s="81">
+      <c r="F22" s="79">
         <v>950</v>
       </c>
-      <c r="G22" s="80"/>
+      <c r="G22" s="78"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="82" t="s">
+      <c r="B23" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C23" s="82" t="s">
+      <c r="C23" s="80" t="s">
         <v>3488</v>
       </c>
-      <c r="D23" s="81">
+      <c r="D23" s="79">
         <v>1250</v>
       </c>
-      <c r="E23" s="81">
+      <c r="E23" s="79">
         <v>1250</v>
       </c>
-      <c r="F23" s="81">
+      <c r="F23" s="79">
         <v>1250</v>
       </c>
-      <c r="G23" s="80"/>
+      <c r="G23" s="78"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="82" t="s">
+      <c r="B24" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C24" s="82" t="s">
+      <c r="C24" s="80" t="s">
         <v>3487</v>
       </c>
-      <c r="D24" s="81">
+      <c r="D24" s="79">
         <v>1150</v>
       </c>
-      <c r="E24" s="81">
+      <c r="E24" s="79">
         <v>1255</v>
       </c>
-      <c r="F24" s="81">
+      <c r="F24" s="79">
         <v>1400</v>
       </c>
-      <c r="G24" s="80"/>
+      <c r="G24" s="78"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="82" t="s">
+      <c r="B25" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C25" s="82" t="s">
+      <c r="C25" s="80" t="s">
         <v>3490</v>
       </c>
-      <c r="D25" s="81">
+      <c r="D25" s="79">
         <v>2410</v>
       </c>
-      <c r="E25" s="81">
+      <c r="E25" s="79">
         <v>1850</v>
       </c>
-      <c r="F25" s="81">
+      <c r="F25" s="79">
         <v>2390</v>
       </c>
-      <c r="G25" s="80"/>
+      <c r="G25" s="78"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="82" t="s">
+      <c r="B26" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C26" s="82" t="s">
+      <c r="C26" s="80" t="s">
         <v>3486</v>
       </c>
-      <c r="D26" s="81">
+      <c r="D26" s="79">
         <v>3200</v>
       </c>
-      <c r="E26" s="81">
+      <c r="E26" s="79">
         <v>3760</v>
       </c>
-      <c r="F26" s="81">
+      <c r="F26" s="79">
         <v>3750</v>
       </c>
-      <c r="G26" s="80"/>
+      <c r="G26" s="78"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="82" t="s">
+      <c r="B27" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C27" s="82" t="s">
+      <c r="C27" s="80" t="s">
         <v>3485</v>
       </c>
-      <c r="D27" s="81">
+      <c r="D27" s="79">
         <v>5000</v>
       </c>
-      <c r="E27" s="81">
+      <c r="E27" s="79">
         <v>4800</v>
       </c>
-      <c r="F27" s="81">
+      <c r="F27" s="79">
         <v>4500</v>
       </c>
-      <c r="G27" s="80"/>
+      <c r="G27" s="78"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="82" t="s">
+      <c r="B28" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C28" s="82" t="s">
+      <c r="C28" s="80" t="s">
         <v>3483</v>
       </c>
-      <c r="D28" s="81">
+      <c r="D28" s="79">
         <v>5250</v>
       </c>
-      <c r="E28" s="81">
+      <c r="E28" s="79">
         <v>8990</v>
       </c>
-      <c r="F28" s="81">
+      <c r="F28" s="79">
         <v>5515</v>
       </c>
-      <c r="G28" s="80"/>
+      <c r="G28" s="78"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="82" t="s">
+      <c r="B29" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C29" s="82" t="s">
+      <c r="C29" s="80" t="s">
         <v>3484</v>
       </c>
-      <c r="D29" s="81">
+      <c r="D29" s="79">
         <v>6020</v>
       </c>
-      <c r="E29" s="81">
+      <c r="E29" s="79">
         <v>6020</v>
       </c>
-      <c r="F29" s="81">
+      <c r="F29" s="79">
         <v>6020</v>
       </c>
-      <c r="G29" s="80"/>
+      <c r="G29" s="78"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="82" t="s">
+      <c r="B30" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C30" s="82" t="s">
+      <c r="C30" s="80" t="s">
         <v>3481</v>
       </c>
-      <c r="D30" s="81">
+      <c r="D30" s="79">
         <v>12940</v>
       </c>
-      <c r="E30" s="81">
+      <c r="E30" s="79">
         <v>11300</v>
       </c>
-      <c r="F30" s="81">
+      <c r="F30" s="79">
         <v>11500</v>
       </c>
-      <c r="G30" s="80"/>
+      <c r="G30" s="78"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B31" s="82" t="s">
+      <c r="B31" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C31" s="82" t="s">
+      <c r="C31" s="80" t="s">
         <v>3482</v>
       </c>
-      <c r="D31" s="81">
+      <c r="D31" s="79">
         <v>14250</v>
       </c>
-      <c r="E31" s="81">
+      <c r="E31" s="79">
         <v>15250</v>
       </c>
-      <c r="F31" s="81">
+      <c r="F31" s="79">
         <v>12050</v>
       </c>
-      <c r="G31" s="80"/>
+      <c r="G31" s="78"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B32" s="82" t="s">
+      <c r="B32" s="80" t="s">
         <v>3494</v>
       </c>
-      <c r="C32" s="82" t="s">
+      <c r="C32" s="80" t="s">
         <v>3478</v>
       </c>
-      <c r="D32" s="81">
+      <c r="D32" s="79">
         <v>25700</v>
       </c>
-      <c r="E32" s="81">
+      <c r="E32" s="79">
         <v>24200</v>
       </c>
-      <c r="F32" s="81">
+      <c r="F32" s="79">
         <v>26930</v>
       </c>
-      <c r="G32" s="80"/>
+      <c r="G32" s="78"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="82" t="s">
+      <c r="B33" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C33" s="82" t="s">
+      <c r="C33" s="80" t="s">
         <v>3492</v>
       </c>
-      <c r="D33" s="81">
+      <c r="D33" s="79">
         <v>2140</v>
       </c>
-      <c r="E33" s="81">
+      <c r="E33" s="79">
         <v>2310</v>
       </c>
-      <c r="F33" s="81">
+      <c r="F33" s="79">
         <v>2000</v>
       </c>
-      <c r="G33" s="80"/>
+      <c r="G33" s="78"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="82" t="s">
+      <c r="B34" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C34" s="82" t="s">
+      <c r="C34" s="80" t="s">
         <v>3491</v>
       </c>
-      <c r="D34" s="81">
+      <c r="D34" s="79">
         <v>730</v>
       </c>
-      <c r="E34" s="81">
+      <c r="E34" s="79">
         <v>525</v>
       </c>
-      <c r="F34" s="81">
+      <c r="F34" s="79">
         <v>430</v>
       </c>
-      <c r="G34" s="80"/>
+      <c r="G34" s="78"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="82" t="s">
+      <c r="B35" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C35" s="82" t="s">
+      <c r="C35" s="80" t="s">
         <v>3312</v>
       </c>
-      <c r="D35" s="81">
+      <c r="D35" s="79">
         <v>700</v>
       </c>
-      <c r="E35" s="81">
+      <c r="E35" s="79">
         <v>750</v>
       </c>
-      <c r="F35" s="81">
+      <c r="F35" s="79">
         <v>750</v>
       </c>
-      <c r="G35" s="80"/>
+      <c r="G35" s="78"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="82" t="s">
+      <c r="B36" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C36" s="82" t="s">
+      <c r="C36" s="80" t="s">
         <v>3489</v>
       </c>
-      <c r="D36" s="81">
+      <c r="D36" s="79">
         <v>2000</v>
       </c>
-      <c r="E36" s="81">
+      <c r="E36" s="79">
         <v>950</v>
       </c>
-      <c r="F36" s="81">
+      <c r="F36" s="79">
         <v>800</v>
       </c>
-      <c r="G36" s="80"/>
+      <c r="G36" s="78"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="82" t="s">
+      <c r="B37" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C37" s="82" t="s">
+      <c r="C37" s="80" t="s">
         <v>3490</v>
       </c>
-      <c r="D37" s="81">
+      <c r="D37" s="79">
         <v>745</v>
       </c>
-      <c r="E37" s="81">
+      <c r="E37" s="79">
         <v>780</v>
       </c>
-      <c r="F37" s="81">
+      <c r="F37" s="79">
         <v>900</v>
       </c>
-      <c r="G37" s="80"/>
+      <c r="G37" s="78"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="82" t="s">
+      <c r="B38" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C38" s="82" t="s">
+      <c r="C38" s="80" t="s">
         <v>3487</v>
       </c>
-      <c r="D38" s="81">
+      <c r="D38" s="79">
         <v>1150</v>
       </c>
-      <c r="E38" s="81">
+      <c r="E38" s="79">
         <v>1200</v>
       </c>
-      <c r="F38" s="81">
+      <c r="F38" s="79">
         <v>1400</v>
       </c>
-      <c r="G38" s="80"/>
+      <c r="G38" s="78"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="82" t="s">
+      <c r="B39" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C39" s="82" t="s">
+      <c r="C39" s="80" t="s">
         <v>3485</v>
       </c>
-      <c r="D39" s="81">
+      <c r="D39" s="79">
         <v>2780</v>
       </c>
-      <c r="E39" s="81">
+      <c r="E39" s="79">
         <v>3590</v>
       </c>
-      <c r="F39" s="81">
+      <c r="F39" s="79">
         <v>2300</v>
       </c>
-      <c r="G39" s="80"/>
+      <c r="G39" s="78"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="82" t="s">
+      <c r="B40" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C40" s="82" t="s">
+      <c r="C40" s="80" t="s">
         <v>3488</v>
       </c>
-      <c r="D40" s="81">
+      <c r="D40" s="79">
         <v>3490</v>
       </c>
-      <c r="E40" s="81">
+      <c r="E40" s="79">
         <v>32840</v>
       </c>
-      <c r="F40" s="81">
+      <c r="F40" s="79">
         <v>3070</v>
       </c>
-      <c r="G40" s="80"/>
+      <c r="G40" s="78"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="82" t="s">
+      <c r="B41" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C41" s="82" t="s">
+      <c r="C41" s="80" t="s">
         <v>3484</v>
       </c>
-      <c r="D41" s="81">
+      <c r="D41" s="79">
         <v>4700</v>
       </c>
-      <c r="E41" s="81">
+      <c r="E41" s="79">
         <v>4700</v>
       </c>
-      <c r="F41" s="81">
+      <c r="F41" s="79">
         <v>4700</v>
       </c>
-      <c r="G41" s="80"/>
+      <c r="G41" s="78"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="82" t="s">
+      <c r="B42" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C42" s="82" t="s">
+      <c r="C42" s="80" t="s">
         <v>3483</v>
       </c>
-      <c r="D42" s="81">
+      <c r="D42" s="79">
         <v>5250</v>
       </c>
-      <c r="E42" s="81">
+      <c r="E42" s="79">
         <v>5000</v>
       </c>
-      <c r="F42" s="81">
+      <c r="F42" s="79">
         <v>5500</v>
       </c>
-      <c r="G42" s="80"/>
+      <c r="G42" s="78"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="82" t="s">
+      <c r="B43" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C43" s="82" t="s">
+      <c r="C43" s="80" t="s">
         <v>3486</v>
       </c>
-      <c r="D43" s="81">
+      <c r="D43" s="79">
         <v>6980</v>
       </c>
-      <c r="E43" s="81">
+      <c r="E43" s="79">
         <v>6310</v>
       </c>
-      <c r="F43" s="81">
+      <c r="F43" s="79">
         <v>6375</v>
       </c>
-      <c r="G43" s="80"/>
+      <c r="G43" s="78"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B44" s="82" t="s">
+      <c r="B44" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C44" s="82" t="s">
+      <c r="C44" s="80" t="s">
         <v>3482</v>
       </c>
-      <c r="D44" s="81">
+      <c r="D44" s="79">
         <v>11250</v>
       </c>
-      <c r="E44" s="81">
+      <c r="E44" s="79">
         <v>11250</v>
       </c>
-      <c r="F44" s="81">
+      <c r="F44" s="79">
         <v>11750</v>
       </c>
-      <c r="G44" s="80"/>
+      <c r="G44" s="78"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B45" s="82" t="s">
+      <c r="B45" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C45" s="82" t="s">
+      <c r="C45" s="80" t="s">
         <v>3481</v>
       </c>
-      <c r="D45" s="81">
+      <c r="D45" s="79">
         <v>24500</v>
       </c>
-      <c r="E45" s="81">
+      <c r="E45" s="79">
         <v>23500</v>
       </c>
-      <c r="F45" s="81">
+      <c r="F45" s="79">
         <v>24500</v>
       </c>
-      <c r="G45" s="80"/>
+      <c r="G45" s="78"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B46" s="82" t="s">
+      <c r="B46" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C46" s="82" t="s">
+      <c r="C46" s="80" t="s">
         <v>3480</v>
       </c>
-      <c r="D46" s="81">
+      <c r="D46" s="79">
         <v>56900</v>
       </c>
-      <c r="E46" s="81">
+      <c r="E46" s="79">
         <v>62800</v>
       </c>
-      <c r="F46" s="81">
+      <c r="F46" s="79">
         <v>60870</v>
       </c>
-      <c r="G46" s="80"/>
+      <c r="G46" s="78"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B47" s="82" t="s">
+      <c r="B47" s="80" t="s">
         <v>3493</v>
       </c>
-      <c r="C47" s="82" t="s">
+      <c r="C47" s="80" t="s">
         <v>3478</v>
       </c>
-      <c r="D47" s="81">
+      <c r="D47" s="79">
         <v>24290</v>
       </c>
-      <c r="E47" s="81">
+      <c r="E47" s="79">
         <v>24050</v>
       </c>
-      <c r="F47" s="81">
+      <c r="F47" s="79">
         <v>26600</v>
       </c>
-      <c r="G47" s="80"/>
+      <c r="G47" s="78"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B48" s="82" t="s">
+      <c r="B48" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C48" s="82" t="s">
+      <c r="C48" s="80" t="s">
         <v>3492</v>
       </c>
-      <c r="D48" s="81">
+      <c r="D48" s="79">
         <v>775</v>
       </c>
-      <c r="E48" s="81">
+      <c r="E48" s="79">
         <v>750</v>
       </c>
-      <c r="F48" s="81">
+      <c r="F48" s="79">
         <v>700</v>
       </c>
-      <c r="G48" s="80"/>
+      <c r="G48" s="78"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B49" s="82" t="s">
+      <c r="B49" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C49" s="82" t="s">
+      <c r="C49" s="80" t="s">
         <v>3312</v>
       </c>
-      <c r="D49" s="81">
+      <c r="D49" s="79">
         <v>700</v>
       </c>
-      <c r="E49" s="81">
+      <c r="E49" s="79">
         <v>750</v>
       </c>
-      <c r="F49" s="81">
+      <c r="F49" s="79">
         <v>750</v>
       </c>
-      <c r="G49" s="80"/>
+      <c r="G49" s="78"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B50" s="82" t="s">
+      <c r="B50" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C50" s="82" t="s">
+      <c r="C50" s="80" t="s">
         <v>3491</v>
       </c>
-      <c r="D50" s="81">
+      <c r="D50" s="79">
         <v>300</v>
       </c>
-      <c r="E50" s="81">
+      <c r="E50" s="79">
         <v>100</v>
       </c>
-      <c r="F50" s="81">
+      <c r="F50" s="79">
         <v>150</v>
       </c>
-      <c r="G50" s="80"/>
+      <c r="G50" s="78"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B51" s="82" t="s">
+      <c r="B51" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C51" s="82" t="s">
+      <c r="C51" s="80" t="s">
         <v>3490</v>
       </c>
-      <c r="D51" s="81">
+      <c r="D51" s="79">
         <v>2000</v>
       </c>
-      <c r="E51" s="81">
+      <c r="E51" s="79">
         <v>1800</v>
       </c>
-      <c r="F51" s="81">
+      <c r="F51" s="79">
         <v>1900</v>
       </c>
-      <c r="G51" s="80"/>
+      <c r="G51" s="78"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B52" s="82" t="s">
+      <c r="B52" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C52" s="82" t="s">
+      <c r="C52" s="80" t="s">
         <v>3489</v>
       </c>
-      <c r="D52" s="81">
+      <c r="D52" s="79">
         <v>2000</v>
       </c>
-      <c r="E52" s="81">
+      <c r="E52" s="79">
         <v>950</v>
       </c>
-      <c r="F52" s="81">
+      <c r="F52" s="79">
         <v>800</v>
       </c>
-      <c r="G52" s="80"/>
+      <c r="G52" s="78"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B53" s="82" t="s">
+      <c r="B53" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C53" s="82" t="s">
+      <c r="C53" s="80" t="s">
         <v>3488</v>
       </c>
-      <c r="D53" s="81">
+      <c r="D53" s="79">
         <v>1250</v>
       </c>
-      <c r="E53" s="81">
+      <c r="E53" s="79">
         <v>1250</v>
       </c>
-      <c r="F53" s="81">
+      <c r="F53" s="79">
         <v>1250</v>
       </c>
-      <c r="G53" s="80"/>
+      <c r="G53" s="78"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B54" s="82" t="s">
+      <c r="B54" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C54" s="82" t="s">
+      <c r="C54" s="80" t="s">
         <v>3487</v>
       </c>
-      <c r="D54" s="81">
+      <c r="D54" s="79">
         <v>1150</v>
       </c>
-      <c r="E54" s="81">
+      <c r="E54" s="79">
         <v>1200</v>
       </c>
-      <c r="F54" s="81">
+      <c r="F54" s="79">
         <v>1435</v>
       </c>
-      <c r="G54" s="80"/>
+      <c r="G54" s="78"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B55" s="82" t="s">
+      <c r="B55" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C55" s="82" t="s">
+      <c r="C55" s="80" t="s">
         <v>3486</v>
       </c>
-      <c r="D55" s="81">
+      <c r="D55" s="79">
         <v>3800</v>
       </c>
-      <c r="E55" s="81">
+      <c r="E55" s="79">
         <v>3700</v>
       </c>
-      <c r="F55" s="81">
+      <c r="F55" s="79">
         <v>3750</v>
       </c>
-      <c r="G55" s="80"/>
+      <c r="G55" s="78"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B56" s="82" t="s">
+      <c r="B56" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C56" s="82" t="s">
+      <c r="C56" s="80" t="s">
         <v>3485</v>
       </c>
-      <c r="D56" s="81">
+      <c r="D56" s="79">
         <v>5000</v>
       </c>
-      <c r="E56" s="81">
+      <c r="E56" s="79">
         <v>4800</v>
       </c>
-      <c r="F56" s="81">
+      <c r="F56" s="79">
         <v>4545</v>
       </c>
-      <c r="G56" s="80"/>
+      <c r="G56" s="78"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B57" s="82" t="s">
+      <c r="B57" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C57" s="82" t="s">
+      <c r="C57" s="80" t="s">
         <v>3484</v>
       </c>
-      <c r="D57" s="81">
+      <c r="D57" s="79">
         <v>5000</v>
       </c>
-      <c r="E57" s="81">
+      <c r="E57" s="79">
         <v>5000</v>
       </c>
-      <c r="F57" s="81">
+      <c r="F57" s="79">
         <v>5000</v>
       </c>
-      <c r="G57" s="80"/>
+      <c r="G57" s="78"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B58" s="82" t="s">
+      <c r="B58" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C58" s="82" t="s">
+      <c r="C58" s="80" t="s">
         <v>3483</v>
       </c>
-      <c r="D58" s="81">
+      <c r="D58" s="79">
         <v>5250</v>
       </c>
-      <c r="E58" s="81">
+      <c r="E58" s="79">
         <v>5335</v>
       </c>
-      <c r="F58" s="81">
+      <c r="F58" s="79">
         <v>5500</v>
       </c>
-      <c r="G58" s="80"/>
+      <c r="G58" s="78"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B59" s="82" t="s">
+      <c r="B59" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C59" s="82" t="s">
+      <c r="C59" s="80" t="s">
         <v>3482</v>
       </c>
-      <c r="D59" s="81">
+      <c r="D59" s="79">
         <v>10250</v>
       </c>
-      <c r="E59" s="81">
+      <c r="E59" s="79">
         <v>10250</v>
       </c>
-      <c r="F59" s="81">
+      <c r="F59" s="79">
         <v>10750</v>
       </c>
-      <c r="G59" s="80"/>
+      <c r="G59" s="78"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B60" s="82" t="s">
+      <c r="B60" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C60" s="82" t="s">
+      <c r="C60" s="80" t="s">
         <v>3481</v>
       </c>
-      <c r="D60" s="81">
+      <c r="D60" s="79">
         <v>14500</v>
       </c>
-      <c r="E60" s="81">
+      <c r="E60" s="79">
         <v>13500</v>
       </c>
-      <c r="F60" s="81">
+      <c r="F60" s="79">
         <v>15500</v>
       </c>
-      <c r="G60" s="80"/>
+      <c r="G60" s="78"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B61" s="82" t="s">
+      <c r="B61" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C61" s="82" t="s">
+      <c r="C61" s="80" t="s">
         <v>3480</v>
       </c>
-      <c r="D61" s="81">
+      <c r="D61" s="79">
         <v>72000</v>
       </c>
-      <c r="E61" s="81">
+      <c r="E61" s="79">
         <v>70000</v>
       </c>
-      <c r="F61" s="81">
+      <c r="F61" s="79">
         <v>70000</v>
       </c>
-      <c r="G61" s="80"/>
+      <c r="G61" s="78"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B62" s="82" t="s">
+      <c r="B62" s="80" t="s">
         <v>3479</v>
       </c>
-      <c r="C62" s="82" t="s">
+      <c r="C62" s="80" t="s">
         <v>3478</v>
       </c>
-      <c r="D62" s="81">
+      <c r="D62" s="79">
         <v>25000</v>
       </c>
-      <c r="E62" s="81">
+      <c r="E62" s="79">
         <v>24000</v>
       </c>
-      <c r="F62" s="81">
+      <c r="F62" s="79">
         <v>26000</v>
       </c>
-      <c r="G62" s="80"/>
+      <c r="G62" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -47850,38 +47880,55 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" style="49" customWidth="1"/>
     <col min="2" max="2" width="13.21875" style="49" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" style="49" customWidth="1"/>
-    <col min="4" max="4" width="9.21875" style="49"/>
-    <col min="5" max="5" width="11.21875" style="49" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="49" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="49" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" style="49" customWidth="1"/>
     <col min="6" max="6" width="10.44140625" style="49" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.21875" style="49" customWidth="1"/>
     <col min="8" max="8" width="10.21875" style="49" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.21875" style="49" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.21875" style="49"/>
+    <col min="10" max="11" width="9.21875" style="49"/>
+    <col min="12" max="12" width="10.77734375" style="49" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" style="49" customWidth="1"/>
+    <col min="14" max="16384" width="9.21875" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="131" t="s">
         <v>3450</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="116"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-    </row>
-    <row r="3" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="K1" s="135" t="s">
+        <v>3571</v>
+      </c>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
+      <c r="P1"/>
+    </row>
+    <row r="2" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="131"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="135"/>
+      <c r="P2"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
         <v>3448</v>
       </c>
@@ -47897,17 +47944,63 @@
       <c r="E3" s="63" t="s">
         <v>3443</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="65">
+      <c r="K3" s="136" t="s">
+        <v>3448</v>
+      </c>
+      <c r="L3" s="136" t="s">
+        <v>3320</v>
+      </c>
+      <c r="M3" s="136" t="s">
+        <v>3323</v>
+      </c>
+      <c r="N3" s="136" t="s">
+        <v>3447</v>
+      </c>
+      <c r="O3" s="136" t="s">
+        <v>3570</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="132">
         <v>1672</v>
       </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="66"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="133" t="str">
+        <f>VLOOKUP(A4,$A$9:$I$46,2,FALSE)</f>
+        <v>Dixon-Waite</v>
+      </c>
+      <c r="C4" s="133" t="str">
+        <f>VLOOKUP($A$4,$A$9:$I$46,3,FALSE)</f>
+        <v>Sherrie</v>
+      </c>
+      <c r="D4" s="133" t="str">
+        <f>VLOOKUP($A$4,$A$9:$I$46,4,FALSE)</f>
+        <v>MF</v>
+      </c>
+      <c r="E4" s="134">
+        <f>VLOOKUP($A$4,$A$9:$I$46,9,FALSE)</f>
+        <v>11.9</v>
+      </c>
+      <c r="K4" s="129">
+        <v>1284</v>
+      </c>
+      <c r="L4" s="130" t="str">
+        <f>VLOOKUP($K$4,$A$9:$I$46,2,FALSE)</f>
+        <v>Bellwood</v>
+      </c>
+      <c r="M4" s="130" t="str">
+        <f>VLOOKUP($K$4,$A$9:$I$46,3,FALSE)</f>
+        <v>Frank</v>
+      </c>
+      <c r="N4" s="130" t="str">
+        <f>VLOOKUP($K$4,$A$9:$I$46,4,FALSE)</f>
+        <v>MK</v>
+      </c>
+      <c r="O4" s="130">
+        <f>VLOOKUP($K$4,$A$9:$I$46,9,FALSE)</f>
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="117" t="s">
         <v>3449</v>
       </c>
@@ -47920,7 +48013,7 @@
       <c r="H7" s="117"/>
       <c r="I7" s="117"/>
     </row>
-    <row r="8" spans="1:9" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="116"/>
       <c r="B8" s="116"/>
       <c r="C8" s="116"/>
@@ -47931,7 +48024,7 @@
       <c r="H8" s="116"/>
       <c r="I8" s="116"/>
     </row>
-    <row r="9" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A9" s="63" t="s">
         <v>3448</v>
       </c>
@@ -47960,7 +48053,7 @@
         <v>3443</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="62">
         <v>1054</v>
       </c>
@@ -47989,7 +48082,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="62">
         <v>1056</v>
       </c>
@@ -48018,7 +48111,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="62">
         <v>1067</v>
       </c>
@@ -48047,7 +48140,7 @@
         <v>14.55</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="62">
         <v>1075</v>
       </c>
@@ -48076,7 +48169,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="62">
         <v>1078</v>
       </c>
@@ -48105,7 +48198,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="62">
         <v>1152</v>
       </c>
@@ -48134,7 +48227,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="62">
         <v>1196</v>
       </c>
@@ -49037,9 +49130,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:E2"/>
     <mergeCell ref="A7:I8"/>
+    <mergeCell ref="K1:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/Advanced Excel for practice.xlsx
+++ b/Advanced Excel for practice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f1c7af14bfcc0abe/Desktop/DA DS ITV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{2BAC444C-25A8-4E7A-A263-1D3A79421BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8E940C1-7243-44C3-84F7-696EB153E310}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{2BAC444C-25A8-4E7A-A263-1D3A79421BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{145843CB-FBCD-4E23-A15C-2B528761A34A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="645" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="645" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formulas" sheetId="19" r:id="rId1"/>
@@ -30,8 +30,8 @@
     <sheet name="Cleaning data" sheetId="27" r:id="rId15"/>
     <sheet name="Formula Formatting" sheetId="41" r:id="rId16"/>
     <sheet name="Date_Time Functions" sheetId="42" r:id="rId17"/>
-    <sheet name="Dates_Time" sheetId="32" r:id="rId18"/>
-    <sheet name="Connecticut" sheetId="37" r:id="rId19"/>
+    <sheet name="Connecticut" sheetId="37" r:id="rId18"/>
+    <sheet name="Dates_Time" sheetId="32" r:id="rId19"/>
     <sheet name="Maine" sheetId="39" r:id="rId20"/>
     <sheet name="New Hampshire" sheetId="38" r:id="rId21"/>
     <sheet name="Consolidate Summary" sheetId="40" r:id="rId22"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6366" uniqueCount="3572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6367" uniqueCount="3573">
   <si>
     <t>State</t>
   </si>
@@ -10819,6 +10819,9 @@
   </si>
   <si>
     <t>Empolyee lookup</t>
+  </si>
+  <si>
+    <t>(</t>
   </si>
 </sst>
 </file>
@@ -11821,6 +11824,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="17" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="11" xfId="17" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="17" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="8" borderId="11" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="11" xfId="17" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="14" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11830,11 +11845,17 @@
     <xf numFmtId="0" fontId="33" fillId="14" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="6" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="6" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="12" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -11869,24 +11890,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="11" xfId="17" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="17" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="8" borderId="11" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="11" xfId="17" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent2" xfId="12" builtinId="34"/>
@@ -15619,16 +15622,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>132080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>425450</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>21590</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -15658,8 +15661,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7213600" y="228600"/>
-          <a:ext cx="2082800" cy="1035050"/>
+          <a:off x="10309860" y="1061720"/>
+          <a:ext cx="2056130" cy="1040130"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15681,15 +15684,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>196850</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:colOff>151130</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>59690</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>355600</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>309880</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -15719,8 +15722,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7143750" y="1517650"/>
-          <a:ext cx="2082800" cy="1035050"/>
+          <a:off x="6955790" y="1179830"/>
+          <a:ext cx="2056130" cy="1037590"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16616,15 +16619,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="131" t="s">
         <v>3463</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
@@ -16637,11 +16640,11 @@
       <c r="C3" s="73" t="s">
         <v>3459</v>
       </c>
-      <c r="E3" s="118" t="s">
+      <c r="E3" s="126" t="s">
         <v>3461</v>
       </c>
-      <c r="F3" s="119"/>
-      <c r="G3" s="120"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="128"/>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="70" t="s">
@@ -16771,10 +16774,10 @@
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="121" t="s">
+      <c r="A12" s="129" t="s">
         <v>3452</v>
       </c>
-      <c r="B12" s="122"/>
+      <c r="B12" s="130"/>
       <c r="C12" s="66" t="s">
         <v>3451</v>
       </c>
@@ -16813,21 +16816,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A2" s="125" t="s">
+      <c r="A2" s="133" t="s">
         <v>3477</v>
       </c>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
     </row>
     <row r="4" spans="1:7" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="124" t="s">
+      <c r="A4" s="132" t="s">
         <v>3476</v>
       </c>
-      <c r="B4" s="124"/>
+      <c r="B4" s="132"/>
       <c r="E4" s="74" t="s">
         <v>3547</v>
       </c>
@@ -16844,30 +16847,39 @@
       <c r="A6" s="75" t="s">
         <v>3466</v>
       </c>
-      <c r="B6" s="64"/>
+      <c r="B6" s="64">
+        <f>HLOOKUP(B5,A11:G14,MATCH(A12,A11:A14,0),FALSE)</f>
+        <v>90</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="75" t="s">
         <v>3465</v>
       </c>
-      <c r="B7" s="64"/>
+      <c r="B7" s="64">
+        <f t="shared" ref="B7:B8" si="0">HLOOKUP(B6,A12:G15,MATCH(A13,A12:A15,0),FALSE)</f>
+        <v>95</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="75" t="s">
         <v>3464</v>
       </c>
-      <c r="B8" s="64"/>
+      <c r="B8" s="64">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="124" t="s">
+      <c r="A10" s="132" t="s">
         <v>3474</v>
       </c>
-      <c r="B10" s="124"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="124"/>
-      <c r="G10" s="124"/>
+      <c r="B10" s="132"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
     </row>
     <row r="11" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" s="75" t="s">
@@ -17075,7 +17087,10 @@
       <c r="F5" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="36"/>
+      <c r="G5" s="36">
+        <f>INDEX(A1:D18,18,2)</f>
+        <v>25347</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
@@ -17313,7 +17328,9 @@
       <c r="C2" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="D2" s="30"/>
+      <c r="D2" s="30" t="s">
+        <v>3572</v>
+      </c>
       <c r="K2" s="43"/>
       <c r="L2" s="43"/>
       <c r="M2" s="43"/>
@@ -36385,7 +36402,7 @@
       </c>
       <c r="C2" s="105">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -36421,7 +36438,7 @@
       </c>
       <c r="F5" s="109">
         <f ca="1">F3-C2</f>
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -36437,7 +36454,7 @@
       </c>
       <c r="F6" s="102">
         <f ca="1">NETWORKDAYS(C2,F3)</f>
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -36446,7 +36463,7 @@
       </c>
       <c r="C7" s="102">
         <f ca="1">DAY(TODAY())</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>3538</v>
@@ -36541,7 +36558,7 @@
       </c>
       <c r="C16" s="110">
         <f ca="1">DATEDIF(E15,TODAY(),"YD")/365*100</f>
-        <v>76.438356164383563</v>
+        <v>77.534246575342465</v>
       </c>
     </row>
   </sheetData>
@@ -36552,6 +36569,145 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A33BC-64DB-41FD-B8F4-E5501B24DD5E}">
+  <sheetPr>
+    <tabColor rgb="FF99FFCC"/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.21875" style="90" customWidth="1"/>
+    <col min="2" max="16384" width="8.77734375" style="90"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="136" t="s">
+        <v>3513</v>
+      </c>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="94" t="s">
+        <v>3512</v>
+      </c>
+      <c r="B3" s="93" t="s">
+        <v>3511</v>
+      </c>
+      <c r="C3" s="93" t="s">
+        <v>3510</v>
+      </c>
+      <c r="D3" s="93" t="s">
+        <v>3509</v>
+      </c>
+      <c r="E3" s="93" t="s">
+        <v>3508</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="90" t="s">
+        <v>3487</v>
+      </c>
+      <c r="B4" s="90">
+        <v>200</v>
+      </c>
+      <c r="C4" s="90">
+        <v>800</v>
+      </c>
+      <c r="D4" s="90">
+        <v>900</v>
+      </c>
+      <c r="E4" s="90">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="90" t="s">
+        <v>3507</v>
+      </c>
+      <c r="B5" s="90">
+        <v>400</v>
+      </c>
+      <c r="C5" s="90">
+        <v>100</v>
+      </c>
+      <c r="D5" s="90">
+        <v>800</v>
+      </c>
+      <c r="E5" s="90">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="90" t="s">
+        <v>3489</v>
+      </c>
+      <c r="B6" s="90">
+        <v>200</v>
+      </c>
+      <c r="C6" s="90">
+        <v>500</v>
+      </c>
+      <c r="D6" s="90">
+        <v>500</v>
+      </c>
+      <c r="E6" s="90">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="90" t="s">
+        <v>3506</v>
+      </c>
+      <c r="B7" s="90">
+        <v>200</v>
+      </c>
+      <c r="C7" s="90">
+        <v>300</v>
+      </c>
+      <c r="D7" s="90">
+        <v>500</v>
+      </c>
+      <c r="E7" s="90">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="92" t="s">
+        <v>3505</v>
+      </c>
+      <c r="B9" s="91">
+        <f>SUM(B4:B7)</f>
+        <v>1000</v>
+      </c>
+      <c r="C9" s="91">
+        <f>SUM(C4:C7)</f>
+        <v>1700</v>
+      </c>
+      <c r="D9" s="91">
+        <f>SUM(D4:D7)</f>
+        <v>2700</v>
+      </c>
+      <c r="E9" s="91">
+        <f>SUM(E4:E7)</f>
+        <v>1100</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter alignWithMargins="0">
+    <oddHeader>&amp;A</oddHeader>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D22298B0-C3E2-46DB-AEEF-43FC52BC4C0A}">
   <sheetPr>
     <tabColor rgb="FFFF6699"/>
@@ -36659,11 +36815,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A12" s="127" t="s">
+      <c r="A12" s="135" t="s">
         <v>3328</v>
       </c>
-      <c r="B12" s="127"/>
-      <c r="C12" s="127"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="135"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="52" t="s">
@@ -36701,145 +36857,6 @@
     <oddFooter>Page &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A33BC-64DB-41FD-B8F4-E5501B24DD5E}">
-  <sheetPr>
-    <tabColor rgb="FF99FFCC"/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.21875" style="90" customWidth="1"/>
-    <col min="2" max="16384" width="8.77734375" style="90"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="128" t="s">
-        <v>3513</v>
-      </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="94" t="s">
-        <v>3512</v>
-      </c>
-      <c r="B3" s="93" t="s">
-        <v>3511</v>
-      </c>
-      <c r="C3" s="93" t="s">
-        <v>3510</v>
-      </c>
-      <c r="D3" s="93" t="s">
-        <v>3509</v>
-      </c>
-      <c r="E3" s="93" t="s">
-        <v>3508</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="90" t="s">
-        <v>3487</v>
-      </c>
-      <c r="B4" s="90">
-        <v>200</v>
-      </c>
-      <c r="C4" s="90">
-        <v>800</v>
-      </c>
-      <c r="D4" s="90">
-        <v>900</v>
-      </c>
-      <c r="E4" s="90">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="90" t="s">
-        <v>3507</v>
-      </c>
-      <c r="B5" s="90">
-        <v>400</v>
-      </c>
-      <c r="C5" s="90">
-        <v>100</v>
-      </c>
-      <c r="D5" s="90">
-        <v>800</v>
-      </c>
-      <c r="E5" s="90">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="90" t="s">
-        <v>3489</v>
-      </c>
-      <c r="B6" s="90">
-        <v>200</v>
-      </c>
-      <c r="C6" s="90">
-        <v>500</v>
-      </c>
-      <c r="D6" s="90">
-        <v>500</v>
-      </c>
-      <c r="E6" s="90">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="90" t="s">
-        <v>3506</v>
-      </c>
-      <c r="B7" s="90">
-        <v>200</v>
-      </c>
-      <c r="C7" s="90">
-        <v>300</v>
-      </c>
-      <c r="D7" s="90">
-        <v>500</v>
-      </c>
-      <c r="E7" s="90">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="92" t="s">
-        <v>3505</v>
-      </c>
-      <c r="B9" s="91">
-        <f>SUM(B4:B7)</f>
-        <v>1000</v>
-      </c>
-      <c r="C9" s="91">
-        <f>SUM(C4:C7)</f>
-        <v>1700</v>
-      </c>
-      <c r="D9" s="91">
-        <f>SUM(D4:D7)</f>
-        <v>2700</v>
-      </c>
-      <c r="E9" s="91">
-        <f>SUM(E4:E7)</f>
-        <v>1100</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter alignWithMargins="0">
-    <oddHeader>&amp;A</oddHeader>
-    <oddFooter>Page &amp;P</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -37261,13 +37278,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="136" t="s">
         <v>3515</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
@@ -37406,13 +37423,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="136" t="s">
         <v>3514</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="94" t="s">
@@ -37545,11 +37562,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="128"/>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
+      <c r="A1" s="136"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="94"/>
@@ -38014,14 +38031,14 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="119" t="s">
         <v>3504</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="115"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="121"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="89" t="s">
@@ -47899,33 +47916,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="122" t="s">
         <v>3450</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="K1" s="135" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="K1" s="125" t="s">
         <v>3571</v>
       </c>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="125"/>
+      <c r="O1" s="125"/>
       <c r="P1"/>
     </row>
     <row r="2" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="131"/>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
+      <c r="A2" s="122"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
       <c r="P2"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -47944,85 +47961,85 @@
       <c r="E3" s="63" t="s">
         <v>3443</v>
       </c>
-      <c r="K3" s="136" t="s">
+      <c r="K3" s="118" t="s">
         <v>3448</v>
       </c>
-      <c r="L3" s="136" t="s">
+      <c r="L3" s="118" t="s">
         <v>3320</v>
       </c>
-      <c r="M3" s="136" t="s">
+      <c r="M3" s="118" t="s">
         <v>3323</v>
       </c>
-      <c r="N3" s="136" t="s">
+      <c r="N3" s="118" t="s">
         <v>3447</v>
       </c>
-      <c r="O3" s="136" t="s">
+      <c r="O3" s="118" t="s">
         <v>3570</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="132">
+      <c r="A4" s="115">
         <v>1672</v>
       </c>
-      <c r="B4" s="133" t="str">
+      <c r="B4" s="116" t="str">
         <f>VLOOKUP(A4,$A$9:$I$46,2,FALSE)</f>
         <v>Dixon-Waite</v>
       </c>
-      <c r="C4" s="133" t="str">
+      <c r="C4" s="116" t="str">
         <f>VLOOKUP($A$4,$A$9:$I$46,3,FALSE)</f>
         <v>Sherrie</v>
       </c>
-      <c r="D4" s="133" t="str">
+      <c r="D4" s="116" t="str">
         <f>VLOOKUP($A$4,$A$9:$I$46,4,FALSE)</f>
         <v>MF</v>
       </c>
-      <c r="E4" s="134">
+      <c r="E4" s="117">
         <f>VLOOKUP($A$4,$A$9:$I$46,9,FALSE)</f>
         <v>11.9</v>
       </c>
-      <c r="K4" s="129">
+      <c r="K4" s="113">
         <v>1284</v>
       </c>
-      <c r="L4" s="130" t="str">
+      <c r="L4" s="114" t="str">
         <f>VLOOKUP($K$4,$A$9:$I$46,2,FALSE)</f>
         <v>Bellwood</v>
       </c>
-      <c r="M4" s="130" t="str">
+      <c r="M4" s="114" t="str">
         <f>VLOOKUP($K$4,$A$9:$I$46,3,FALSE)</f>
         <v>Frank</v>
       </c>
-      <c r="N4" s="130" t="str">
+      <c r="N4" s="114" t="str">
         <f>VLOOKUP($K$4,$A$9:$I$46,4,FALSE)</f>
         <v>MK</v>
       </c>
-      <c r="O4" s="130">
+      <c r="O4" s="114">
         <f>VLOOKUP($K$4,$A$9:$I$46,9,FALSE)</f>
         <v>12.3</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="117" t="s">
+      <c r="A7" s="123" t="s">
         <v>3449</v>
       </c>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+      <c r="H7" s="123"/>
+      <c r="I7" s="123"/>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="116"/>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="116"/>
-      <c r="F8" s="116"/>
-      <c r="G8" s="116"/>
-      <c r="H8" s="116"/>
-      <c r="I8" s="116"/>
+      <c r="A8" s="124"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
     </row>
     <row r="9" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A9" s="63" t="s">
